--- a/research/traditional_assets/database/data/singapore/singapore_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_precious_metals.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="catalist_5tp" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0819</v>
+        <v>0.0789</v>
+      </c>
+      <c r="E2">
+        <v>0.3720000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.04841567866334753</v>
+        <v>0.2156328626978021</v>
       </c>
       <c r="H2">
-        <v>-0.04841567866334753</v>
+        <v>0.1236198041213533</v>
       </c>
       <c r="I2">
-        <v>-0.2496835576557951</v>
+        <v>-0.1409307354806513</v>
       </c>
       <c r="J2">
-        <v>-0.2496835576557951</v>
+        <v>-0.1316024629893129</v>
       </c>
       <c r="K2">
-        <v>-19.486</v>
+        <v>-12.047</v>
       </c>
       <c r="L2">
-        <v>-0.2055398506392135</v>
+        <v>-0.1252521261774552</v>
       </c>
       <c r="M2">
-        <v>0.578</v>
+        <v>0.95</v>
       </c>
       <c r="N2">
-        <v>0.002064359441408621</v>
+        <v>0.005350002815790956</v>
       </c>
       <c r="O2">
-        <v>-0.02966232166683773</v>
+        <v>-0.07885780692288537</v>
       </c>
       <c r="P2">
-        <v>0.578</v>
+        <v>0.593</v>
       </c>
       <c r="Q2">
-        <v>0.002064359441408621</v>
+        <v>0.003339528073435828</v>
       </c>
       <c r="R2">
-        <v>-0.02966232166683773</v>
+        <v>-0.04922387316344318</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.3757894736842105</v>
       </c>
       <c r="U2">
-        <v>19.12</v>
+        <v>8.218</v>
       </c>
       <c r="V2">
-        <v>0.06828815314832673</v>
+        <v>0.04628034014754745</v>
       </c>
       <c r="W2">
-        <v>-0.1914614249087095</v>
+        <v>0.01533209186840472</v>
       </c>
       <c r="X2">
-        <v>0.0549369242098971</v>
+        <v>0.1041589124331721</v>
       </c>
       <c r="Y2">
-        <v>-0.2463983491186066</v>
+        <v>-0.08882682056476736</v>
       </c>
       <c r="Z2">
-        <v>0.4665229757792278</v>
+        <v>0.4510927680330176</v>
       </c>
       <c r="AA2">
-        <v>-0.1280198286281706</v>
+        <v>-0.06162201581606713</v>
       </c>
       <c r="AB2">
-        <v>0.05463923853233191</v>
+        <v>0.1040516760226008</v>
       </c>
       <c r="AC2">
-        <v>-0.1829734652492805</v>
+        <v>-0.1653300427926861</v>
       </c>
       <c r="AD2">
-        <v>39.641</v>
+        <v>34.398</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>39.641</v>
+        <v>34.398</v>
       </c>
       <c r="AG2">
-        <v>20.521</v>
+        <v>26.18</v>
       </c>
       <c r="AH2">
-        <v>0.1240211368734572</v>
+        <v>0.1622792119565218</v>
       </c>
       <c r="AI2">
-        <v>0.174359583377318</v>
+        <v>0.1567264144925687</v>
       </c>
       <c r="AJ2">
-        <v>0.0682870177797152</v>
+        <v>0.1284907975460123</v>
       </c>
       <c r="AK2">
-        <v>0.0985487341042683</v>
+        <v>0.123923127899271</v>
       </c>
       <c r="AL2">
-        <v>0.7150000000000001</v>
+        <v>0.9410000000000001</v>
       </c>
       <c r="AM2">
-        <v>-0.111</v>
+        <v>-0.359</v>
       </c>
       <c r="AN2">
-        <v>-9.218837209302324</v>
+        <v>2.798860862489829</v>
       </c>
       <c r="AO2">
-        <v>-33.10629370629371</v>
+        <v>-14.40488841657811</v>
       </c>
       <c r="AP2">
-        <v>-4.772325581395347</v>
+        <v>2.130187144019528</v>
       </c>
       <c r="AQ2">
-        <v>213.2522522522523</v>
+        <v>37.75766016713092</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bonanza Goldfields Corp. (OTCPK:BONZ)</t>
+          <t>CNMC Goldmine Holdings Limited (Catalist:5TP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,101 +723,122 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0789</v>
+      </c>
+      <c r="E3">
+        <v>0.3720000000000001</v>
+      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="I3">
-        <v>-0.384180790960452</v>
+        <v>0.1335294117647059</v>
       </c>
       <c r="J3">
-        <v>-0.384180790960452</v>
+        <v>0.08049915966386556</v>
       </c>
       <c r="K3">
-        <v>-0.068</v>
+        <v>1.76</v>
       </c>
       <c r="L3">
-        <v>-0.384180790960452</v>
+        <v>0.05176470588235294</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.95</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01588628762541806</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.5397727272727273</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.593</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.00991638795986622</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.3369318181818182</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.357</v>
+      </c>
+      <c r="T3">
+        <v>0.3757894736842105</v>
       </c>
       <c r="U3">
-        <v>0.003</v>
+        <v>6.21</v>
       </c>
       <c r="V3">
-        <v>0.0002362204724409449</v>
+        <v>0.1038461538461539</v>
       </c>
       <c r="W3">
-        <v>0.02775510204081633</v>
+        <v>0.04444444444444445</v>
       </c>
       <c r="X3">
-        <v>0.05477045294224128</v>
+        <v>0.1042485975904507</v>
       </c>
       <c r="Y3">
-        <v>-0.02701535090142496</v>
+        <v>-0.05980415314600623</v>
       </c>
       <c r="Z3">
-        <v>-0.1383893666927287</v>
+        <v>1.250597712141832</v>
       </c>
       <c r="AA3">
-        <v>0.05316653635652854</v>
+        <v>0.1006720649049703</v>
       </c>
       <c r="AB3">
-        <v>0.05464753411164727</v>
+        <v>0.1040341247693082</v>
       </c>
       <c r="AC3">
-        <v>-0.001480997755118729</v>
+        <v>-0.00336205986433781</v>
       </c>
       <c r="AD3">
-        <v>0.054</v>
+        <v>0.198</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.054</v>
+        <v>0.198</v>
       </c>
       <c r="AG3">
-        <v>0.051</v>
+        <v>-6.012</v>
       </c>
       <c r="AH3">
-        <v>0.004233965814646385</v>
+        <v>0.003300110003666789</v>
       </c>
       <c r="AI3">
-        <v>-3.599999999999998</v>
+        <v>0.004459660345060588</v>
       </c>
       <c r="AJ3">
-        <v>0.003999686299113795</v>
+        <v>-0.1117721424853127</v>
       </c>
       <c r="AK3">
-        <v>-2.833333333333332</v>
+        <v>-0.1574316539226982</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.05299999999999999</v>
+      </c>
+      <c r="AN3">
+        <v>0.02129032258064516</v>
+      </c>
+      <c r="AO3">
+        <v>28.73417721518987</v>
+      </c>
+      <c r="AP3">
+        <v>-0.6464516129032257</v>
+      </c>
+      <c r="AQ3">
+        <v>-85.66037735849058</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +858,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-1.38</v>
+        <v>-1.48</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -856,31 +882,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.177</v>
+        <v>0.132</v>
       </c>
       <c r="V4">
-        <v>0.001845672575599583</v>
+        <v>0.002986425339366516</v>
       </c>
       <c r="W4">
-        <v>-0.01276595744680851</v>
+        <v>-0.01378026070763501</v>
       </c>
       <c r="X4">
-        <v>0.05463094295301654</v>
+        <v>0.1040692272758935</v>
       </c>
       <c r="Y4">
-        <v>-0.06739690039982506</v>
+        <v>-0.1178494879835285</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.004318893770042077</v>
+        <v>-0.005828973261333856</v>
       </c>
       <c r="AB4">
-        <v>0.05463094295301654</v>
+        <v>0.1040692272758935</v>
       </c>
       <c r="AC4">
-        <v>-0.05894983672305862</v>
+        <v>-0.1098982005372273</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -892,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.177</v>
+        <v>-0.132</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -901,19 +927,19 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.001849085381778674</v>
+        <v>-0.002995370790596351</v>
       </c>
       <c r="AK4">
-        <v>-0.001650765227609748</v>
+        <v>-0.001248014522350806</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.037</v>
+        <v>-0.319</v>
       </c>
       <c r="AQ4">
-        <v>12.5945945945946</v>
+        <v>1.959247648902821</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +950,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wilton Resources Corporation Limited (Catalist:5F7)</t>
+          <t>Shen Yao Holdings Limited (Catalist:A78)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -933,22 +959,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-10.37470725995316</v>
+        <v>0.1797101449275362</v>
       </c>
       <c r="H5">
-        <v>-10.37470725995316</v>
+        <v>0.1797101449275362</v>
       </c>
       <c r="I5">
-        <v>-9.742388758782202</v>
+        <v>-0.02246376811594203</v>
       </c>
       <c r="J5">
-        <v>-9.742388758782202</v>
+        <v>-0.02246376811594203</v>
       </c>
       <c r="K5">
-        <v>-3.92</v>
+        <v>-0.997</v>
       </c>
       <c r="L5">
-        <v>-9.180327868852459</v>
+        <v>-0.01806159420289855</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -972,70 +998,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.39</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="V5">
-        <v>0.01358885017421603</v>
+        <v>0.02729083665338645</v>
       </c>
       <c r="W5">
-        <v>-0.3213114754098361</v>
+        <v>-0.03058282208588957</v>
       </c>
       <c r="X5">
-        <v>0.08606975037122568</v>
+        <v>0.1269472616015234</v>
       </c>
       <c r="Y5">
-        <v>-0.4073812257810617</v>
+        <v>-0.1575300836874129</v>
       </c>
       <c r="Z5">
-        <v>0.01280359820089955</v>
+        <v>1.392181588902901</v>
       </c>
       <c r="AA5">
-        <v>-0.1247376311844078</v>
+        <v>-0.03127364438839849</v>
       </c>
       <c r="AB5">
-        <v>0.05531100837040492</v>
+        <v>0.1037450606778218</v>
       </c>
       <c r="AC5">
-        <v>-0.1800486395548127</v>
+        <v>-0.1350187050662203</v>
       </c>
       <c r="AD5">
-        <v>27.5</v>
+        <v>10.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>27.5</v>
+        <v>10.6</v>
       </c>
       <c r="AG5">
-        <v>27.11</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.4893238434163701</v>
+        <v>0.2969187675070027</v>
       </c>
       <c r="AI5">
-        <v>0.8008153756552125</v>
+        <v>0.3569023569023568</v>
       </c>
       <c r="AJ5">
-        <v>0.4857552409962372</v>
+        <v>0.283164358132229</v>
       </c>
       <c r="AK5">
-        <v>0.7985272459499263</v>
+        <v>0.3417198001033948</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.783</v>
       </c>
       <c r="AM5">
-        <v>-0.552</v>
+        <v>0.77</v>
       </c>
       <c r="AN5">
-        <v>-6.997455470737913</v>
+        <v>1.766666666666667</v>
+      </c>
+      <c r="AO5">
+        <v>-1.583652618135377</v>
       </c>
       <c r="AP5">
-        <v>-6.898218829516539</v>
+        <v>1.6525</v>
       </c>
       <c r="AQ5">
-        <v>7.536231884057971</v>
+        <v>-1.61038961038961</v>
       </c>
     </row>
     <row r="6">
@@ -1046,7 +1075,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CNMC Goldmine Holdings Limited (Catalist:5TP)</t>
+          <t>Wilton Resources Corporation Limited (Catalist:5F7)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1054,119 +1083,110 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.0819</v>
-      </c>
       <c r="G6">
-        <v>0.1068441064638783</v>
+        <v>-8.216374269005847</v>
       </c>
       <c r="H6">
-        <v>0.1068441064638783</v>
+        <v>-8.216374269005847</v>
       </c>
       <c r="I6">
-        <v>-0.15893536121673</v>
+        <v>-9.444444444444443</v>
       </c>
       <c r="J6">
-        <v>-0.15893536121673</v>
+        <v>-9.444444444444443</v>
       </c>
       <c r="K6">
-        <v>-2.6</v>
+        <v>1.69</v>
       </c>
       <c r="L6">
-        <v>-0.09885931558935361</v>
+        <v>4.941520467836257</v>
       </c>
       <c r="M6">
-        <v>0.578</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.009383116883116882</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0.2223076923076923</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>0.578</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.009383116883116882</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0.2223076923076923</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>13.3</v>
+        <v>1.02</v>
       </c>
       <c r="V6">
-        <v>0.2159090909090909</v>
+        <v>0.02481751824817518</v>
       </c>
       <c r="W6">
-        <v>-0.06161137440758294</v>
+        <v>0.2109862671660424</v>
       </c>
       <c r="X6">
-        <v>0.05510339547755291</v>
+        <v>0.1351761281002293</v>
       </c>
       <c r="Y6">
-        <v>-0.1167147698851358</v>
+        <v>0.07581013906581316</v>
       </c>
       <c r="Z6">
-        <v>0.8261347573425474</v>
+        <v>0.009738041002277906</v>
       </c>
       <c r="AA6">
-        <v>-0.1313020260719334</v>
+        <v>-0.09197038724373577</v>
       </c>
       <c r="AB6">
-        <v>0.05459626487181496</v>
+        <v>0.1036709932754161</v>
       </c>
       <c r="AC6">
-        <v>-0.1858982909437484</v>
+        <v>-0.1956413805191519</v>
       </c>
       <c r="AD6">
-        <v>0.887</v>
+        <v>23.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.887</v>
+        <v>23.6</v>
       </c>
       <c r="AG6">
-        <v>-12.413</v>
+        <v>22.58</v>
       </c>
       <c r="AH6">
-        <v>0.01419495255013043</v>
+        <v>0.3647604327666151</v>
       </c>
       <c r="AI6">
-        <v>0.01903964625324661</v>
+        <v>0.6723646723646723</v>
       </c>
       <c r="AJ6">
-        <v>-0.2523634293614166</v>
+        <v>0.3545854271356784</v>
       </c>
       <c r="AK6">
-        <v>-0.3729083425962086</v>
+        <v>0.6625586854460095</v>
       </c>
       <c r="AL6">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.04900000000000002</v>
+        <v>-0.757</v>
       </c>
       <c r="AN6">
-        <v>0.22175</v>
-      </c>
-      <c r="AO6">
-        <v>-23.88571428571429</v>
+        <v>-7.840531561461795</v>
       </c>
       <c r="AP6">
-        <v>-3.10325</v>
+        <v>-7.501661129568108</v>
       </c>
       <c r="AQ6">
-        <v>85.30612244897956</v>
+        <v>4.266842800528401</v>
       </c>
     </row>
     <row r="7">
@@ -1177,7 +1197,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shen Yao Holdings Limited (Catalist:A78)</t>
+          <t>Kainantu Resources Ltd. (TSXV:KRL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1185,23 +1205,8 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="G7">
-        <v>-0.04374079528718704</v>
-      </c>
-      <c r="H7">
-        <v>-0.04374079528718704</v>
-      </c>
-      <c r="I7">
-        <v>-0.2106038291605302</v>
-      </c>
-      <c r="J7">
-        <v>-0.2106038291605302</v>
-      </c>
       <c r="K7">
-        <v>-10.7</v>
-      </c>
-      <c r="L7">
-        <v>-0.1575846833578792</v>
+        <v>-1.32</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1225,73 +1230,61 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>4.15</v>
+        <v>0.145</v>
       </c>
       <c r="V7">
-        <v>0.05533333333333334</v>
+        <v>0.03403755868544601</v>
       </c>
       <c r="W7">
-        <v>-0.3531353135313531</v>
+        <v>-0.2568093385214008</v>
       </c>
       <c r="X7">
-        <v>0.05953067156223309</v>
+        <v>0.1040692272758935</v>
       </c>
       <c r="Y7">
-        <v>-0.4126659850935862</v>
+        <v>-0.3608785657972943</v>
       </c>
       <c r="Z7">
-        <v>2.161731932505572</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>-0.4552690226042662</v>
+        <v>-0.3217821782178218</v>
       </c>
       <c r="AB7">
-        <v>0.06181054593824753</v>
+        <v>0.1040692272758935</v>
       </c>
       <c r="AC7">
-        <v>-0.5170795685425138</v>
+        <v>-0.4258514054937154</v>
       </c>
       <c r="AD7">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>7.049999999999999</v>
+        <v>-0.145</v>
       </c>
       <c r="AH7">
-        <v>0.1299303944315545</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.3303834808259587</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.08592321755027421</v>
+        <v>-0.03523693803159173</v>
       </c>
       <c r="AK7">
-        <v>0.2369747899159663</v>
+        <v>-0.02418682235195996</v>
       </c>
       <c r="AL7">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.527</v>
-      </c>
-      <c r="AN7">
-        <v>-2.562929061784897</v>
-      </c>
-      <c r="AO7">
-        <v>-26.48148148148148</v>
-      </c>
-      <c r="AP7">
-        <v>-1.613272311212814</v>
-      </c>
-      <c r="AQ7">
-        <v>-27.13472485768501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1302,7 +1295,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kainantu Resources Ltd. (TSXV:KRL)</t>
+          <t>Bonanza Goldfields Corp. (OTCPK:BONZ)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1310,8 +1303,23 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="G8">
+        <v>1.016566265060241</v>
+      </c>
+      <c r="H8">
+        <v>-0.3162650602409639</v>
+      </c>
+      <c r="I8">
+        <v>-1.762048192771084</v>
+      </c>
+      <c r="J8">
+        <v>-1.762048192771084</v>
+      </c>
       <c r="K8">
-        <v>-0.8179999999999999</v>
+        <v>-11.7</v>
+      </c>
+      <c r="L8">
+        <v>-1.762048192771084</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1335,16 +1343,22 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1.1</v>
+        <v>0.026</v>
       </c>
       <c r="V8">
-        <v>0.180623973727422</v>
+        <v>0.008360128617363344</v>
+      </c>
+      <c r="W8">
+        <v>167.1428571428571</v>
       </c>
       <c r="X8">
-        <v>0.05463094295301654</v>
+        <v>0.1040692272758935</v>
+      </c>
+      <c r="Y8">
+        <v>167.0387879155812</v>
       </c>
       <c r="AB8">
-        <v>0.05463094295301654</v>
+        <v>0.1040692272758935</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1356,24 +1370,8736 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-1.1</v>
+        <v>-0.026</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8">
-        <v>-0.2204408817635271</v>
+        <v>-0.008430609597924773</v>
       </c>
       <c r="AK8">
-        <v>-0.2722772277227724</v>
+        <v>0.01455767077267637</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CNMC Goldmine Holdings Limited (Catalist:5TP)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Catalist:5TP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Precious Metals</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.00330011000366679</v>
+      </c>
+      <c r="F2">
+        <v>0.15</v>
+      </c>
+      <c r="G2">
+        <v>59.8</v>
+      </c>
+      <c r="H2">
+        <v>51.9644572412626</v>
+      </c>
+      <c r="I2">
+        <v>53.788</v>
+      </c>
+      <c r="J2">
+        <v>54.7541572412625</v>
+      </c>
+      <c r="K2">
+        <v>0.198</v>
+      </c>
+      <c r="L2">
+        <v>8.999700000000001</v>
+      </c>
+      <c r="M2">
+        <v>0.104034124769308</v>
+      </c>
+      <c r="N2">
+        <v>0.102473711980358</v>
+      </c>
+      <c r="O2">
+        <v>0.039259</v>
+      </c>
+      <c r="P2">
+        <v>0.039259</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.104248597590451</v>
+      </c>
+      <c r="T2">
+        <v>0.113629249388657</v>
+      </c>
+      <c r="U2">
+        <v>1.10662729530197</v>
+      </c>
+      <c r="V2">
+        <v>1.26523856750336</v>
+      </c>
+      <c r="W2">
+        <v>10.45371937579973</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>59.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AH2">
+        <v>4.85</v>
+      </c>
+      <c r="AI2">
+        <v>3.859999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>0.198</v>
+      </c>
+      <c r="AK2">
+        <v>0.198</v>
+      </c>
+      <c r="AL2">
+        <v>0.158</v>
+      </c>
+      <c r="AM2">
+        <v>0.198</v>
+      </c>
+      <c r="AN2">
+        <v>6.21</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1040692272758935</v>
+      </c>
+      <c r="C2">
+        <v>59.97665764288254</v>
+      </c>
+      <c r="D2">
+        <v>53.76665764288254</v>
+      </c>
+      <c r="E2">
+        <v>-0.198</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>6.21</v>
+      </c>
+      <c r="H2">
+        <v>59.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K2">
+        <v>4.85</v>
+      </c>
+      <c r="L2">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="O2">
+        <v>0.7564999999999998</v>
+      </c>
+      <c r="P2">
+        <v>3.693500000000001</v>
+      </c>
+      <c r="Q2">
+        <v>8.543500000000002</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1040692272758935</v>
+      </c>
+      <c r="T2">
+        <v>1.103594440613497</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1039495795895245</v>
+      </c>
+      <c r="C3">
+        <v>59.44949316425582</v>
+      </c>
+      <c r="D3">
+        <v>53.83947316425582</v>
+      </c>
+      <c r="E3">
+        <v>0.4019799999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.59998</v>
+      </c>
+      <c r="G3">
+        <v>6.21</v>
+      </c>
+      <c r="H3">
+        <v>59.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K3">
+        <v>4.85</v>
+      </c>
+      <c r="L3">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M3">
+        <v>0.027419086</v>
+      </c>
+      <c r="N3">
+        <v>4.422580914000001</v>
+      </c>
+      <c r="O3">
+        <v>0.7518387553799999</v>
+      </c>
+      <c r="P3">
+        <v>3.670742158620001</v>
+      </c>
+      <c r="Q3">
+        <v>8.520742158620001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1046164339288126</v>
+      </c>
+      <c r="T3">
+        <v>1.112846798044903</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>162.2957089087507</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1038299319031554</v>
+      </c>
+      <c r="C4">
+        <v>58.9225261794177</v>
+      </c>
+      <c r="D4">
+        <v>53.9124861794177</v>
+      </c>
+      <c r="E4">
+        <v>1.00196</v>
+      </c>
+      <c r="F4">
+        <v>1.19996</v>
+      </c>
+      <c r="G4">
+        <v>6.21</v>
+      </c>
+      <c r="H4">
+        <v>59.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K4">
+        <v>4.85</v>
+      </c>
+      <c r="L4">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M4">
+        <v>0.054838172</v>
+      </c>
+      <c r="N4">
+        <v>4.395161828000001</v>
+      </c>
+      <c r="O4">
+        <v>0.7471775107599998</v>
+      </c>
+      <c r="P4">
+        <v>3.647984317240001</v>
+      </c>
+      <c r="Q4">
+        <v>8.49798431724</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1051748080644443</v>
+      </c>
+      <c r="T4">
+        <v>1.122287979097359</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W4">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>81.14785445437533</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1037102842167864</v>
+      </c>
+      <c r="C5">
+        <v>58.39575749293765</v>
+      </c>
+      <c r="D5">
+        <v>53.98569749293765</v>
+      </c>
+      <c r="E5">
+        <v>1.60194</v>
+      </c>
+      <c r="F5">
+        <v>1.79994</v>
+      </c>
+      <c r="G5">
+        <v>6.21</v>
+      </c>
+      <c r="H5">
+        <v>59.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K5">
+        <v>4.85</v>
+      </c>
+      <c r="L5">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M5">
+        <v>0.082257258</v>
+      </c>
+      <c r="N5">
+        <v>4.367742742000001</v>
+      </c>
+      <c r="O5">
+        <v>0.7425162661399998</v>
+      </c>
+      <c r="P5">
+        <v>3.625226475860001</v>
+      </c>
+      <c r="Q5">
+        <v>8.475226475860001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.105744695068852</v>
+      </c>
+      <c r="T5">
+        <v>1.131923823676669</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>54.09856963625023</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1035906365304174</v>
+      </c>
+      <c r="C6">
+        <v>57.86918791376133</v>
+      </c>
+      <c r="D6">
+        <v>54.05910791376133</v>
+      </c>
+      <c r="E6">
+        <v>2.20192</v>
+      </c>
+      <c r="F6">
+        <v>2.39992</v>
+      </c>
+      <c r="G6">
+        <v>6.21</v>
+      </c>
+      <c r="H6">
+        <v>59.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K6">
+        <v>4.85</v>
+      </c>
+      <c r="L6">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M6">
+        <v>0.109676344</v>
+      </c>
+      <c r="N6">
+        <v>4.340323656000001</v>
+      </c>
+      <c r="O6">
+        <v>0.7378550215199998</v>
+      </c>
+      <c r="P6">
+        <v>3.602468634480001</v>
+      </c>
+      <c r="Q6">
+        <v>8.452468634480001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1063264547191848</v>
+      </c>
+      <c r="T6">
+        <v>1.141760415018048</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>40.57392722718766</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1034709888440484</v>
+      </c>
+      <c r="C7">
+        <v>57.34281825524053</v>
+      </c>
+      <c r="D7">
+        <v>54.13271825524053</v>
+      </c>
+      <c r="E7">
+        <v>2.8019</v>
+      </c>
+      <c r="F7">
+        <v>2.9999</v>
+      </c>
+      <c r="G7">
+        <v>6.21</v>
+      </c>
+      <c r="H7">
+        <v>59.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K7">
+        <v>4.85</v>
+      </c>
+      <c r="L7">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M7">
+        <v>0.13709543</v>
+      </c>
+      <c r="N7">
+        <v>4.312904570000001</v>
+      </c>
+      <c r="O7">
+        <v>0.7331937768999998</v>
+      </c>
+      <c r="P7">
+        <v>3.579710793100001</v>
+      </c>
+      <c r="Q7">
+        <v>8.4297107931</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1069204619411036</v>
+      </c>
+      <c r="T7">
+        <v>1.151804092492929</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>32.45914178175013</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1033513411576794</v>
+      </c>
+      <c r="C8">
+        <v>56.81664933516305</v>
+      </c>
+      <c r="D8">
+        <v>54.20652933516305</v>
+      </c>
+      <c r="E8">
+        <v>3.40188</v>
+      </c>
+      <c r="F8">
+        <v>3.59988</v>
+      </c>
+      <c r="G8">
+        <v>6.21</v>
+      </c>
+      <c r="H8">
+        <v>59.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K8">
+        <v>4.85</v>
+      </c>
+      <c r="L8">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M8">
+        <v>0.164514516</v>
+      </c>
+      <c r="N8">
+        <v>4.285485484000001</v>
+      </c>
+      <c r="O8">
+        <v>0.7285325322799999</v>
+      </c>
+      <c r="P8">
+        <v>3.556952951720001</v>
+      </c>
+      <c r="Q8">
+        <v>8.406952951720001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1075271076145525</v>
+      </c>
+      <c r="T8">
+        <v>1.162061465233234</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>27.04928481812512</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1032316934713103</v>
+      </c>
+      <c r="C9">
+        <v>56.29068197578313</v>
+      </c>
+      <c r="D9">
+        <v>54.28054197578313</v>
+      </c>
+      <c r="E9">
+        <v>4.00186</v>
+      </c>
+      <c r="F9">
+        <v>4.19986</v>
+      </c>
+      <c r="G9">
+        <v>6.21</v>
+      </c>
+      <c r="H9">
+        <v>59.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K9">
+        <v>4.85</v>
+      </c>
+      <c r="L9">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M9">
+        <v>0.191933602</v>
+      </c>
+      <c r="N9">
+        <v>4.258066398000001</v>
+      </c>
+      <c r="O9">
+        <v>0.72387128766</v>
+      </c>
+      <c r="P9">
+        <v>3.534195110340002</v>
+      </c>
+      <c r="Q9">
+        <v>8.384195110340002</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1081467994315165</v>
+      </c>
+      <c r="T9">
+        <v>1.17253942663462</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>23.18510127267866</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1031120457849413</v>
+      </c>
+      <c r="C10">
+        <v>55.76491700385183</v>
+      </c>
+      <c r="D10">
+        <v>54.35475700385184</v>
+      </c>
+      <c r="E10">
+        <v>4.601839999999999</v>
+      </c>
+      <c r="F10">
+        <v>4.79984</v>
+      </c>
+      <c r="G10">
+        <v>6.21</v>
+      </c>
+      <c r="H10">
+        <v>59.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K10">
+        <v>4.85</v>
+      </c>
+      <c r="L10">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M10">
+        <v>0.219352688</v>
+      </c>
+      <c r="N10">
+        <v>4.230647312000001</v>
+      </c>
+      <c r="O10">
+        <v>0.7192100430399999</v>
+      </c>
+      <c r="P10">
+        <v>3.511437268960001</v>
+      </c>
+      <c r="Q10">
+        <v>8.361437268960001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1087799628097188</v>
+      </c>
+      <c r="T10">
+        <v>1.183245169805602</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>20.28696361359383</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1029923980985723</v>
+      </c>
+      <c r="C11">
+        <v>55.23935525064802</v>
+      </c>
+      <c r="D11">
+        <v>54.42917525064802</v>
+      </c>
+      <c r="E11">
+        <v>5.201819999999999</v>
+      </c>
+      <c r="F11">
+        <v>5.399819999999999</v>
+      </c>
+      <c r="G11">
+        <v>6.21</v>
+      </c>
+      <c r="H11">
+        <v>59.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K11">
+        <v>4.85</v>
+      </c>
+      <c r="L11">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M11">
+        <v>0.246771774</v>
+      </c>
+      <c r="N11">
+        <v>4.203228226000001</v>
+      </c>
+      <c r="O11">
+        <v>0.7145487984199999</v>
+      </c>
+      <c r="P11">
+        <v>3.488679427580001</v>
+      </c>
+      <c r="Q11">
+        <v>8.338679427580001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.109427041866563</v>
+      </c>
+      <c r="T11">
+        <v>1.194186204035287</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W11">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>18.03285654541674</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1028727504122033</v>
+      </c>
+      <c r="C12">
+        <v>54.7139975520092</v>
+      </c>
+      <c r="D12">
+        <v>54.5037975520092</v>
+      </c>
+      <c r="E12">
+        <v>5.8018</v>
+      </c>
+      <c r="F12">
+        <v>5.9998</v>
+      </c>
+      <c r="G12">
+        <v>6.21</v>
+      </c>
+      <c r="H12">
+        <v>59.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K12">
+        <v>4.85</v>
+      </c>
+      <c r="L12">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M12">
+        <v>0.27419086</v>
+      </c>
+      <c r="N12">
+        <v>4.175809140000001</v>
+      </c>
+      <c r="O12">
+        <v>0.7098875537999999</v>
+      </c>
+      <c r="P12">
+        <v>3.465921586200001</v>
+      </c>
+      <c r="Q12">
+        <v>8.315921586200002</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1100885004580037</v>
+      </c>
+      <c r="T12">
+        <v>1.205370372358964</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W12">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>16.22957089087507</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1027531027258343</v>
+      </c>
+      <c r="C13">
+        <v>54.1888447483629</v>
+      </c>
+      <c r="D13">
+        <v>54.5786247483629</v>
+      </c>
+      <c r="E13">
+        <v>6.40178</v>
+      </c>
+      <c r="F13">
+        <v>6.59978</v>
+      </c>
+      <c r="G13">
+        <v>6.21</v>
+      </c>
+      <c r="H13">
+        <v>59.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K13">
+        <v>4.85</v>
+      </c>
+      <c r="L13">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M13">
+        <v>0.301609946</v>
+      </c>
+      <c r="N13">
+        <v>4.148390054000001</v>
+      </c>
+      <c r="O13">
+        <v>0.7052263091799998</v>
+      </c>
+      <c r="P13">
+        <v>3.443163744820001</v>
+      </c>
+      <c r="Q13">
+        <v>8.293163744820001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1107648232874542</v>
+      </c>
+      <c r="T13">
+        <v>1.216805870307893</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W13">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>14.75415535534097</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1026334550394652</v>
+      </c>
+      <c r="C14">
+        <v>53.66389768475828</v>
+      </c>
+      <c r="D14">
+        <v>54.65365768475828</v>
+      </c>
+      <c r="E14">
+        <v>7.001759999999999</v>
+      </c>
+      <c r="F14">
+        <v>7.199759999999999</v>
+      </c>
+      <c r="G14">
+        <v>6.21</v>
+      </c>
+      <c r="H14">
+        <v>59.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K14">
+        <v>4.85</v>
+      </c>
+      <c r="L14">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M14">
+        <v>0.329029032</v>
+      </c>
+      <c r="N14">
+        <v>4.120970968000001</v>
+      </c>
+      <c r="O14">
+        <v>0.7005650645599999</v>
+      </c>
+      <c r="P14">
+        <v>3.420405903440001</v>
+      </c>
+      <c r="Q14">
+        <v>8.27040590344</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1114565170903014</v>
+      </c>
+      <c r="T14">
+        <v>1.22850126593748</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.52464240906256</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1026864473530962</v>
+      </c>
+      <c r="C15">
+        <v>53.03065993920229</v>
+      </c>
+      <c r="D15">
+        <v>54.62039993920229</v>
+      </c>
+      <c r="E15">
+        <v>7.601739999999999</v>
+      </c>
+      <c r="F15">
+        <v>7.79974</v>
+      </c>
+      <c r="G15">
+        <v>6.21</v>
+      </c>
+      <c r="H15">
+        <v>59.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K15">
+        <v>4.85</v>
+      </c>
+      <c r="L15">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M15">
+        <v>0.368927702</v>
+      </c>
+      <c r="N15">
+        <v>4.081072298000001</v>
+      </c>
+      <c r="O15">
+        <v>0.69378229066</v>
+      </c>
+      <c r="P15">
+        <v>3.387290007340002</v>
+      </c>
+      <c r="Q15">
+        <v>8.23729000734</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1121641119001106</v>
+      </c>
+      <c r="T15">
+        <v>1.240465521236712</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W15">
+        <v>0.039259</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>12.06198389515353</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1025800796667272</v>
+      </c>
+      <c r="C16">
+        <v>52.49747680240024</v>
+      </c>
+      <c r="D16">
+        <v>54.68719680240024</v>
+      </c>
+      <c r="E16">
+        <v>8.20172</v>
+      </c>
+      <c r="F16">
+        <v>8.39972</v>
+      </c>
+      <c r="G16">
+        <v>6.21</v>
+      </c>
+      <c r="H16">
+        <v>59.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K16">
+        <v>4.85</v>
+      </c>
+      <c r="L16">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M16">
+        <v>0.397306756</v>
+      </c>
+      <c r="N16">
+        <v>4.052693244000001</v>
+      </c>
+      <c r="O16">
+        <v>0.6889578514799999</v>
+      </c>
+      <c r="P16">
+        <v>3.363735392520002</v>
+      </c>
+      <c r="Q16">
+        <v>8.21373539252</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1128881624031712</v>
+      </c>
+      <c r="T16">
+        <v>1.252708015031275</v>
+      </c>
+      <c r="U16">
+        <v>0.0473</v>
+      </c>
+      <c r="V16">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W16">
+        <v>0.039259</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.20041361692828</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1024737119803582</v>
+      </c>
+      <c r="C17">
+        <v>51.96445724126255</v>
+      </c>
+      <c r="D17">
+        <v>54.75415724126255</v>
+      </c>
+      <c r="E17">
+        <v>8.801699999999999</v>
+      </c>
+      <c r="F17">
+        <v>8.999699999999999</v>
+      </c>
+      <c r="G17">
+        <v>6.21</v>
+      </c>
+      <c r="H17">
+        <v>59.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K17">
+        <v>4.85</v>
+      </c>
+      <c r="L17">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M17">
+        <v>0.4256858099999999</v>
+      </c>
+      <c r="N17">
+        <v>4.024314190000001</v>
+      </c>
+      <c r="O17">
+        <v>0.6841334122999999</v>
+      </c>
+      <c r="P17">
+        <v>3.340180777700001</v>
+      </c>
+      <c r="Q17">
+        <v>8.1901807777</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1136292493886567</v>
+      </c>
+      <c r="T17">
+        <v>1.265238567503357</v>
+      </c>
+      <c r="U17">
+        <v>0.0473</v>
+      </c>
+      <c r="V17">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W17">
+        <v>0.039259</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>10.45371937579973</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1028719842939892</v>
+      </c>
+      <c r="C18">
+        <v>51.11459602666961</v>
+      </c>
+      <c r="D18">
+        <v>54.50427602666961</v>
+      </c>
+      <c r="E18">
+        <v>9.401679999999999</v>
+      </c>
+      <c r="F18">
+        <v>9.599679999999999</v>
+      </c>
+      <c r="G18">
+        <v>6.21</v>
+      </c>
+      <c r="H18">
+        <v>59.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K18">
+        <v>4.85</v>
+      </c>
+      <c r="L18">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M18">
+        <v>0.4905436479999999</v>
+      </c>
+      <c r="N18">
+        <v>3.959456352000001</v>
+      </c>
+      <c r="O18">
+        <v>0.6731075798399999</v>
+      </c>
+      <c r="P18">
+        <v>3.286348772160001</v>
+      </c>
+      <c r="Q18">
+        <v>8.136348772160002</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1143879813023681</v>
+      </c>
+      <c r="T18">
+        <v>1.278067466462869</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W18">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>9.071567878094308</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1027971566076201</v>
+      </c>
+      <c r="C19">
+        <v>50.56138973702392</v>
+      </c>
+      <c r="D19">
+        <v>54.55104973702392</v>
+      </c>
+      <c r="E19">
+        <v>10.00166</v>
+      </c>
+      <c r="F19">
+        <v>10.19966</v>
+      </c>
+      <c r="G19">
+        <v>6.21</v>
+      </c>
+      <c r="H19">
+        <v>59.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K19">
+        <v>4.85</v>
+      </c>
+      <c r="L19">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M19">
+        <v>0.521202626</v>
+      </c>
+      <c r="N19">
+        <v>3.928797374000001</v>
+      </c>
+      <c r="O19">
+        <v>0.6678955535799999</v>
+      </c>
+      <c r="P19">
+        <v>3.260901820420001</v>
+      </c>
+      <c r="Q19">
+        <v>8.110901820420001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1151649959127954</v>
+      </c>
+      <c r="T19">
+        <v>1.291205495517792</v>
+      </c>
+      <c r="U19">
+        <v>0.0511</v>
+      </c>
+      <c r="V19">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W19">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.537946238206407</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1027223289212511</v>
+      </c>
+      <c r="C20">
+        <v>50.00826379553548</v>
+      </c>
+      <c r="D20">
+        <v>54.59790379553547</v>
+      </c>
+      <c r="E20">
+        <v>10.60164</v>
+      </c>
+      <c r="F20">
+        <v>10.79964</v>
+      </c>
+      <c r="G20">
+        <v>6.21</v>
+      </c>
+      <c r="H20">
+        <v>59.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K20">
+        <v>4.85</v>
+      </c>
+      <c r="L20">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M20">
+        <v>0.551861604</v>
+      </c>
+      <c r="N20">
+        <v>3.898138396000001</v>
+      </c>
+      <c r="O20">
+        <v>0.6626835273199999</v>
+      </c>
+      <c r="P20">
+        <v>3.235454868680001</v>
+      </c>
+      <c r="Q20">
+        <v>8.085454868680001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1159609620990868</v>
+      </c>
+      <c r="T20">
+        <v>1.304663964305761</v>
+      </c>
+      <c r="U20">
+        <v>0.0511</v>
+      </c>
+      <c r="V20">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W20">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.063615891639387</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1029471312348821</v>
+      </c>
+      <c r="C21">
+        <v>49.26776340988513</v>
+      </c>
+      <c r="D21">
+        <v>54.45738340988513</v>
+      </c>
+      <c r="E21">
+        <v>11.20162</v>
+      </c>
+      <c r="F21">
+        <v>11.39962</v>
+      </c>
+      <c r="G21">
+        <v>6.21</v>
+      </c>
+      <c r="H21">
+        <v>59.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K21">
+        <v>4.85</v>
+      </c>
+      <c r="L21">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M21">
+        <v>0.6041798600000001</v>
+      </c>
+      <c r="N21">
+        <v>3.845820140000001</v>
+      </c>
+      <c r="O21">
+        <v>0.6537894237999998</v>
+      </c>
+      <c r="P21">
+        <v>3.192030716200001</v>
+      </c>
+      <c r="Q21">
+        <v>8.042030716200001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1167765817714594</v>
+      </c>
+      <c r="T21">
+        <v>1.318454740965039</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W21">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>7.365356402313708</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1028880735485131</v>
+      </c>
+      <c r="C22">
+        <v>48.70462934065406</v>
+      </c>
+      <c r="D22">
+        <v>54.49422934065406</v>
+      </c>
+      <c r="E22">
+        <v>11.8016</v>
+      </c>
+      <c r="F22">
+        <v>11.9996</v>
+      </c>
+      <c r="G22">
+        <v>6.21</v>
+      </c>
+      <c r="H22">
+        <v>59.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K22">
+        <v>4.85</v>
+      </c>
+      <c r="L22">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M22">
+        <v>0.6359788000000001</v>
+      </c>
+      <c r="N22">
+        <v>3.814021200000001</v>
+      </c>
+      <c r="O22">
+        <v>0.6483836039999998</v>
+      </c>
+      <c r="P22">
+        <v>3.165637596000001</v>
+      </c>
+      <c r="Q22">
+        <v>8.015637596000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1176125919356414</v>
+      </c>
+      <c r="T22">
+        <v>1.332590287040798</v>
+      </c>
+      <c r="U22">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W22">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>6.997088582198024</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1028290158621441</v>
+      </c>
+      <c r="C23">
+        <v>48.14154516518285</v>
+      </c>
+      <c r="D23">
+        <v>54.53112516518284</v>
+      </c>
+      <c r="E23">
+        <v>12.40158</v>
+      </c>
+      <c r="F23">
+        <v>12.59958</v>
+      </c>
+      <c r="G23">
+        <v>6.21</v>
+      </c>
+      <c r="H23">
+        <v>59.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K23">
+        <v>4.85</v>
+      </c>
+      <c r="L23">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M23">
+        <v>0.66777774</v>
+      </c>
+      <c r="N23">
+        <v>3.782222260000001</v>
+      </c>
+      <c r="O23">
+        <v>0.6429777842</v>
+      </c>
+      <c r="P23">
+        <v>3.139244475800001</v>
+      </c>
+      <c r="Q23">
+        <v>7.989244475800001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1184697669141064</v>
+      </c>
+      <c r="T23">
+        <v>1.347083695042526</v>
+      </c>
+      <c r="U23">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W23">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>6.663893887807642</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1027699581757751</v>
+      </c>
+      <c r="C24">
+        <v>47.57851098488325</v>
+      </c>
+      <c r="D24">
+        <v>54.56807098488325</v>
+      </c>
+      <c r="E24">
+        <v>13.00156</v>
+      </c>
+      <c r="F24">
+        <v>13.19956</v>
+      </c>
+      <c r="G24">
+        <v>6.21</v>
+      </c>
+      <c r="H24">
+        <v>59.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K24">
+        <v>4.85</v>
+      </c>
+      <c r="L24">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M24">
+        <v>0.6995766800000001</v>
+      </c>
+      <c r="N24">
+        <v>3.750423320000001</v>
+      </c>
+      <c r="O24">
+        <v>0.6375719644</v>
+      </c>
+      <c r="P24">
+        <v>3.112851355600001</v>
+      </c>
+      <c r="Q24">
+        <v>7.962851355600001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1193489207381732</v>
+      </c>
+      <c r="T24">
+        <v>1.361948728890452</v>
+      </c>
+      <c r="U24">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W24">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.360989620180022</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1030927004894061</v>
+      </c>
+      <c r="C25">
+        <v>46.77723556066069</v>
+      </c>
+      <c r="D25">
+        <v>54.36677556066068</v>
+      </c>
+      <c r="E25">
+        <v>13.60154</v>
+      </c>
+      <c r="F25">
+        <v>13.79954</v>
+      </c>
+      <c r="G25">
+        <v>6.21</v>
+      </c>
+      <c r="H25">
+        <v>59.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K25">
+        <v>4.85</v>
+      </c>
+      <c r="L25">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M25">
+        <v>0.7589747</v>
+      </c>
+      <c r="N25">
+        <v>3.691025300000001</v>
+      </c>
+      <c r="O25">
+        <v>0.6274743009999999</v>
+      </c>
+      <c r="P25">
+        <v>3.063550999000001</v>
+      </c>
+      <c r="Q25">
+        <v>7.913550999000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1202509097265014</v>
+      </c>
+      <c r="T25">
+        <v>1.377199867513649</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W25">
+        <v>0.04565</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.863173041209412</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.103050242803037</v>
+      </c>
+      <c r="C26">
+        <v>46.20365168110251</v>
+      </c>
+      <c r="D26">
+        <v>54.39317168110252</v>
+      </c>
+      <c r="E26">
+        <v>14.20152</v>
+      </c>
+      <c r="F26">
+        <v>14.39952</v>
+      </c>
+      <c r="G26">
+        <v>6.21</v>
+      </c>
+      <c r="H26">
+        <v>59.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K26">
+        <v>4.85</v>
+      </c>
+      <c r="L26">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M26">
+        <v>0.7919735999999999</v>
+      </c>
+      <c r="N26">
+        <v>3.658026400000001</v>
+      </c>
+      <c r="O26">
+        <v>0.6218644879999999</v>
+      </c>
+      <c r="P26">
+        <v>3.036161912000001</v>
+      </c>
+      <c r="Q26">
+        <v>7.886161912</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.121176635267154</v>
+      </c>
+      <c r="T26">
+        <v>1.392852351890088</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W26">
+        <v>0.04565</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.618874164492354</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.103007785116668</v>
+      </c>
+      <c r="C27">
+        <v>45.63009344564848</v>
+      </c>
+      <c r="D27">
+        <v>54.41959344564847</v>
+      </c>
+      <c r="E27">
+        <v>14.8015</v>
+      </c>
+      <c r="F27">
+        <v>14.9995</v>
+      </c>
+      <c r="G27">
+        <v>6.21</v>
+      </c>
+      <c r="H27">
+        <v>59.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K27">
+        <v>4.85</v>
+      </c>
+      <c r="L27">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M27">
+        <v>0.8249725</v>
+      </c>
+      <c r="N27">
+        <v>3.625027500000001</v>
+      </c>
+      <c r="O27">
+        <v>0.616254675</v>
+      </c>
+      <c r="P27">
+        <v>3.008772825000001</v>
+      </c>
+      <c r="Q27">
+        <v>7.858772825000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.122127046822224</v>
+      </c>
+      <c r="T27">
+        <v>1.408922235849898</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.04565</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.394119197912659</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.102965327430299</v>
+      </c>
+      <c r="C28">
+        <v>45.05656089168698</v>
+      </c>
+      <c r="D28">
+        <v>54.44604089168698</v>
+      </c>
+      <c r="E28">
+        <v>15.40148</v>
+      </c>
+      <c r="F28">
+        <v>15.59948</v>
+      </c>
+      <c r="G28">
+        <v>6.21</v>
+      </c>
+      <c r="H28">
+        <v>59.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K28">
+        <v>4.85</v>
+      </c>
+      <c r="L28">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M28">
+        <v>0.8579713999999999</v>
+      </c>
+      <c r="N28">
+        <v>3.592028600000001</v>
+      </c>
+      <c r="O28">
+        <v>0.610644862</v>
+      </c>
+      <c r="P28">
+        <v>2.981383738000001</v>
+      </c>
+      <c r="Q28">
+        <v>7.831383738000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1231031451760797</v>
+      </c>
+      <c r="T28">
+        <v>1.425426440997812</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W28">
+        <v>0.04565</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.186653074916019</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.10292286974393</v>
+      </c>
+      <c r="C29">
+        <v>44.48305405667922</v>
+      </c>
+      <c r="D29">
+        <v>54.47251405667922</v>
+      </c>
+      <c r="E29">
+        <v>16.00146</v>
+      </c>
+      <c r="F29">
+        <v>16.19946</v>
+      </c>
+      <c r="G29">
+        <v>6.21</v>
+      </c>
+      <c r="H29">
+        <v>59.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K29">
+        <v>4.85</v>
+      </c>
+      <c r="L29">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M29">
+        <v>0.8909703000000001</v>
+      </c>
+      <c r="N29">
+        <v>3.559029700000001</v>
+      </c>
+      <c r="O29">
+        <v>0.6050350489999999</v>
+      </c>
+      <c r="P29">
+        <v>2.953994651000001</v>
+      </c>
+      <c r="Q29">
+        <v>7.803994651</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.124105985950589</v>
+      </c>
+      <c r="T29">
+        <v>1.442382816149778</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.04565</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.994554812882091</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1028804120575609</v>
+      </c>
+      <c r="C30">
+        <v>43.9095729781592</v>
+      </c>
+      <c r="D30">
+        <v>54.4990129781592</v>
+      </c>
+      <c r="E30">
+        <v>16.60144</v>
+      </c>
+      <c r="F30">
+        <v>16.79944</v>
+      </c>
+      <c r="G30">
+        <v>6.21</v>
+      </c>
+      <c r="H30">
+        <v>59.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K30">
+        <v>4.85</v>
+      </c>
+      <c r="L30">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M30">
+        <v>0.9239692</v>
+      </c>
+      <c r="N30">
+        <v>3.526030800000001</v>
+      </c>
+      <c r="O30">
+        <v>0.5994252359999999</v>
+      </c>
+      <c r="P30">
+        <v>2.926605564000001</v>
+      </c>
+      <c r="Q30">
+        <v>7.776605564</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1251366834132791</v>
+      </c>
+      <c r="T30">
+        <v>1.459810201722632</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W30">
+        <v>0.04565</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.816177855279159</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1028379543711919</v>
+      </c>
+      <c r="C31">
+        <v>43.33611769373402</v>
+      </c>
+      <c r="D31">
+        <v>54.52553769373402</v>
+      </c>
+      <c r="E31">
+        <v>17.20142</v>
+      </c>
+      <c r="F31">
+        <v>17.39942</v>
+      </c>
+      <c r="G31">
+        <v>6.21</v>
+      </c>
+      <c r="H31">
+        <v>59.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K31">
+        <v>4.85</v>
+      </c>
+      <c r="L31">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M31">
+        <v>0.9569681</v>
+      </c>
+      <c r="N31">
+        <v>3.493031900000001</v>
+      </c>
+      <c r="O31">
+        <v>0.5938154229999999</v>
+      </c>
+      <c r="P31">
+        <v>2.899216477000001</v>
+      </c>
+      <c r="Q31">
+        <v>7.749216477000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1261964146073126</v>
+      </c>
+      <c r="T31">
+        <v>1.477728499565144</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W31">
+        <v>0.04565</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.650102756821258</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1037416966848229</v>
+      </c>
+      <c r="C32">
+        <v>42.17705725217002</v>
+      </c>
+      <c r="D32">
+        <v>53.96645725217001</v>
+      </c>
+      <c r="E32">
+        <v>17.8014</v>
+      </c>
+      <c r="F32">
+        <v>17.9994</v>
+      </c>
+      <c r="G32">
+        <v>6.21</v>
+      </c>
+      <c r="H32">
+        <v>59.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K32">
+        <v>4.85</v>
+      </c>
+      <c r="L32">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M32">
+        <v>1.05836472</v>
+      </c>
+      <c r="N32">
+        <v>3.391635280000001</v>
+      </c>
+      <c r="O32">
+        <v>0.5765779975999999</v>
+      </c>
+      <c r="P32">
+        <v>2.815057282400001</v>
+      </c>
+      <c r="Q32">
+        <v>7.665057282400001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1272864238354613</v>
+      </c>
+      <c r="T32">
+        <v>1.496158748774584</v>
+      </c>
+      <c r="U32">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W32">
+        <v>0.04880400000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.204599714926251</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1037307789984539</v>
+      </c>
+      <c r="C33">
+        <v>41.58376281612321</v>
+      </c>
+      <c r="D33">
+        <v>53.97314281612321</v>
+      </c>
+      <c r="E33">
+        <v>18.40138</v>
+      </c>
+      <c r="F33">
+        <v>18.59938</v>
+      </c>
+      <c r="G33">
+        <v>6.21</v>
+      </c>
+      <c r="H33">
+        <v>59.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K33">
+        <v>4.85</v>
+      </c>
+      <c r="L33">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M33">
+        <v>1.093643544</v>
+      </c>
+      <c r="N33">
+        <v>3.356356456000001</v>
+      </c>
+      <c r="O33">
+        <v>0.57058059752</v>
+      </c>
+      <c r="P33">
+        <v>2.785775858480001</v>
+      </c>
+      <c r="Q33">
+        <v>7.635775858480001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1284080275339912</v>
+      </c>
+      <c r="T33">
+        <v>1.515123208106038</v>
+      </c>
+      <c r="U33">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W33">
+        <v>0.04880400000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.068967466057662</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1048353813120849</v>
+      </c>
+      <c r="C34">
+        <v>40.31565805407993</v>
+      </c>
+      <c r="D34">
+        <v>53.30501805407992</v>
+      </c>
+      <c r="E34">
+        <v>19.00136</v>
+      </c>
+      <c r="F34">
+        <v>19.19936</v>
+      </c>
+      <c r="G34">
+        <v>6.21</v>
+      </c>
+      <c r="H34">
+        <v>59.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K34">
+        <v>4.85</v>
+      </c>
+      <c r="L34">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M34">
+        <v>1.20955968</v>
+      </c>
+      <c r="N34">
+        <v>3.240440320000001</v>
+      </c>
+      <c r="O34">
+        <v>0.5508748543999999</v>
+      </c>
+      <c r="P34">
+        <v>2.689565465600001</v>
+      </c>
+      <c r="Q34">
+        <v>7.539565465600001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1295626195765954</v>
+      </c>
+      <c r="T34">
+        <v>1.534645445653122</v>
+      </c>
+      <c r="U34">
+        <v>0.063</v>
+      </c>
+      <c r="V34">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W34">
+        <v>0.05229</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.679024750560469</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1048593236257159</v>
+      </c>
+      <c r="C35">
+        <v>39.70137951682001</v>
+      </c>
+      <c r="D35">
+        <v>53.29071951682001</v>
+      </c>
+      <c r="E35">
+        <v>19.60134</v>
+      </c>
+      <c r="F35">
+        <v>19.79934</v>
+      </c>
+      <c r="G35">
+        <v>6.21</v>
+      </c>
+      <c r="H35">
+        <v>59.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K35">
+        <v>4.85</v>
+      </c>
+      <c r="L35">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M35">
+        <v>1.24735842</v>
+      </c>
+      <c r="N35">
+        <v>3.202641580000001</v>
+      </c>
+      <c r="O35">
+        <v>0.5444490685999999</v>
+      </c>
+      <c r="P35">
+        <v>2.658192511400001</v>
+      </c>
+      <c r="Q35">
+        <v>7.508192511400001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1307516770533073</v>
+      </c>
+      <c r="T35">
+        <v>1.554750436559821</v>
+      </c>
+      <c r="U35">
+        <v>0.063</v>
+      </c>
+      <c r="V35">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W35">
+        <v>0.05229</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>3.567539152058636</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1068868859393468</v>
+      </c>
+      <c r="C36">
+        <v>37.91773630314741</v>
+      </c>
+      <c r="D36">
+        <v>52.1070563031474</v>
+      </c>
+      <c r="E36">
+        <v>20.20132</v>
+      </c>
+      <c r="F36">
+        <v>20.39932</v>
+      </c>
+      <c r="G36">
+        <v>6.21</v>
+      </c>
+      <c r="H36">
+        <v>59.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K36">
+        <v>4.85</v>
+      </c>
+      <c r="L36">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M36">
+        <v>1.429992332</v>
+      </c>
+      <c r="N36">
+        <v>3.020007668000001</v>
+      </c>
+      <c r="O36">
+        <v>0.51340130356</v>
+      </c>
+      <c r="P36">
+        <v>2.506606364440001</v>
+      </c>
+      <c r="Q36">
+        <v>7.356606364440001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.131976766574768</v>
+      </c>
+      <c r="T36">
+        <v>1.575464669615208</v>
+      </c>
+      <c r="U36">
+        <v>0.0701</v>
+      </c>
+      <c r="V36">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W36">
+        <v>0.058183</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.111904798661537</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1069697582529778</v>
+      </c>
+      <c r="C37">
+        <v>37.27049406700701</v>
+      </c>
+      <c r="D37">
+        <v>52.05979406700701</v>
+      </c>
+      <c r="E37">
+        <v>20.8013</v>
+      </c>
+      <c r="F37">
+        <v>20.9993</v>
+      </c>
+      <c r="G37">
+        <v>6.21</v>
+      </c>
+      <c r="H37">
+        <v>59.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K37">
+        <v>4.85</v>
+      </c>
+      <c r="L37">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M37">
+        <v>1.47205093</v>
+      </c>
+      <c r="N37">
+        <v>2.977949070000001</v>
+      </c>
+      <c r="O37">
+        <v>0.5062513419</v>
+      </c>
+      <c r="P37">
+        <v>2.471697728100001</v>
+      </c>
+      <c r="Q37">
+        <v>7.3216977281</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1332395511584274</v>
+      </c>
+      <c r="T37">
+        <v>1.596816263687684</v>
+      </c>
+      <c r="U37">
+        <v>0.0701</v>
+      </c>
+      <c r="V37">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W37">
+        <v>0.058183</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.022993232985493</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1134170705666088</v>
+      </c>
+      <c r="C38">
+        <v>33.23907309303821</v>
+      </c>
+      <c r="D38">
+        <v>48.62835309303821</v>
+      </c>
+      <c r="E38">
+        <v>21.40128</v>
+      </c>
+      <c r="F38">
+        <v>21.59928</v>
+      </c>
+      <c r="G38">
+        <v>6.21</v>
+      </c>
+      <c r="H38">
+        <v>59.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K38">
+        <v>4.85</v>
+      </c>
+      <c r="L38">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M38">
+        <v>1.974174192</v>
+      </c>
+      <c r="N38">
+        <v>2.475825808000001</v>
+      </c>
+      <c r="O38">
+        <v>0.42089038736</v>
+      </c>
+      <c r="P38">
+        <v>2.054935420640001</v>
+      </c>
+      <c r="Q38">
+        <v>6.904935420640001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1345417977603263</v>
+      </c>
+      <c r="T38">
+        <v>1.618835095074924</v>
+      </c>
+      <c r="U38">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W38">
+        <v>0.07586200000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.254107068177093</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1136767328802398</v>
+      </c>
+      <c r="C39">
+        <v>32.51034449814091</v>
+      </c>
+      <c r="D39">
+        <v>48.49960449814091</v>
+      </c>
+      <c r="E39">
+        <v>22.00126</v>
+      </c>
+      <c r="F39">
+        <v>22.19926</v>
+      </c>
+      <c r="G39">
+        <v>6.21</v>
+      </c>
+      <c r="H39">
+        <v>59.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K39">
+        <v>4.85</v>
+      </c>
+      <c r="L39">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M39">
+        <v>2.029012364</v>
+      </c>
+      <c r="N39">
+        <v>2.420987636000001</v>
+      </c>
+      <c r="O39">
+        <v>0.41156789812</v>
+      </c>
+      <c r="P39">
+        <v>2.009419737880001</v>
+      </c>
+      <c r="Q39">
+        <v>6.859419737880001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1358853855241901</v>
+      </c>
+      <c r="T39">
+        <v>1.641552936982394</v>
+      </c>
+      <c r="U39">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W39">
+        <v>0.07586200000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.193185255523658</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1139363951938708</v>
+      </c>
+      <c r="C40">
+        <v>31.7822958534504</v>
+      </c>
+      <c r="D40">
+        <v>48.3715358534504</v>
+      </c>
+      <c r="E40">
+        <v>22.60124</v>
+      </c>
+      <c r="F40">
+        <v>22.79924</v>
+      </c>
+      <c r="G40">
+        <v>6.21</v>
+      </c>
+      <c r="H40">
+        <v>59.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K40">
+        <v>4.85</v>
+      </c>
+      <c r="L40">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M40">
+        <v>2.083850536</v>
+      </c>
+      <c r="N40">
+        <v>2.366149464000001</v>
+      </c>
+      <c r="O40">
+        <v>0.4022454088799999</v>
+      </c>
+      <c r="P40">
+        <v>1.963904055120001</v>
+      </c>
+      <c r="Q40">
+        <v>6.81390405512</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1372723148288238</v>
+      </c>
+      <c r="T40">
+        <v>1.665003612499783</v>
+      </c>
+      <c r="U40">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W40">
+        <v>0.07586200000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.135469854062508</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1141960575075017</v>
+      </c>
+      <c r="C41">
+        <v>31.05492178669848</v>
+      </c>
+      <c r="D41">
+        <v>48.24414178669848</v>
+      </c>
+      <c r="E41">
+        <v>23.20122</v>
+      </c>
+      <c r="F41">
+        <v>23.39922</v>
+      </c>
+      <c r="G41">
+        <v>6.21</v>
+      </c>
+      <c r="H41">
+        <v>59.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K41">
+        <v>4.85</v>
+      </c>
+      <c r="L41">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M41">
+        <v>2.138688708</v>
+      </c>
+      <c r="N41">
+        <v>2.311311292000001</v>
+      </c>
+      <c r="O41">
+        <v>0.39292291964</v>
+      </c>
+      <c r="P41">
+        <v>1.918388372360001</v>
+      </c>
+      <c r="Q41">
+        <v>6.76838837236</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1387047172254127</v>
+      </c>
+      <c r="T41">
+        <v>1.689223162624299</v>
+      </c>
+      <c r="U41">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W41">
+        <v>0.07586200000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.080714216778855</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1144557198211327</v>
+      </c>
+      <c r="C42">
+        <v>30.32821698206305</v>
+      </c>
+      <c r="D42">
+        <v>48.11741698206305</v>
+      </c>
+      <c r="E42">
+        <v>23.8012</v>
+      </c>
+      <c r="F42">
+        <v>23.9992</v>
+      </c>
+      <c r="G42">
+        <v>6.21</v>
+      </c>
+      <c r="H42">
+        <v>59.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K42">
+        <v>4.85</v>
+      </c>
+      <c r="L42">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M42">
+        <v>2.19352688</v>
+      </c>
+      <c r="N42">
+        <v>2.256473120000001</v>
+      </c>
+      <c r="O42">
+        <v>0.3836004304</v>
+      </c>
+      <c r="P42">
+        <v>1.872872689600001</v>
+      </c>
+      <c r="Q42">
+        <v>6.722872689600001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1401848663685545</v>
+      </c>
+      <c r="T42">
+        <v>1.714250031086299</v>
+      </c>
+      <c r="U42">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W42">
+        <v>0.07586200000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.028696361359383</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1218957121347637</v>
+      </c>
+      <c r="C43">
+        <v>26.36026649224844</v>
+      </c>
+      <c r="D43">
+        <v>44.74944649224844</v>
+      </c>
+      <c r="E43">
+        <v>24.40118</v>
+      </c>
+      <c r="F43">
+        <v>24.59918</v>
+      </c>
+      <c r="G43">
+        <v>6.21</v>
+      </c>
+      <c r="H43">
+        <v>59.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K43">
+        <v>4.85</v>
+      </c>
+      <c r="L43">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M43">
+        <v>2.76740775</v>
+      </c>
+      <c r="N43">
+        <v>1.682592250000001</v>
+      </c>
+      <c r="O43">
+        <v>0.2860406825</v>
+      </c>
+      <c r="P43">
+        <v>1.396551567500001</v>
+      </c>
+      <c r="Q43">
+        <v>6.246551567500001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1417151900589215</v>
+      </c>
+      <c r="T43">
+        <v>1.74012526797074</v>
+      </c>
+      <c r="U43">
+        <v>0.1125</v>
+      </c>
+      <c r="V43">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W43">
+        <v>0.09337500000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>1.608003012927893</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1223305044483947</v>
+      </c>
+      <c r="C44">
+        <v>25.57798502798161</v>
+      </c>
+      <c r="D44">
+        <v>44.56714502798161</v>
+      </c>
+      <c r="E44">
+        <v>25.00116</v>
+      </c>
+      <c r="F44">
+        <v>25.19916</v>
+      </c>
+      <c r="G44">
+        <v>6.21</v>
+      </c>
+      <c r="H44">
+        <v>59.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K44">
+        <v>4.85</v>
+      </c>
+      <c r="L44">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M44">
+        <v>2.8349055</v>
+      </c>
+      <c r="N44">
+        <v>1.615094500000001</v>
+      </c>
+      <c r="O44">
+        <v>0.274566065</v>
+      </c>
+      <c r="P44">
+        <v>1.340528435000001</v>
+      </c>
+      <c r="Q44">
+        <v>6.190528435000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.143298283531715</v>
+      </c>
+      <c r="T44">
+        <v>1.76689275440292</v>
+      </c>
+      <c r="U44">
+        <v>0.1125</v>
+      </c>
+      <c r="V44">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W44">
+        <v>0.09337500000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>1.5697172269058</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1227652967620257</v>
+      </c>
+      <c r="C45">
+        <v>24.79718286622962</v>
+      </c>
+      <c r="D45">
+        <v>44.38632286622962</v>
+      </c>
+      <c r="E45">
+        <v>25.60114</v>
+      </c>
+      <c r="F45">
+        <v>25.79914</v>
+      </c>
+      <c r="G45">
+        <v>6.21</v>
+      </c>
+      <c r="H45">
+        <v>59.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K45">
+        <v>4.85</v>
+      </c>
+      <c r="L45">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M45">
+        <v>2.90240325</v>
+      </c>
+      <c r="N45">
+        <v>1.547596750000001</v>
+      </c>
+      <c r="O45">
+        <v>0.2630914475000001</v>
+      </c>
+      <c r="P45">
+        <v>1.284505302500001</v>
+      </c>
+      <c r="Q45">
+        <v>6.134505302500001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1449369241439047</v>
+      </c>
+      <c r="T45">
+        <v>1.794599450885352</v>
+      </c>
+      <c r="U45">
+        <v>0.1125</v>
+      </c>
+      <c r="V45">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W45">
+        <v>0.09337500000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>1.533212175117293</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.156706493966013</v>
+      </c>
+      <c r="C46">
+        <v>13.52052161111323</v>
+      </c>
+      <c r="D46">
+        <v>33.70964161111323</v>
+      </c>
+      <c r="E46">
+        <v>26.20112</v>
+      </c>
+      <c r="F46">
+        <v>26.39912</v>
+      </c>
+      <c r="G46">
+        <v>6.21</v>
+      </c>
+      <c r="H46">
+        <v>59.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K46">
+        <v>4.85</v>
+      </c>
+      <c r="L46">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M46">
+        <v>5.190066992</v>
+      </c>
+      <c r="N46">
+        <v>-0.7400669919999991</v>
+      </c>
+      <c r="O46">
+        <v>-0.1258113886399998</v>
+      </c>
+      <c r="P46">
+        <v>-0.6142556033599993</v>
+      </c>
+      <c r="Q46">
+        <v>4.23574439664</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1478772278413104</v>
+      </c>
+      <c r="T46">
+        <v>1.844315112455175</v>
+      </c>
+      <c r="U46">
+        <v>0.1966</v>
+      </c>
+      <c r="V46">
+        <v>0.1457591975529552</v>
+      </c>
+      <c r="W46">
+        <v>0.167943741761089</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.8574070444291484</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1582844939660129</v>
+      </c>
+      <c r="C47">
+        <v>12.5477284534216</v>
+      </c>
+      <c r="D47">
+        <v>33.3368284534216</v>
+      </c>
+      <c r="E47">
+        <v>26.8011</v>
+      </c>
+      <c r="F47">
+        <v>26.9991</v>
+      </c>
+      <c r="G47">
+        <v>6.21</v>
+      </c>
+      <c r="H47">
+        <v>59.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K47">
+        <v>4.85</v>
+      </c>
+      <c r="L47">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M47">
+        <v>5.30802306</v>
+      </c>
+      <c r="N47">
+        <v>-0.8580230599999989</v>
+      </c>
+      <c r="O47">
+        <v>-0.1458639201999997</v>
+      </c>
+      <c r="P47">
+        <v>-0.7121591397999992</v>
+      </c>
+      <c r="Q47">
+        <v>4.137840860200001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1498604501656978</v>
+      </c>
+      <c r="T47">
+        <v>1.877848114499815</v>
+      </c>
+      <c r="U47">
+        <v>0.1966</v>
+      </c>
+      <c r="V47">
+        <v>0.1425201042740006</v>
+      </c>
+      <c r="W47">
+        <v>0.1685805474997315</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.8383535545529452</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1598624939660129</v>
+      </c>
+      <c r="C48">
+        <v>11.5830913778837</v>
+      </c>
+      <c r="D48">
+        <v>32.9721713778837</v>
+      </c>
+      <c r="E48">
+        <v>27.40108</v>
+      </c>
+      <c r="F48">
+        <v>27.59908</v>
+      </c>
+      <c r="G48">
+        <v>6.21</v>
+      </c>
+      <c r="H48">
+        <v>59.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K48">
+        <v>4.85</v>
+      </c>
+      <c r="L48">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M48">
+        <v>5.425979128</v>
+      </c>
+      <c r="N48">
+        <v>-0.9759791279999988</v>
+      </c>
+      <c r="O48">
+        <v>-0.1659164517599997</v>
+      </c>
+      <c r="P48">
+        <v>-0.8100626762399991</v>
+      </c>
+      <c r="Q48">
+        <v>4.03993732376</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1519171251687663</v>
+      </c>
+      <c r="T48">
+        <v>1.912623079583144</v>
+      </c>
+      <c r="U48">
+        <v>0.1966</v>
+      </c>
+      <c r="V48">
+        <v>0.1394218411376093</v>
+      </c>
+      <c r="W48">
+        <v>0.169189666032346</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.8201284772800551</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.161440493966013</v>
+      </c>
+      <c r="C49">
+        <v>10.62634563298912</v>
+      </c>
+      <c r="D49">
+        <v>32.61540563298912</v>
+      </c>
+      <c r="E49">
+        <v>28.00106</v>
+      </c>
+      <c r="F49">
+        <v>28.19906</v>
+      </c>
+      <c r="G49">
+        <v>6.21</v>
+      </c>
+      <c r="H49">
+        <v>59.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K49">
+        <v>4.85</v>
+      </c>
+      <c r="L49">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M49">
+        <v>5.543935196</v>
+      </c>
+      <c r="N49">
+        <v>-1.093935195999999</v>
+      </c>
+      <c r="O49">
+        <v>-0.1859689833199997</v>
+      </c>
+      <c r="P49">
+        <v>-0.9079662126799989</v>
+      </c>
+      <c r="Q49">
+        <v>3.942033787320001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.154051410549309</v>
+      </c>
+      <c r="T49">
+        <v>1.948710307499808</v>
+      </c>
+      <c r="U49">
+        <v>0.1966</v>
+      </c>
+      <c r="V49">
+        <v>0.1364554189857453</v>
+      </c>
+      <c r="W49">
+        <v>0.1697728646274025</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.8026789352102668</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1716112519200722</v>
+      </c>
+      <c r="C50">
+        <v>7.900056177114337</v>
+      </c>
+      <c r="D50">
+        <v>30.48909617711434</v>
+      </c>
+      <c r="E50">
+        <v>28.60104</v>
+      </c>
+      <c r="F50">
+        <v>28.79904</v>
+      </c>
+      <c r="G50">
+        <v>6.21</v>
+      </c>
+      <c r="H50">
+        <v>59.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K50">
+        <v>4.85</v>
+      </c>
+      <c r="L50">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M50">
+        <v>6.157234751999999</v>
+      </c>
+      <c r="N50">
+        <v>-1.707234751999998</v>
+      </c>
+      <c r="O50">
+        <v>-0.2902299078399995</v>
+      </c>
+      <c r="P50">
+        <v>-1.417004844159999</v>
+      </c>
+      <c r="Q50">
+        <v>3.432995155840001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1569153952792174</v>
+      </c>
+      <c r="T50">
+        <v>1.997135541838321</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1228635955051531</v>
+      </c>
+      <c r="W50">
+        <v>0.1875317632809982</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.7227270323832542</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1733612519200722</v>
+      </c>
+      <c r="C51">
+        <v>6.961864596178525</v>
+      </c>
+      <c r="D51">
+        <v>30.15088459617852</v>
+      </c>
+      <c r="E51">
+        <v>29.20102</v>
+      </c>
+      <c r="F51">
+        <v>29.39902</v>
+      </c>
+      <c r="G51">
+        <v>6.21</v>
+      </c>
+      <c r="H51">
+        <v>59.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K51">
+        <v>4.85</v>
+      </c>
+      <c r="L51">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M51">
+        <v>6.285510475999999</v>
+      </c>
+      <c r="N51">
+        <v>-1.835510475999998</v>
+      </c>
+      <c r="O51">
+        <v>-0.3120367809199995</v>
+      </c>
+      <c r="P51">
+        <v>-1.523473695079998</v>
+      </c>
+      <c r="Q51">
+        <v>3.326526304920002</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1592313834219471</v>
+      </c>
+      <c r="T51">
+        <v>2.036295062266523</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1203561751887215</v>
+      </c>
+      <c r="W51">
+        <v>0.1880678497446513</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.7079775011101266</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1751112519200722</v>
+      </c>
+      <c r="C52">
+        <v>6.031094167577944</v>
+      </c>
+      <c r="D52">
+        <v>29.82009416757795</v>
+      </c>
+      <c r="E52">
+        <v>29.801</v>
+      </c>
+      <c r="F52">
+        <v>29.999</v>
+      </c>
+      <c r="G52">
+        <v>6.21</v>
+      </c>
+      <c r="H52">
+        <v>59.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K52">
+        <v>4.85</v>
+      </c>
+      <c r="L52">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M52">
+        <v>6.4137862</v>
+      </c>
+      <c r="N52">
+        <v>-1.963786199999999</v>
+      </c>
+      <c r="O52">
+        <v>-0.3338436539999996</v>
+      </c>
+      <c r="P52">
+        <v>-1.629942545999999</v>
+      </c>
+      <c r="Q52">
+        <v>3.220057454000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1616400110903861</v>
+      </c>
+      <c r="T52">
+        <v>2.077020963511853</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.117949051684947</v>
+      </c>
+      <c r="W52">
+        <v>0.1885824927497583</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6938179510879239</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1768612519200722</v>
+      </c>
+      <c r="C53">
+        <v>5.107503285873317</v>
+      </c>
+      <c r="D53">
+        <v>29.49648328587332</v>
+      </c>
+      <c r="E53">
+        <v>30.40098</v>
+      </c>
+      <c r="F53">
+        <v>30.59898</v>
+      </c>
+      <c r="G53">
+        <v>6.21</v>
+      </c>
+      <c r="H53">
+        <v>59.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K53">
+        <v>4.85</v>
+      </c>
+      <c r="L53">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M53">
+        <v>6.542061924</v>
+      </c>
+      <c r="N53">
+        <v>-2.092061923999998</v>
+      </c>
+      <c r="O53">
+        <v>-0.3556505270799996</v>
+      </c>
+      <c r="P53">
+        <v>-1.736411396919999</v>
+      </c>
+      <c r="Q53">
+        <v>3.113588603080001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1641469500922307</v>
+      </c>
+      <c r="T53">
+        <v>2.119409146440667</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1156363251813206</v>
+      </c>
+      <c r="W53">
+        <v>0.1890769536762336</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.6802136775371803</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1786112519200722</v>
+      </c>
+      <c r="C54">
+        <v>4.190860720746663</v>
+      </c>
+      <c r="D54">
+        <v>29.17982072074666</v>
+      </c>
+      <c r="E54">
+        <v>31.00096</v>
+      </c>
+      <c r="F54">
+        <v>31.19896</v>
+      </c>
+      <c r="G54">
+        <v>6.21</v>
+      </c>
+      <c r="H54">
+        <v>59.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K54">
+        <v>4.85</v>
+      </c>
+      <c r="L54">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M54">
+        <v>6.670337647999999</v>
+      </c>
+      <c r="N54">
+        <v>-2.220337647999998</v>
+      </c>
+      <c r="O54">
+        <v>-0.3774574001599996</v>
+      </c>
+      <c r="P54">
+        <v>-1.842880247839999</v>
+      </c>
+      <c r="Q54">
+        <v>3.007119752160001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1667583448858188</v>
+      </c>
+      <c r="T54">
+        <v>2.163563503658181</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1134125496970644</v>
+      </c>
+      <c r="W54">
+        <v>0.1895523968747676</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.66713264527685</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1803612519200722</v>
+      </c>
+      <c r="C55">
+        <v>3.280945066000662</v>
+      </c>
+      <c r="D55">
+        <v>28.86988506600067</v>
+      </c>
+      <c r="E55">
+        <v>31.60094</v>
+      </c>
+      <c r="F55">
+        <v>31.79894</v>
+      </c>
+      <c r="G55">
+        <v>6.21</v>
+      </c>
+      <c r="H55">
+        <v>59.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K55">
+        <v>4.85</v>
+      </c>
+      <c r="L55">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M55">
+        <v>6.798613372</v>
+      </c>
+      <c r="N55">
+        <v>-2.348613371999999</v>
+      </c>
+      <c r="O55">
+        <v>-0.3992642732399997</v>
+      </c>
+      <c r="P55">
+        <v>-1.94934909876</v>
+      </c>
+      <c r="Q55">
+        <v>2.90065090124</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1694808628621128</v>
+      </c>
+      <c r="T55">
+        <v>2.209596769693461</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1112726902688179</v>
+      </c>
+      <c r="W55">
+        <v>0.1900098988205267</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.6545452368753999</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1821112519200722</v>
+      </c>
+      <c r="C56">
+        <v>2.37754422330395</v>
+      </c>
+      <c r="D56">
+        <v>28.56646422330396</v>
+      </c>
+      <c r="E56">
+        <v>32.20092</v>
+      </c>
+      <c r="F56">
+        <v>32.39892</v>
+      </c>
+      <c r="G56">
+        <v>6.21</v>
+      </c>
+      <c r="H56">
+        <v>59.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K56">
+        <v>4.85</v>
+      </c>
+      <c r="L56">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M56">
+        <v>6.926889096000001</v>
+      </c>
+      <c r="N56">
+        <v>-2.476889096</v>
+      </c>
+      <c r="O56">
+        <v>-0.4210711463199998</v>
+      </c>
+      <c r="P56">
+        <v>-2.05581794968</v>
+      </c>
+      <c r="Q56">
+        <v>2.794182050319999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1723217511852022</v>
+      </c>
+      <c r="T56">
+        <v>2.257631482078101</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.1092120848934694</v>
+      </c>
+      <c r="W56">
+        <v>0.1904504562497762</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.6424240287851146</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1838612519200722</v>
+      </c>
+      <c r="C57">
+        <v>1.480454918152624</v>
+      </c>
+      <c r="D57">
+        <v>28.26935491815263</v>
+      </c>
+      <c r="E57">
+        <v>32.8009</v>
+      </c>
+      <c r="F57">
+        <v>32.9989</v>
+      </c>
+      <c r="G57">
+        <v>6.21</v>
+      </c>
+      <c r="H57">
+        <v>59.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K57">
+        <v>4.85</v>
+      </c>
+      <c r="L57">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M57">
+        <v>7.05516482</v>
+      </c>
+      <c r="N57">
+        <v>-2.605164819999999</v>
+      </c>
+      <c r="O57">
+        <v>-0.4428780193999996</v>
+      </c>
+      <c r="P57">
+        <v>-2.162286800599999</v>
+      </c>
+      <c r="Q57">
+        <v>2.687713199400001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1752889012115401</v>
+      </c>
+      <c r="T57">
+        <v>2.307801070568726</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1072264106226791</v>
+      </c>
+      <c r="W57">
+        <v>0.1908749934088712</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.6307435918981126</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1856112519200722</v>
+      </c>
+      <c r="C58">
+        <v>0.5894822457266571</v>
+      </c>
+      <c r="D58">
+        <v>27.97836224572666</v>
+      </c>
+      <c r="E58">
+        <v>33.40088</v>
+      </c>
+      <c r="F58">
+        <v>33.59888</v>
+      </c>
+      <c r="G58">
+        <v>6.21</v>
+      </c>
+      <c r="H58">
+        <v>59.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K58">
+        <v>4.85</v>
+      </c>
+      <c r="L58">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M58">
+        <v>7.183440544</v>
+      </c>
+      <c r="N58">
+        <v>-2.733440543999999</v>
+      </c>
+      <c r="O58">
+        <v>-0.4646848924799996</v>
+      </c>
+      <c r="P58">
+        <v>-2.268755651519999</v>
+      </c>
+      <c r="Q58">
+        <v>2.581244348480001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1783909216936205</v>
+      </c>
+      <c r="T58">
+        <v>2.360251094899833</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1053116532901313</v>
+      </c>
+      <c r="W58">
+        <v>0.1912843685265699</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.6194803134713607</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1873612519200722</v>
+      </c>
+      <c r="C59">
+        <v>-0.2955607554908681</v>
+      </c>
+      <c r="D59">
+        <v>27.69329924450914</v>
+      </c>
+      <c r="E59">
+        <v>34.00086</v>
+      </c>
+      <c r="F59">
+        <v>34.19886</v>
+      </c>
+      <c r="G59">
+        <v>6.21</v>
+      </c>
+      <c r="H59">
+        <v>59.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K59">
+        <v>4.85</v>
+      </c>
+      <c r="L59">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M59">
+        <v>7.311716268000001</v>
+      </c>
+      <c r="N59">
+        <v>-2.861716267999999</v>
+      </c>
+      <c r="O59">
+        <v>-0.4864917655599997</v>
+      </c>
+      <c r="P59">
+        <v>-2.37522450244</v>
+      </c>
+      <c r="Q59">
+        <v>2.47477549756</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1816372221981233</v>
+      </c>
+      <c r="T59">
+        <v>2.415140655246341</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1034640804253921</v>
+      </c>
+      <c r="W59">
+        <v>0.1916793796050512</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.6086122377964244</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1891112519200722</v>
+      </c>
+      <c r="C60">
+        <v>-1.174853504291825</v>
+      </c>
+      <c r="D60">
+        <v>27.41398649570818</v>
+      </c>
+      <c r="E60">
+        <v>34.60084</v>
+      </c>
+      <c r="F60">
+        <v>34.79884</v>
+      </c>
+      <c r="G60">
+        <v>6.21</v>
+      </c>
+      <c r="H60">
+        <v>59.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K60">
+        <v>4.85</v>
+      </c>
+      <c r="L60">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M60">
+        <v>7.439991991999999</v>
+      </c>
+      <c r="N60">
+        <v>-2.989991991999998</v>
+      </c>
+      <c r="O60">
+        <v>-0.5082986386399995</v>
+      </c>
+      <c r="P60">
+        <v>-2.481693353359999</v>
+      </c>
+      <c r="Q60">
+        <v>2.368306646640001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1850381084409358</v>
+      </c>
+      <c r="T60">
+        <v>2.472644004180777</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.1016802169697819</v>
+      </c>
+      <c r="W60">
+        <v>0.1920607696118606</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5981189233516586</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1908612519200722</v>
+      </c>
+      <c r="C61">
+        <v>-2.04856825332206</v>
+      </c>
+      <c r="D61">
+        <v>27.14025174667794</v>
+      </c>
+      <c r="E61">
+        <v>35.20081999999999</v>
+      </c>
+      <c r="F61">
+        <v>35.39881999999999</v>
+      </c>
+      <c r="G61">
+        <v>6.21</v>
+      </c>
+      <c r="H61">
+        <v>59.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K61">
+        <v>4.85</v>
+      </c>
+      <c r="L61">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M61">
+        <v>7.568267715999998</v>
+      </c>
+      <c r="N61">
+        <v>-3.118267715999997</v>
+      </c>
+      <c r="O61">
+        <v>-0.5301055117199993</v>
+      </c>
+      <c r="P61">
+        <v>-2.588162204279998</v>
+      </c>
+      <c r="Q61">
+        <v>2.261837795720002</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1886048915736415</v>
+      </c>
+      <c r="T61">
+        <v>2.53295239452665</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.09995682346181951</v>
+      </c>
+      <c r="W61">
+        <v>0.192429231143863</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5879813144812915</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1926112519200722</v>
+      </c>
+      <c r="C62">
+        <v>-2.916870443321926</v>
+      </c>
+      <c r="D62">
+        <v>26.87192955667807</v>
+      </c>
+      <c r="E62">
+        <v>35.8008</v>
+      </c>
+      <c r="F62">
+        <v>35.9988</v>
+      </c>
+      <c r="G62">
+        <v>6.21</v>
+      </c>
+      <c r="H62">
+        <v>59.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K62">
+        <v>4.85</v>
+      </c>
+      <c r="L62">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M62">
+        <v>7.696543439999998</v>
+      </c>
+      <c r="N62">
+        <v>-3.246543439999997</v>
+      </c>
+      <c r="O62">
+        <v>-0.5519123847999993</v>
+      </c>
+      <c r="P62">
+        <v>-2.694631055199998</v>
+      </c>
+      <c r="Q62">
+        <v>2.155368944800002</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1923500138629825</v>
+      </c>
+      <c r="T62">
+        <v>2.596276204389816</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.09829087640412254</v>
+      </c>
+      <c r="W62">
+        <v>0.1927854106247986</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5781816259066033</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1943612519200722</v>
+      </c>
+      <c r="C63">
+        <v>-3.779919036559512</v>
+      </c>
+      <c r="D63">
+        <v>26.60886096344049</v>
+      </c>
+      <c r="E63">
+        <v>36.40078</v>
+      </c>
+      <c r="F63">
+        <v>36.59878</v>
+      </c>
+      <c r="G63">
+        <v>6.21</v>
+      </c>
+      <c r="H63">
+        <v>59.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K63">
+        <v>4.85</v>
+      </c>
+      <c r="L63">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M63">
+        <v>7.824819163999999</v>
+      </c>
+      <c r="N63">
+        <v>-3.374819163999998</v>
+      </c>
+      <c r="O63">
+        <v>-0.5737192578799994</v>
+      </c>
+      <c r="P63">
+        <v>-2.801099906119998</v>
+      </c>
+      <c r="Q63">
+        <v>2.048900093880001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1962871937056231</v>
+      </c>
+      <c r="T63">
+        <v>2.66284738911776</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.09667955056143197</v>
+      </c>
+      <c r="W63">
+        <v>0.1931299120899658</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5687032385966589</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1961112519200722</v>
+      </c>
+      <c r="C64">
+        <v>-4.637866830868305</v>
+      </c>
+      <c r="D64">
+        <v>26.35089316913169</v>
+      </c>
+      <c r="E64">
+        <v>37.00076</v>
+      </c>
+      <c r="F64">
+        <v>37.19876</v>
+      </c>
+      <c r="G64">
+        <v>6.21</v>
+      </c>
+      <c r="H64">
+        <v>59.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K64">
+        <v>4.85</v>
+      </c>
+      <c r="L64">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M64">
+        <v>7.953094888</v>
+      </c>
+      <c r="N64">
+        <v>-3.503094887999999</v>
+      </c>
+      <c r="O64">
+        <v>-0.5955261309599995</v>
+      </c>
+      <c r="P64">
+        <v>-2.907568757039999</v>
+      </c>
+      <c r="Q64">
+        <v>1.942431242960001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2004315935399816</v>
+      </c>
+      <c r="T64">
+        <v>2.732922320410333</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.09512020297173146</v>
+      </c>
+      <c r="W64">
+        <v>0.1934633006046438</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5595306057160676</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1978612519200722</v>
+      </c>
+      <c r="C65">
+        <v>-5.490860755593111</v>
+      </c>
+      <c r="D65">
+        <v>26.09787924440689</v>
+      </c>
+      <c r="E65">
+        <v>37.60074</v>
+      </c>
+      <c r="F65">
+        <v>37.79874</v>
+      </c>
+      <c r="G65">
+        <v>6.21</v>
+      </c>
+      <c r="H65">
+        <v>59.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K65">
+        <v>4.85</v>
+      </c>
+      <c r="L65">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M65">
+        <v>8.081370612000001</v>
+      </c>
+      <c r="N65">
+        <v>-3.631370612</v>
+      </c>
+      <c r="O65">
+        <v>-0.6173330040399997</v>
+      </c>
+      <c r="P65">
+        <v>-3.01403760796</v>
+      </c>
+      <c r="Q65">
+        <v>1.83596239204</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2048000149870082</v>
+      </c>
+      <c r="T65">
+        <v>2.806785085826829</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.09361035848011667</v>
+      </c>
+      <c r="W65">
+        <v>0.193786105356951</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5506491675300982</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1996112519200722</v>
+      </c>
+      <c r="C66">
+        <v>-6.339042150648581</v>
+      </c>
+      <c r="D66">
+        <v>25.84967784935142</v>
+      </c>
+      <c r="E66">
+        <v>38.20072</v>
+      </c>
+      <c r="F66">
+        <v>38.39872</v>
+      </c>
+      <c r="G66">
+        <v>6.21</v>
+      </c>
+      <c r="H66">
+        <v>59.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K66">
+        <v>4.85</v>
+      </c>
+      <c r="L66">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M66">
+        <v>8.209646335999999</v>
+      </c>
+      <c r="N66">
+        <v>-3.759646335999998</v>
+      </c>
+      <c r="O66">
+        <v>-0.6391398771199993</v>
+      </c>
+      <c r="P66">
+        <v>-3.120506458879998</v>
+      </c>
+      <c r="Q66">
+        <v>1.729493541120001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2094111265144251</v>
+      </c>
+      <c r="T66">
+        <v>2.884751338210907</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.09214769662886488</v>
+      </c>
+      <c r="W66">
+        <v>0.1940988224607487</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5420452742874406</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2013612519200722</v>
+      </c>
+      <c r="C67">
+        <v>-7.182547029803992</v>
+      </c>
+      <c r="D67">
+        <v>25.60615297019601</v>
+      </c>
+      <c r="E67">
+        <v>38.8007</v>
+      </c>
+      <c r="F67">
+        <v>38.9987</v>
+      </c>
+      <c r="G67">
+        <v>6.21</v>
+      </c>
+      <c r="H67">
+        <v>59.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K67">
+        <v>4.85</v>
+      </c>
+      <c r="L67">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M67">
+        <v>8.33792206</v>
+      </c>
+      <c r="N67">
+        <v>-3.887922059999999</v>
+      </c>
+      <c r="O67">
+        <v>-0.6609467501999996</v>
+      </c>
+      <c r="P67">
+        <v>-3.2269753098</v>
+      </c>
+      <c r="Q67">
+        <v>1.6230246902</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2142857301291229</v>
+      </c>
+      <c r="T67">
+        <v>2.967172805016933</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.09073003975765155</v>
+      </c>
+      <c r="W67">
+        <v>0.1944019174998141</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5337061162214799</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2031112519200722</v>
+      </c>
+      <c r="C68">
+        <v>-8.021506329224721</v>
+      </c>
+      <c r="D68">
+        <v>25.36717367077528</v>
+      </c>
+      <c r="E68">
+        <v>39.40068</v>
+      </c>
+      <c r="F68">
+        <v>39.59868</v>
+      </c>
+      <c r="G68">
+        <v>6.21</v>
+      </c>
+      <c r="H68">
+        <v>59.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K68">
+        <v>4.85</v>
+      </c>
+      <c r="L68">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M68">
+        <v>8.466197784</v>
+      </c>
+      <c r="N68">
+        <v>-4.016197783999999</v>
+      </c>
+      <c r="O68">
+        <v>-0.6827536232799996</v>
+      </c>
+      <c r="P68">
+        <v>-3.33344416072</v>
+      </c>
+      <c r="Q68">
+        <v>1.51655583928</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2194470751329207</v>
+      </c>
+      <c r="T68">
+        <v>3.054442593399784</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.08935534218556591</v>
+      </c>
+      <c r="W68">
+        <v>0.194695827840726</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5256196599150937</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2048612519200722</v>
+      </c>
+      <c r="C69">
+        <v>-8.856046142224901</v>
+      </c>
+      <c r="D69">
+        <v>25.1326138577751</v>
+      </c>
+      <c r="E69">
+        <v>40.00066</v>
+      </c>
+      <c r="F69">
+        <v>40.19866</v>
+      </c>
+      <c r="G69">
+        <v>6.21</v>
+      </c>
+      <c r="H69">
+        <v>59.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K69">
+        <v>4.85</v>
+      </c>
+      <c r="L69">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M69">
+        <v>8.594473508</v>
+      </c>
+      <c r="N69">
+        <v>-4.144473507999999</v>
+      </c>
+      <c r="O69">
+        <v>-0.7045604963599995</v>
+      </c>
+      <c r="P69">
+        <v>-3.439913011639999</v>
+      </c>
+      <c r="Q69">
+        <v>1.41008698836</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2249212289248274</v>
+      </c>
+      <c r="T69">
+        <v>3.147001459866445</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.08802168036190076</v>
+      </c>
+      <c r="W69">
+        <v>0.1949809647386256</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5177745903641222</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2066112519200722</v>
+      </c>
+      <c r="C70">
+        <v>-9.686287941115239</v>
+      </c>
+      <c r="D70">
+        <v>24.90235205888476</v>
+      </c>
+      <c r="E70">
+        <v>40.60064</v>
+      </c>
+      <c r="F70">
+        <v>40.79864</v>
+      </c>
+      <c r="G70">
+        <v>6.21</v>
+      </c>
+      <c r="H70">
+        <v>59.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K70">
+        <v>4.85</v>
+      </c>
+      <c r="L70">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M70">
+        <v>8.722749232</v>
+      </c>
+      <c r="N70">
+        <v>-4.272749231999999</v>
+      </c>
+      <c r="O70">
+        <v>-0.7263673694399995</v>
+      </c>
+      <c r="P70">
+        <v>-3.54638186256</v>
+      </c>
+      <c r="Q70">
+        <v>1.30361813744</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2307375173287282</v>
+      </c>
+      <c r="T70">
+        <v>3.245345255487271</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.08672724388599046</v>
+      </c>
+      <c r="W70">
+        <v>0.1952577152571752</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5101602581528852</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2083612519200722</v>
+      </c>
+      <c r="C71">
+        <v>-10.51234878696651</v>
+      </c>
+      <c r="D71">
+        <v>24.67627121303349</v>
+      </c>
+      <c r="E71">
+        <v>41.20062</v>
+      </c>
+      <c r="F71">
+        <v>41.39862</v>
+      </c>
+      <c r="G71">
+        <v>6.21</v>
+      </c>
+      <c r="H71">
+        <v>59.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K71">
+        <v>4.85</v>
+      </c>
+      <c r="L71">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M71">
+        <v>8.851024956</v>
+      </c>
+      <c r="N71">
+        <v>-4.401024955999999</v>
+      </c>
+      <c r="O71">
+        <v>-0.7481742425199995</v>
+      </c>
+      <c r="P71">
+        <v>-3.652850713479999</v>
+      </c>
+      <c r="Q71">
+        <v>1.19714928652</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.236929050145784</v>
+      </c>
+      <c r="T71">
+        <v>3.350033812115893</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.08547032730793262</v>
+      </c>
+      <c r="W71">
+        <v>0.195526444021564</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5027666312231333</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2280142273943918</v>
+      </c>
+      <c r="C72">
+        <v>-13.3954494474307</v>
+      </c>
+      <c r="D72">
+        <v>22.39315055256931</v>
+      </c>
+      <c r="E72">
+        <v>41.8006</v>
+      </c>
+      <c r="F72">
+        <v>41.9986</v>
+      </c>
+      <c r="G72">
+        <v>6.21</v>
+      </c>
+      <c r="H72">
+        <v>59.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K72">
+        <v>4.85</v>
+      </c>
+      <c r="L72">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M72">
+        <v>10.02926568</v>
+      </c>
+      <c r="N72">
+        <v>-5.579265680000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.9484751655999997</v>
+      </c>
+      <c r="P72">
+        <v>-4.630790514400001</v>
+      </c>
+      <c r="Q72">
+        <v>0.2192094855999986</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2448766033983754</v>
+      </c>
+      <c r="T72">
+        <v>3.484413763466703</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07542925116726988</v>
+      </c>
+      <c r="W72">
+        <v>0.220787494821256</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4437014774545289</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2300142273943918</v>
+      </c>
+      <c r="C73">
+        <v>-14.2043091172438</v>
+      </c>
+      <c r="D73">
+        <v>22.1842708827562</v>
+      </c>
+      <c r="E73">
+        <v>42.40058</v>
+      </c>
+      <c r="F73">
+        <v>42.59858</v>
+      </c>
+      <c r="G73">
+        <v>6.21</v>
+      </c>
+      <c r="H73">
+        <v>59.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K73">
+        <v>4.85</v>
+      </c>
+      <c r="L73">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M73">
+        <v>10.172540904</v>
+      </c>
+      <c r="N73">
+        <v>-5.722540903999999</v>
+      </c>
+      <c r="O73">
+        <v>-0.9728319536799994</v>
+      </c>
+      <c r="P73">
+        <v>-4.74970895032</v>
+      </c>
+      <c r="Q73">
+        <v>0.10029104968</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2519826931707331</v>
+      </c>
+      <c r="T73">
+        <v>3.604565962206933</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07436686734801257</v>
+      </c>
+      <c r="W73">
+        <v>0.2210411920772946</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.4374521608706624</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2320142273943918</v>
+      </c>
+      <c r="C74">
+        <v>-15.00930800853108</v>
+      </c>
+      <c r="D74">
+        <v>21.97925199146891</v>
+      </c>
+      <c r="E74">
+        <v>43.00055999999999</v>
+      </c>
+      <c r="F74">
+        <v>43.19855999999999</v>
+      </c>
+      <c r="G74">
+        <v>6.21</v>
+      </c>
+      <c r="H74">
+        <v>59.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K74">
+        <v>4.85</v>
+      </c>
+      <c r="L74">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M74">
+        <v>10.315816128</v>
+      </c>
+      <c r="N74">
+        <v>-5.865816127999999</v>
+      </c>
+      <c r="O74">
+        <v>-0.9971887417599994</v>
+      </c>
+      <c r="P74">
+        <v>-4.868627386239999</v>
+      </c>
+      <c r="Q74">
+        <v>-0.01862738623999949</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2595963607839735</v>
+      </c>
+      <c r="T74">
+        <v>3.733300460857181</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07333399419040128</v>
+      </c>
+      <c r="W74">
+        <v>0.2212878421873322</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.4313764364141254</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2340142273943918</v>
+      </c>
+      <c r="C75">
+        <v>-15.81055218082471</v>
+      </c>
+      <c r="D75">
+        <v>21.77798781917529</v>
+      </c>
+      <c r="E75">
+        <v>43.60054</v>
+      </c>
+      <c r="F75">
+        <v>43.79854</v>
+      </c>
+      <c r="G75">
+        <v>6.21</v>
+      </c>
+      <c r="H75">
+        <v>59.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K75">
+        <v>4.85</v>
+      </c>
+      <c r="L75">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M75">
+        <v>10.459091352</v>
+      </c>
+      <c r="N75">
+        <v>-6.009091351999999</v>
+      </c>
+      <c r="O75">
+        <v>-1.021545529839999</v>
+      </c>
+      <c r="P75">
+        <v>-4.98754582216</v>
+      </c>
+      <c r="Q75">
+        <v>-0.1375458221599999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2677740037759725</v>
+      </c>
+      <c r="T75">
+        <v>3.871570848296335</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.07232941892751907</v>
+      </c>
+      <c r="W75">
+        <v>0.2215277347601085</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4254671701618771</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2360142273943918</v>
+      </c>
+      <c r="C76">
+        <v>-16.60814384415507</v>
+      </c>
+      <c r="D76">
+        <v>21.58037615584493</v>
+      </c>
+      <c r="E76">
+        <v>44.20052</v>
+      </c>
+      <c r="F76">
+        <v>44.39852</v>
+      </c>
+      <c r="G76">
+        <v>6.21</v>
+      </c>
+      <c r="H76">
+        <v>59.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K76">
+        <v>4.85</v>
+      </c>
+      <c r="L76">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M76">
+        <v>10.602366576</v>
+      </c>
+      <c r="N76">
+        <v>-6.152366575999999</v>
+      </c>
+      <c r="O76">
+        <v>-1.045902317919999</v>
+      </c>
+      <c r="P76">
+        <v>-5.106464258079999</v>
+      </c>
+      <c r="Q76">
+        <v>-0.2564642580799994</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2765806962288946</v>
+      </c>
+      <c r="T76">
+        <v>4.020477419384656</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.07135199434741747</v>
+      </c>
+      <c r="W76">
+        <v>0.2217611437498367</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4197176138083383</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2380142273943918</v>
+      </c>
+      <c r="C77">
+        <v>-17.40218153213059</v>
+      </c>
+      <c r="D77">
+        <v>21.3863184678694</v>
+      </c>
+      <c r="E77">
+        <v>44.8005</v>
+      </c>
+      <c r="F77">
+        <v>44.9985</v>
+      </c>
+      <c r="G77">
+        <v>6.21</v>
+      </c>
+      <c r="H77">
+        <v>59.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K77">
+        <v>4.85</v>
+      </c>
+      <c r="L77">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M77">
+        <v>10.7456418</v>
+      </c>
+      <c r="N77">
+        <v>-6.2956418</v>
+      </c>
+      <c r="O77">
+        <v>-1.070259106</v>
+      </c>
+      <c r="P77">
+        <v>-5.225382694</v>
+      </c>
+      <c r="Q77">
+        <v>-0.3753826940000007</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2860919240780503</v>
+      </c>
+      <c r="T77">
+        <v>4.181296516160042</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07040063442278523</v>
+      </c>
+      <c r="W77">
+        <v>0.2219883284998389</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.4141213789575603</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2400142273943918</v>
+      </c>
+      <c r="C78">
+        <v>-18.19276026576247</v>
+      </c>
+      <c r="D78">
+        <v>21.19571973423754</v>
+      </c>
+      <c r="E78">
+        <v>45.40048</v>
+      </c>
+      <c r="F78">
+        <v>45.59848</v>
+      </c>
+      <c r="G78">
+        <v>6.21</v>
+      </c>
+      <c r="H78">
+        <v>59.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K78">
+        <v>4.85</v>
+      </c>
+      <c r="L78">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M78">
+        <v>10.888917024</v>
+      </c>
+      <c r="N78">
+        <v>-6.438917024</v>
+      </c>
+      <c r="O78">
+        <v>-1.094615894079999</v>
+      </c>
+      <c r="P78">
+        <v>-5.344301129920001</v>
+      </c>
+      <c r="Q78">
+        <v>-0.4943011299200011</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2963957542479692</v>
+      </c>
+      <c r="T78">
+        <v>4.355517204333379</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06947431028564331</v>
+      </c>
+      <c r="W78">
+        <v>0.2222095347037884</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.4086724134449609</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2420142273943918</v>
+      </c>
+      <c r="C79">
+        <v>-18.97997170860642</v>
+      </c>
+      <c r="D79">
+        <v>21.00848829139358</v>
+      </c>
+      <c r="E79">
+        <v>46.00046</v>
+      </c>
+      <c r="F79">
+        <v>46.19846</v>
+      </c>
+      <c r="G79">
+        <v>6.21</v>
+      </c>
+      <c r="H79">
+        <v>59.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K79">
+        <v>4.85</v>
+      </c>
+      <c r="L79">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M79">
+        <v>11.032192248</v>
+      </c>
+      <c r="N79">
+        <v>-6.582192247999998</v>
+      </c>
+      <c r="O79">
+        <v>-1.118972682159999</v>
+      </c>
+      <c r="P79">
+        <v>-5.463219565839999</v>
+      </c>
+      <c r="Q79">
+        <v>-0.6132195658399997</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3075955696500547</v>
+      </c>
+      <c r="T79">
+        <v>4.544887517565264</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06857204651569991</v>
+      </c>
+      <c r="W79">
+        <v>0.2224249952920509</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4033649795041172</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2440142273943918</v>
+      </c>
+      <c r="C80">
+        <v>-19.76390431375402</v>
+      </c>
+      <c r="D80">
+        <v>20.82453568624598</v>
+      </c>
+      <c r="E80">
+        <v>46.60044</v>
+      </c>
+      <c r="F80">
+        <v>46.79844</v>
+      </c>
+      <c r="G80">
+        <v>6.21</v>
+      </c>
+      <c r="H80">
+        <v>59.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K80">
+        <v>4.85</v>
+      </c>
+      <c r="L80">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M80">
+        <v>11.175467472</v>
+      </c>
+      <c r="N80">
+        <v>-6.725467472</v>
+      </c>
+      <c r="O80">
+        <v>-1.143329470239999</v>
+      </c>
+      <c r="P80">
+        <v>-5.582138001760001</v>
+      </c>
+      <c r="Q80">
+        <v>-0.732138001760001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3198135500886936</v>
+      </c>
+      <c r="T80">
+        <v>4.751473313818231</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06769291771421657</v>
+      </c>
+      <c r="W80">
+        <v>0.2226349312498451</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3981936336130387</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2460142273943918</v>
+      </c>
+      <c r="C81">
+        <v>-20.54464346316844</v>
+      </c>
+      <c r="D81">
+        <v>20.64377653683156</v>
+      </c>
+      <c r="E81">
+        <v>47.20042</v>
+      </c>
+      <c r="F81">
+        <v>47.39842</v>
+      </c>
+      <c r="G81">
+        <v>6.21</v>
+      </c>
+      <c r="H81">
+        <v>59.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K81">
+        <v>4.85</v>
+      </c>
+      <c r="L81">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M81">
+        <v>11.318742696</v>
+      </c>
+      <c r="N81">
+        <v>-6.868742696</v>
+      </c>
+      <c r="O81">
+        <v>-1.16768625832</v>
+      </c>
+      <c r="P81">
+        <v>-5.70105643768</v>
+      </c>
+      <c r="Q81">
+        <v>-0.8510564376800005</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3331951477119648</v>
+      </c>
+      <c r="T81">
+        <v>4.977733947809576</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06683604533808724</v>
+      </c>
+      <c r="W81">
+        <v>0.2228395523732648</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3931532078711015</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2480142273943918</v>
+      </c>
+      <c r="C82">
+        <v>-21.32227159982606</v>
+      </c>
+      <c r="D82">
+        <v>20.46612840017395</v>
+      </c>
+      <c r="E82">
+        <v>47.8004</v>
+      </c>
+      <c r="F82">
+        <v>47.9984</v>
+      </c>
+      <c r="G82">
+        <v>6.21</v>
+      </c>
+      <c r="H82">
+        <v>59.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K82">
+        <v>4.85</v>
+      </c>
+      <c r="L82">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M82">
+        <v>11.46201792</v>
+      </c>
+      <c r="N82">
+        <v>-7.01201792</v>
+      </c>
+      <c r="O82">
+        <v>-1.1920430464</v>
+      </c>
+      <c r="P82">
+        <v>-5.819974873600001</v>
+      </c>
+      <c r="Q82">
+        <v>-0.9699748736000009</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.347914905097563</v>
+      </c>
+      <c r="T82">
+        <v>5.226620645200055</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06600059477136115</v>
+      </c>
+      <c r="W82">
+        <v>0.223039057968599</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3882387927727128</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2500142273943917</v>
+      </c>
+      <c r="C83">
+        <v>-22.09686835309344</v>
+      </c>
+      <c r="D83">
+        <v>20.29151164690655</v>
+      </c>
+      <c r="E83">
+        <v>48.40038</v>
+      </c>
+      <c r="F83">
+        <v>48.59838</v>
+      </c>
+      <c r="G83">
+        <v>6.21</v>
+      </c>
+      <c r="H83">
+        <v>59.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K83">
+        <v>4.85</v>
+      </c>
+      <c r="L83">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M83">
+        <v>11.605293144</v>
+      </c>
+      <c r="N83">
+        <v>-7.155293144</v>
+      </c>
+      <c r="O83">
+        <v>-1.21639983448</v>
+      </c>
+      <c r="P83">
+        <v>-5.93889330952</v>
+      </c>
+      <c r="Q83">
+        <v>-1.08889330952</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3641841106290137</v>
+      </c>
+      <c r="T83">
+        <v>5.501705942315847</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06518577261369003</v>
+      </c>
+      <c r="W83">
+        <v>0.2232336374998508</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3834457212570003</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2520142273943918</v>
+      </c>
+      <c r="C84">
+        <v>-22.86851065774042</v>
+      </c>
+      <c r="D84">
+        <v>20.11984934225958</v>
+      </c>
+      <c r="E84">
+        <v>49.00036</v>
+      </c>
+      <c r="F84">
+        <v>49.19836</v>
+      </c>
+      <c r="G84">
+        <v>6.21</v>
+      </c>
+      <c r="H84">
+        <v>59.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K84">
+        <v>4.85</v>
+      </c>
+      <c r="L84">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M84">
+        <v>11.748568368</v>
+      </c>
+      <c r="N84">
+        <v>-7.298568368</v>
+      </c>
+      <c r="O84">
+        <v>-1.24075662256</v>
+      </c>
+      <c r="P84">
+        <v>-6.05781174544</v>
+      </c>
+      <c r="Q84">
+        <v>-1.207811745440001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3822610056639589</v>
+      </c>
+      <c r="T84">
+        <v>5.807356272444506</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06439082416718162</v>
+      </c>
+      <c r="W84">
+        <v>0.2234234711888771</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3787695539245979</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2540142273943918</v>
+      </c>
+      <c r="C85">
+        <v>-23.63727286696265</v>
+      </c>
+      <c r="D85">
+        <v>19.95106713303735</v>
+      </c>
+      <c r="E85">
+        <v>49.60034</v>
+      </c>
+      <c r="F85">
+        <v>49.79834</v>
+      </c>
+      <c r="G85">
+        <v>6.21</v>
+      </c>
+      <c r="H85">
+        <v>59.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K85">
+        <v>4.85</v>
+      </c>
+      <c r="L85">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M85">
+        <v>11.891843592</v>
+      </c>
+      <c r="N85">
+        <v>-7.441843592</v>
+      </c>
+      <c r="O85">
+        <v>-1.265113410639999</v>
+      </c>
+      <c r="P85">
+        <v>-6.17673018136</v>
+      </c>
+      <c r="Q85">
+        <v>-1.32673018136</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4024645942324271</v>
+      </c>
+      <c r="T85">
+        <v>6.148965464941242</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06361503110492642</v>
+      </c>
+      <c r="W85">
+        <v>0.2236087305721436</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3742060653230966</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2560142273943917</v>
+      </c>
+      <c r="C86">
+        <v>-24.40322685976302</v>
+      </c>
+      <c r="D86">
+        <v>19.78509314023698</v>
+      </c>
+      <c r="E86">
+        <v>50.20032</v>
+      </c>
+      <c r="F86">
+        <v>50.39832</v>
+      </c>
+      <c r="G86">
+        <v>6.21</v>
+      </c>
+      <c r="H86">
+        <v>59.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K86">
+        <v>4.85</v>
+      </c>
+      <c r="L86">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M86">
+        <v>12.035118816</v>
+      </c>
+      <c r="N86">
+        <v>-7.585118816</v>
+      </c>
+      <c r="O86">
+        <v>-1.289470198719999</v>
+      </c>
+      <c r="P86">
+        <v>-6.29564861728</v>
+      </c>
+      <c r="Q86">
+        <v>-1.445648617280001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4251936313719536</v>
+      </c>
+      <c r="T86">
+        <v>6.533275806500066</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06285770930605825</v>
+      </c>
+      <c r="W86">
+        <v>0.2237895790177133</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3697512312121074</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2580142273943918</v>
+      </c>
+      <c r="C87">
+        <v>-25.16644214301722</v>
+      </c>
+      <c r="D87">
+        <v>19.62185785698277</v>
+      </c>
+      <c r="E87">
+        <v>50.80029999999999</v>
+      </c>
+      <c r="F87">
+        <v>50.99829999999999</v>
+      </c>
+      <c r="G87">
+        <v>6.21</v>
+      </c>
+      <c r="H87">
+        <v>59.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K87">
+        <v>4.85</v>
+      </c>
+      <c r="L87">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M87">
+        <v>12.17839404</v>
+      </c>
+      <c r="N87">
+        <v>-7.728394039999998</v>
+      </c>
+      <c r="O87">
+        <v>-1.313826986799999</v>
+      </c>
+      <c r="P87">
+        <v>-6.414567053199999</v>
+      </c>
+      <c r="Q87">
+        <v>-1.564567053199999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4509532067967506</v>
+      </c>
+      <c r="T87">
+        <v>6.968827526933405</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.06211820684363403</v>
+      </c>
+      <c r="W87">
+        <v>0.2239661722057402</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3654012167272592</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2600142273943917</v>
+      </c>
+      <c r="C88">
+        <v>-25.92698594852817</v>
+      </c>
+      <c r="D88">
+        <v>19.46129405147182</v>
+      </c>
+      <c r="E88">
+        <v>51.40028</v>
+      </c>
+      <c r="F88">
+        <v>51.59828</v>
+      </c>
+      <c r="G88">
+        <v>6.21</v>
+      </c>
+      <c r="H88">
+        <v>59.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K88">
+        <v>4.85</v>
+      </c>
+      <c r="L88">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M88">
+        <v>12.321669264</v>
+      </c>
+      <c r="N88">
+        <v>-7.871669263999998</v>
+      </c>
+      <c r="O88">
+        <v>-1.338183774879999</v>
+      </c>
+      <c r="P88">
+        <v>-6.533485489119998</v>
+      </c>
+      <c r="Q88">
+        <v>-1.683485489119999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.480392721567947</v>
+      </c>
+      <c r="T88">
+        <v>7.466600921714361</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06139590211289411</v>
+      </c>
+      <c r="W88">
+        <v>0.2241386585754409</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3611523653699654</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2620142273943918</v>
+      </c>
+      <c r="C89">
+        <v>-26.68492332535412</v>
+      </c>
+      <c r="D89">
+        <v>19.30333667464588</v>
+      </c>
+      <c r="E89">
+        <v>52.00026</v>
+      </c>
+      <c r="F89">
+        <v>52.19826</v>
+      </c>
+      <c r="G89">
+        <v>6.21</v>
+      </c>
+      <c r="H89">
+        <v>59.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K89">
+        <v>4.85</v>
+      </c>
+      <c r="L89">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M89">
+        <v>12.464944488</v>
+      </c>
+      <c r="N89">
+        <v>-8.014944487999999</v>
+      </c>
+      <c r="O89">
+        <v>-1.362540562959999</v>
+      </c>
+      <c r="P89">
+        <v>-6.65240392504</v>
+      </c>
+      <c r="Q89">
+        <v>-1.80240392504</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5143613924577891</v>
+      </c>
+      <c r="T89">
+        <v>8.040954838769313</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06069020208860796</v>
+      </c>
+      <c r="W89">
+        <v>0.2243071797412404</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3570011887565175</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2640142273943918</v>
+      </c>
+      <c r="C90">
+        <v>-27.44031722767647</v>
+      </c>
+      <c r="D90">
+        <v>19.14792277232353</v>
+      </c>
+      <c r="E90">
+        <v>52.60024</v>
+      </c>
+      <c r="F90">
+        <v>52.79824</v>
+      </c>
+      <c r="G90">
+        <v>6.21</v>
+      </c>
+      <c r="H90">
+        <v>59.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K90">
+        <v>4.85</v>
+      </c>
+      <c r="L90">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M90">
+        <v>12.608219712</v>
+      </c>
+      <c r="N90">
+        <v>-8.158219711999999</v>
+      </c>
+      <c r="O90">
+        <v>-1.386897351039999</v>
+      </c>
+      <c r="P90">
+        <v>-6.77132236096</v>
+      </c>
+      <c r="Q90">
+        <v>-1.921322360960001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5539915084959384</v>
+      </c>
+      <c r="T90">
+        <v>8.711034408666757</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06000054070123741</v>
+      </c>
+      <c r="W90">
+        <v>0.2244718708805445</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3529443570661026</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2660142273943918</v>
+      </c>
+      <c r="C91">
+        <v>-28.19322859845708</v>
+      </c>
+      <c r="D91">
+        <v>18.99499140154292</v>
+      </c>
+      <c r="E91">
+        <v>53.20022</v>
+      </c>
+      <c r="F91">
+        <v>53.39822</v>
+      </c>
+      <c r="G91">
+        <v>6.21</v>
+      </c>
+      <c r="H91">
+        <v>59.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K91">
+        <v>4.85</v>
+      </c>
+      <c r="L91">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M91">
+        <v>12.751494936</v>
+      </c>
+      <c r="N91">
+        <v>-8.301494935999999</v>
+      </c>
+      <c r="O91">
+        <v>-1.411254139119999</v>
+      </c>
+      <c r="P91">
+        <v>-6.89024079688</v>
+      </c>
+      <c r="Q91">
+        <v>-2.04024079688</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6008271001773873</v>
+      </c>
+      <c r="T91">
+        <v>9.502946627636462</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05932637732257183</v>
+      </c>
+      <c r="W91">
+        <v>0.2246328610953699</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3489786901327756</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2680142273943917</v>
+      </c>
+      <c r="C92">
+        <v>-28.94371644911826</v>
+      </c>
+      <c r="D92">
+        <v>18.84448355088174</v>
+      </c>
+      <c r="E92">
+        <v>53.8002</v>
+      </c>
+      <c r="F92">
+        <v>53.9982</v>
+      </c>
+      <c r="G92">
+        <v>6.21</v>
+      </c>
+      <c r="H92">
+        <v>59.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K92">
+        <v>4.85</v>
+      </c>
+      <c r="L92">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M92">
+        <v>12.89477016</v>
+      </c>
+      <c r="N92">
+        <v>-8.444770159999999</v>
+      </c>
+      <c r="O92">
+        <v>-1.435610927199999</v>
+      </c>
+      <c r="P92">
+        <v>-7.0091592328</v>
+      </c>
+      <c r="Q92">
+        <v>-2.1591592328</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.657029810195126</v>
+      </c>
+      <c r="T92">
+        <v>10.45324129040011</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05866719535232102</v>
+      </c>
+      <c r="W92">
+        <v>0.2247902737498658</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3451011491313003</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2700142273943917</v>
+      </c>
+      <c r="C93">
+        <v>-29.69183793546456</v>
+      </c>
+      <c r="D93">
+        <v>18.69634206453544</v>
+      </c>
+      <c r="E93">
+        <v>54.40018</v>
+      </c>
+      <c r="F93">
+        <v>54.59818</v>
+      </c>
+      <c r="G93">
+        <v>6.21</v>
+      </c>
+      <c r="H93">
+        <v>59.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K93">
+        <v>4.85</v>
+      </c>
+      <c r="L93">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M93">
+        <v>13.038045384</v>
+      </c>
+      <c r="N93">
+        <v>-8.588045383999999</v>
+      </c>
+      <c r="O93">
+        <v>-1.459967715279999</v>
+      </c>
+      <c r="P93">
+        <v>-7.12807766872</v>
+      </c>
+      <c r="Q93">
+        <v>-2.27807766872</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7257220113279177</v>
+      </c>
+      <c r="T93">
+        <v>11.61471254488901</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05802250089789992</v>
+      </c>
+      <c r="W93">
+        <v>0.2249442267855815</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3413088288111761</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2720142273943917</v>
+      </c>
+      <c r="C94">
+        <v>-30.43764843005128</v>
+      </c>
+      <c r="D94">
+        <v>18.55051156994872</v>
+      </c>
+      <c r="E94">
+        <v>55.00016</v>
+      </c>
+      <c r="F94">
+        <v>55.19816</v>
+      </c>
+      <c r="G94">
+        <v>6.21</v>
+      </c>
+      <c r="H94">
+        <v>59.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K94">
+        <v>4.85</v>
+      </c>
+      <c r="L94">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M94">
+        <v>13.181320608</v>
+      </c>
+      <c r="N94">
+        <v>-8.731320608000001</v>
+      </c>
+      <c r="O94">
+        <v>-1.484324503359999</v>
+      </c>
+      <c r="P94">
+        <v>-7.246996104640001</v>
+      </c>
+      <c r="Q94">
+        <v>-2.396996104640001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8115872627439078</v>
+      </c>
+      <c r="T94">
+        <v>13.06655161300014</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05739182154031404</v>
+      </c>
+      <c r="W94">
+        <v>0.225094833016173</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3375989502371416</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2740142273943917</v>
+      </c>
+      <c r="C95">
+        <v>-31.18120159119255</v>
+      </c>
+      <c r="D95">
+        <v>18.40693840880746</v>
+      </c>
+      <c r="E95">
+        <v>55.60014</v>
+      </c>
+      <c r="F95">
+        <v>55.79814</v>
+      </c>
+      <c r="G95">
+        <v>6.21</v>
+      </c>
+      <c r="H95">
+        <v>59.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K95">
+        <v>4.85</v>
+      </c>
+      <c r="L95">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M95">
+        <v>13.324595832</v>
+      </c>
+      <c r="N95">
+        <v>-8.874595832000001</v>
+      </c>
+      <c r="O95">
+        <v>-1.508681291439999</v>
+      </c>
+      <c r="P95">
+        <v>-7.365914540560001</v>
+      </c>
+      <c r="Q95">
+        <v>-2.515914540560002</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9219854431358947</v>
+      </c>
+      <c r="T95">
+        <v>14.93320184342873</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0567747051796655</v>
+      </c>
+      <c r="W95">
+        <v>0.2252422004030959</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3339688539980326</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2760142273943917</v>
+      </c>
+      <c r="C96">
+        <v>-31.92254942878931</v>
+      </c>
+      <c r="D96">
+        <v>18.26557057121069</v>
+      </c>
+      <c r="E96">
+        <v>56.20012</v>
+      </c>
+      <c r="F96">
+        <v>56.39812</v>
+      </c>
+      <c r="G96">
+        <v>6.21</v>
+      </c>
+      <c r="H96">
+        <v>59.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K96">
+        <v>4.85</v>
+      </c>
+      <c r="L96">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M96">
+        <v>13.467871056</v>
+      </c>
+      <c r="N96">
+        <v>-9.017871055999999</v>
+      </c>
+      <c r="O96">
+        <v>-1.533038079519999</v>
+      </c>
+      <c r="P96">
+        <v>-7.48483297648</v>
+      </c>
+      <c r="Q96">
+        <v>-2.63483297648</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.069183016991877</v>
+      </c>
+      <c r="T96">
+        <v>17.42206881733353</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05617071895434992</v>
+      </c>
+      <c r="W96">
+        <v>0.2253864323137013</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3304159938491174</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2780142273943917</v>
+      </c>
+      <c r="C97">
+        <v>-32.66174236714716</v>
+      </c>
+      <c r="D97">
+        <v>18.12635763285284</v>
+      </c>
+      <c r="E97">
+        <v>56.8001</v>
+      </c>
+      <c r="F97">
+        <v>56.9981</v>
+      </c>
+      <c r="G97">
+        <v>6.21</v>
+      </c>
+      <c r="H97">
+        <v>59.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K97">
+        <v>4.85</v>
+      </c>
+      <c r="L97">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M97">
+        <v>13.61114628</v>
+      </c>
+      <c r="N97">
+        <v>-9.161146280000001</v>
+      </c>
+      <c r="O97">
+        <v>-1.557394867599999</v>
+      </c>
+      <c r="P97">
+        <v>-7.603751412400001</v>
+      </c>
+      <c r="Q97">
+        <v>-2.753751412400002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.275259620390253</v>
+      </c>
+      <c r="T97">
+        <v>20.90648258080024</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05557944822851465</v>
+      </c>
+      <c r="W97">
+        <v>0.2255276277630307</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3269379307559687</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2800142273943917</v>
+      </c>
+      <c r="C98">
+        <v>-33.39882930494313</v>
+      </c>
+      <c r="D98">
+        <v>17.98925069505686</v>
+      </c>
+      <c r="E98">
+        <v>57.40008</v>
+      </c>
+      <c r="F98">
+        <v>57.59808</v>
+      </c>
+      <c r="G98">
+        <v>6.21</v>
+      </c>
+      <c r="H98">
+        <v>59.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K98">
+        <v>4.85</v>
+      </c>
+      <c r="L98">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M98">
+        <v>13.754421504</v>
+      </c>
+      <c r="N98">
+        <v>-9.304421503999999</v>
+      </c>
+      <c r="O98">
+        <v>-1.581751655679999</v>
+      </c>
+      <c r="P98">
+        <v>-7.72266984832</v>
+      </c>
+      <c r="Q98">
+        <v>-2.87266984832</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.584374525487813</v>
+      </c>
+      <c r="T98">
+        <v>26.13310322600024</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05500049564280097</v>
+      </c>
+      <c r="W98">
+        <v>0.2256658816404991</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.323532327310594</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2820142273943917</v>
+      </c>
+      <c r="C99">
+        <v>-34.13385767249148</v>
+      </c>
+      <c r="D99">
+        <v>17.85420232750852</v>
+      </c>
+      <c r="E99">
+        <v>58.00006</v>
+      </c>
+      <c r="F99">
+        <v>58.19806</v>
+      </c>
+      <c r="G99">
+        <v>6.21</v>
+      </c>
+      <c r="H99">
+        <v>59.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K99">
+        <v>4.85</v>
+      </c>
+      <c r="L99">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M99">
+        <v>13.897696728</v>
+      </c>
+      <c r="N99">
+        <v>-9.447696727999999</v>
+      </c>
+      <c r="O99">
+        <v>-1.606108443759999</v>
+      </c>
+      <c r="P99">
+        <v>-7.841588284239999</v>
+      </c>
+      <c r="Q99">
+        <v>-2.99158828424</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.099566033983751</v>
+      </c>
+      <c r="T99">
+        <v>34.84413763466699</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05443348022380302</v>
+      </c>
+      <c r="W99">
+        <v>0.2258012849225559</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.320196942492959</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2840142273943917</v>
+      </c>
+      <c r="C100">
+        <v>-34.86687348644926</v>
+      </c>
+      <c r="D100">
+        <v>17.72116651355072</v>
+      </c>
+      <c r="E100">
+        <v>58.60003999999999</v>
+      </c>
+      <c r="F100">
+        <v>58.79803999999999</v>
+      </c>
+      <c r="G100">
+        <v>6.21</v>
+      </c>
+      <c r="H100">
+        <v>59.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K100">
+        <v>4.85</v>
+      </c>
+      <c r="L100">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M100">
+        <v>14.040971952</v>
+      </c>
+      <c r="N100">
+        <v>-9.590971951999999</v>
+      </c>
+      <c r="O100">
+        <v>-1.630465231839999</v>
+      </c>
+      <c r="P100">
+        <v>-7.96050672016</v>
+      </c>
+      <c r="Q100">
+        <v>-3.11050672016</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.129949050975627</v>
+      </c>
+      <c r="T100">
+        <v>52.26620645200049</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05387803654804993</v>
+      </c>
+      <c r="W100">
+        <v>0.2259339248723257</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.316929626753235</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2860142273943918</v>
+      </c>
+      <c r="C101">
+        <v>-35.59792140209424</v>
+      </c>
+      <c r="D101">
+        <v>17.59009859790576</v>
+      </c>
+      <c r="E101">
+        <v>59.20001999999999</v>
+      </c>
+      <c r="F101">
+        <v>59.39802</v>
+      </c>
+      <c r="G101">
+        <v>6.21</v>
+      </c>
+      <c r="H101">
+        <v>59.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K101">
+        <v>4.85</v>
+      </c>
+      <c r="L101">
+        <v>4.450000000000001</v>
+      </c>
+      <c r="M101">
+        <v>14.184247176</v>
+      </c>
+      <c r="N101">
+        <v>-9.734247175999998</v>
+      </c>
+      <c r="O101">
+        <v>-1.654822019919999</v>
+      </c>
+      <c r="P101">
+        <v>-8.079425156079999</v>
+      </c>
+      <c r="Q101">
+        <v>-3.22942515608</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.221098101951253</v>
+      </c>
+      <c r="T101">
+        <v>104.532412904001</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05333381395665548</v>
+      </c>
+      <c r="W101">
+        <v>0.2260638852271507</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3137283173920912</v>
+      </c>
+      <c r="Z101">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/singapore/singapore_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_precious_metals.xlsx
@@ -1504,7 +1504,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1641,22 +1641,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09062491126523738</v>
+        <v>0.09050819891608648</v>
       </c>
       <c r="C2">
-        <v>74.31684348433835</v>
+        <v>73.61123530424562</v>
       </c>
       <c r="D2">
-        <v>59.61684348433835</v>
+        <v>59.65513530424563</v>
       </c>
       <c r="E2">
-        <v>-1.59</v>
+        <v>-0.8461000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7439</v>
       </c>
       <c r="G2">
         <v>14.7</v>
@@ -1677,28 +1677,28 @@
         <v>11.66</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03741817</v>
       </c>
       <c r="N2">
-        <v>11.66</v>
+        <v>11.62258183</v>
       </c>
       <c r="O2">
-        <v>1.9822</v>
+        <v>1.9758389111</v>
       </c>
       <c r="P2">
-        <v>9.6778</v>
+        <v>9.646742918899999</v>
       </c>
       <c r="Q2">
-        <v>15.3178</v>
+        <v>15.2867429189</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09062491126523738</v>
+        <v>0.09100071607685503</v>
       </c>
       <c r="T2">
-        <v>1.035217350236429</v>
+        <v>1.043896445192957</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>311.6133151354008</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1723,22 +1723,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09050819891608648</v>
+        <v>0.09039148656693556</v>
       </c>
       <c r="C3">
-        <v>73.61123530424562</v>
+        <v>72.90567634533841</v>
       </c>
       <c r="D3">
-        <v>59.65513530424563</v>
+        <v>59.69347634533842</v>
       </c>
       <c r="E3">
-        <v>-0.8461000000000001</v>
+        <v>-0.1022000000000001</v>
       </c>
       <c r="F3">
-        <v>0.7439</v>
+        <v>1.4878</v>
       </c>
       <c r="G3">
         <v>14.7</v>
@@ -1759,28 +1759,28 @@
         <v>11.66</v>
       </c>
       <c r="M3">
-        <v>0.03741817</v>
+        <v>0.07483634</v>
       </c>
       <c r="N3">
-        <v>11.62258183</v>
+        <v>11.58516366</v>
       </c>
       <c r="O3">
-        <v>1.9758389111</v>
+        <v>1.9694778222</v>
       </c>
       <c r="P3">
-        <v>9.646742918899999</v>
+        <v>9.615685837800001</v>
       </c>
       <c r="Q3">
-        <v>15.2867429189</v>
+        <v>15.2556858378</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09100071607685503</v>
+        <v>0.09138419037442405</v>
       </c>
       <c r="T3">
-        <v>1.043896445192957</v>
+        <v>1.052752664536352</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>311.6133151354008</v>
+        <v>155.8066575677004</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1805,22 +1805,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09039148656693556</v>
+        <v>0.09027477421778467</v>
       </c>
       <c r="C4">
-        <v>72.90567634533841</v>
+        <v>72.20016670258279</v>
       </c>
       <c r="D4">
-        <v>59.69347634533842</v>
+        <v>59.7318667025828</v>
       </c>
       <c r="E4">
-        <v>-0.1022000000000001</v>
+        <v>0.6416999999999999</v>
       </c>
       <c r="F4">
-        <v>1.4878</v>
+        <v>2.2317</v>
       </c>
       <c r="G4">
         <v>14.7</v>
@@ -1841,28 +1841,28 @@
         <v>11.66</v>
       </c>
       <c r="M4">
-        <v>0.07483634</v>
+        <v>0.11225451</v>
       </c>
       <c r="N4">
-        <v>11.58516366</v>
+        <v>11.54774549</v>
       </c>
       <c r="O4">
-        <v>1.9694778222</v>
+        <v>1.9631167333</v>
       </c>
       <c r="P4">
-        <v>9.615685837800001</v>
+        <v>9.584628756700001</v>
       </c>
       <c r="Q4">
-        <v>15.2556858378</v>
+        <v>15.2246287567</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09138419037442405</v>
+        <v>0.09177557135854089</v>
       </c>
       <c r="T4">
-        <v>1.052752664536352</v>
+        <v>1.061791486340436</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>155.8066575677004</v>
+        <v>103.8711050451336</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1887,22 +1887,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09027477421778467</v>
+        <v>0.09015806186863377</v>
       </c>
       <c r="C5">
-        <v>72.20016670258279</v>
+        <v>71.49470647118935</v>
       </c>
       <c r="D5">
-        <v>59.7318667025828</v>
+        <v>59.77030647118935</v>
       </c>
       <c r="E5">
-        <v>0.6416999999999999</v>
+        <v>1.3856</v>
       </c>
       <c r="F5">
-        <v>2.2317</v>
+        <v>2.9756</v>
       </c>
       <c r="G5">
         <v>14.7</v>
@@ -1923,28 +1923,28 @@
         <v>11.66</v>
       </c>
       <c r="M5">
-        <v>0.11225451</v>
+        <v>0.14967268</v>
       </c>
       <c r="N5">
-        <v>11.54774549</v>
+        <v>11.51032732</v>
       </c>
       <c r="O5">
-        <v>1.9631167333</v>
+        <v>1.9567556444</v>
       </c>
       <c r="P5">
-        <v>9.584628756700001</v>
+        <v>9.553571675600001</v>
       </c>
       <c r="Q5">
-        <v>15.2246287567</v>
+        <v>15.1935716756</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09177557135854089</v>
+        <v>0.09217510611316018</v>
       </c>
       <c r="T5">
-        <v>1.061791486340436</v>
+        <v>1.071018616932106</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>103.8711050451336</v>
+        <v>77.9033287838502</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1969,22 +1969,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09015806186863377</v>
+        <v>0.09004134951948285</v>
       </c>
       <c r="C6">
-        <v>71.49470647118935</v>
+        <v>70.78929574661389</v>
       </c>
       <c r="D6">
-        <v>59.77030647118935</v>
+        <v>59.80879574661388</v>
       </c>
       <c r="E6">
-        <v>1.3856</v>
+        <v>2.1295</v>
       </c>
       <c r="F6">
-        <v>2.9756</v>
+        <v>3.7195</v>
       </c>
       <c r="G6">
         <v>14.7</v>
@@ -2005,28 +2005,28 @@
         <v>11.66</v>
       </c>
       <c r="M6">
-        <v>0.14967268</v>
+        <v>0.18709085</v>
       </c>
       <c r="N6">
-        <v>11.51032732</v>
+        <v>11.47290915</v>
       </c>
       <c r="O6">
-        <v>1.9567556444</v>
+        <v>1.9503945555</v>
       </c>
       <c r="P6">
-        <v>9.553571675600001</v>
+        <v>9.522514594499999</v>
       </c>
       <c r="Q6">
-        <v>15.1935716756</v>
+        <v>15.1625145945</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09217510611316018</v>
+        <v>0.09258305212577142</v>
       </c>
       <c r="T6">
-        <v>1.071018616932106</v>
+        <v>1.080440002904652</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>77.9033287838502</v>
+        <v>62.32266302708015</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2051,22 +2051,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09004134951948285</v>
+        <v>0.08992463717033194</v>
       </c>
       <c r="C7">
-        <v>70.78929574661389</v>
+        <v>70.0839346245582</v>
       </c>
       <c r="D7">
-        <v>59.80879574661388</v>
+        <v>59.84733462455821</v>
       </c>
       <c r="E7">
-        <v>2.1295</v>
+        <v>2.8734</v>
       </c>
       <c r="F7">
-        <v>3.7195</v>
+        <v>4.4634</v>
       </c>
       <c r="G7">
         <v>14.7</v>
@@ -2087,28 +2087,28 @@
         <v>11.66</v>
       </c>
       <c r="M7">
-        <v>0.18709085</v>
+        <v>0.22450902</v>
       </c>
       <c r="N7">
-        <v>11.47290915</v>
+        <v>11.43549098</v>
       </c>
       <c r="O7">
-        <v>1.9503945555</v>
+        <v>1.9440334666</v>
       </c>
       <c r="P7">
-        <v>9.522514594499999</v>
+        <v>9.4914575134</v>
       </c>
       <c r="Q7">
-        <v>15.1625145945</v>
+        <v>15.1314575134</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09258305212577142</v>
+        <v>0.09299967784077867</v>
       </c>
       <c r="T7">
-        <v>1.080440002904652</v>
+        <v>1.090061843897891</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>62.32266302708015</v>
+        <v>51.9355525225668</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08992463717033194</v>
+        <v>0.08980792482118106</v>
       </c>
       <c r="C8">
-        <v>70.0839346245582</v>
+        <v>69.37862320097098</v>
       </c>
       <c r="D8">
-        <v>59.84733462455821</v>
+        <v>59.88592320097099</v>
       </c>
       <c r="E8">
-        <v>2.8734</v>
+        <v>3.617299999999999</v>
       </c>
       <c r="F8">
-        <v>4.4634</v>
+        <v>5.207299999999999</v>
       </c>
       <c r="G8">
         <v>14.7</v>
@@ -2169,28 +2169,28 @@
         <v>11.66</v>
       </c>
       <c r="M8">
-        <v>0.22450902</v>
+        <v>0.2619271899999999</v>
       </c>
       <c r="N8">
-        <v>11.43549098</v>
+        <v>11.39807281</v>
       </c>
       <c r="O8">
-        <v>1.9440334666</v>
+        <v>1.9376723777</v>
       </c>
       <c r="P8">
-        <v>9.4914575134</v>
+        <v>9.4604004323</v>
       </c>
       <c r="Q8">
-        <v>15.1314575134</v>
+        <v>15.1004004323</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09299967784077867</v>
+        <v>0.09342526324858177</v>
       </c>
       <c r="T8">
-        <v>1.090061843897891</v>
+        <v>1.099890606202812</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.9355525225668</v>
+        <v>44.51618787648584</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2215,22 +2215,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08980792482118105</v>
+        <v>0.08969121247203014</v>
       </c>
       <c r="C9">
-        <v>69.37862320097098</v>
+        <v>68.67336157204855</v>
       </c>
       <c r="D9">
-        <v>59.88592320097099</v>
+        <v>59.92456157204855</v>
       </c>
       <c r="E9">
-        <v>3.617300000000001</v>
+        <v>4.3612</v>
       </c>
       <c r="F9">
-        <v>5.207300000000001</v>
+        <v>5.9512</v>
       </c>
       <c r="G9">
         <v>14.7</v>
@@ -2251,28 +2251,28 @@
         <v>11.66</v>
       </c>
       <c r="M9">
-        <v>0.26192719</v>
+        <v>0.29934536</v>
       </c>
       <c r="N9">
-        <v>11.39807281</v>
+        <v>11.36065464</v>
       </c>
       <c r="O9">
-        <v>1.9376723777</v>
+        <v>1.9313112888</v>
       </c>
       <c r="P9">
-        <v>9.4604004323</v>
+        <v>9.4293433512</v>
       </c>
       <c r="Q9">
-        <v>15.1004004323</v>
+        <v>15.0693433512</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09342526324858177</v>
+        <v>0.09386010051307625</v>
       </c>
       <c r="T9">
-        <v>1.099890606202812</v>
+        <v>1.109933037253493</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.51618787648582</v>
+        <v>38.9516643919251</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2297,22 +2297,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08969121247203014</v>
+        <v>0.08957450012287925</v>
       </c>
       <c r="C10">
-        <v>68.67336157204855</v>
+        <v>67.96814983423558</v>
       </c>
       <c r="D10">
-        <v>59.92456157204855</v>
+        <v>59.96324983423557</v>
       </c>
       <c r="E10">
-        <v>4.3612</v>
+        <v>5.1051</v>
       </c>
       <c r="F10">
-        <v>5.9512</v>
+        <v>6.6951</v>
       </c>
       <c r="G10">
         <v>14.7</v>
@@ -2333,28 +2333,28 @@
         <v>11.66</v>
       </c>
       <c r="M10">
-        <v>0.29934536</v>
+        <v>0.33676353</v>
       </c>
       <c r="N10">
-        <v>11.36065464</v>
+        <v>11.32323647</v>
       </c>
       <c r="O10">
-        <v>1.9313112888</v>
+        <v>1.9249501999</v>
       </c>
       <c r="P10">
-        <v>9.4293433512</v>
+        <v>9.3982862701</v>
       </c>
       <c r="Q10">
-        <v>15.0693433512</v>
+        <v>15.0382862701</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09386010051307625</v>
+        <v>0.09430449464052665</v>
       </c>
       <c r="T10">
-        <v>1.109933037253493</v>
+        <v>1.120196181074518</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.9516643919251</v>
+        <v>34.6237016817112</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2379,22 +2379,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08957450012287925</v>
+        <v>0.08945778777372834</v>
       </c>
       <c r="C11">
-        <v>67.96814983423558</v>
+        <v>67.26298808422601</v>
       </c>
       <c r="D11">
-        <v>59.96324983423557</v>
+        <v>60.00198808422601</v>
       </c>
       <c r="E11">
-        <v>5.1051</v>
+        <v>5.848999999999999</v>
       </c>
       <c r="F11">
-        <v>6.6951</v>
+        <v>7.438999999999999</v>
       </c>
       <c r="G11">
         <v>14.7</v>
@@ -2415,28 +2415,28 @@
         <v>11.66</v>
       </c>
       <c r="M11">
-        <v>0.33676353</v>
+        <v>0.3741817</v>
       </c>
       <c r="N11">
-        <v>11.32323647</v>
+        <v>11.2858183</v>
       </c>
       <c r="O11">
-        <v>1.9249501999</v>
+        <v>1.918589111</v>
       </c>
       <c r="P11">
-        <v>9.3982862701</v>
+        <v>9.367229189</v>
       </c>
       <c r="Q11">
-        <v>15.0382862701</v>
+        <v>15.007229189</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09430449464052665</v>
+        <v>0.09475876419303149</v>
       </c>
       <c r="T11">
-        <v>1.120196181074518</v>
+        <v>1.130687394758233</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.6237016817112</v>
+        <v>31.16133151354008</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2461,22 +2461,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08945778777372834</v>
+        <v>0.08934107542457743</v>
       </c>
       <c r="C12">
-        <v>67.26298808422601</v>
+        <v>66.55787641896383</v>
       </c>
       <c r="D12">
-        <v>60.00198808422601</v>
+        <v>60.04077641896383</v>
       </c>
       <c r="E12">
-        <v>5.849</v>
+        <v>6.5929</v>
       </c>
       <c r="F12">
-        <v>7.439</v>
+        <v>8.1829</v>
       </c>
       <c r="G12">
         <v>14.7</v>
@@ -2497,28 +2497,28 @@
         <v>11.66</v>
       </c>
       <c r="M12">
-        <v>0.3741817</v>
+        <v>0.41159987</v>
       </c>
       <c r="N12">
-        <v>11.2858183</v>
+        <v>11.24840013</v>
       </c>
       <c r="O12">
-        <v>1.918589111</v>
+        <v>1.9122280221</v>
       </c>
       <c r="P12">
-        <v>9.367229189</v>
+        <v>9.3361721079</v>
       </c>
       <c r="Q12">
-        <v>15.007229189</v>
+        <v>14.9761721079</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09475876419303149</v>
+        <v>0.095223242050087</v>
       </c>
       <c r="T12">
-        <v>1.130687394758233</v>
+        <v>1.141414366052818</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.16133151354008</v>
+        <v>28.32848319412735</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2543,22 +2543,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08934107542457743</v>
+        <v>0.08922436307542653</v>
       </c>
       <c r="C13">
-        <v>66.55787641896383</v>
+        <v>65.85281493564385</v>
       </c>
       <c r="D13">
-        <v>60.04077641896383</v>
+        <v>60.07961493564385</v>
       </c>
       <c r="E13">
-        <v>6.5929</v>
+        <v>7.3368</v>
       </c>
       <c r="F13">
-        <v>8.1829</v>
+        <v>8.9268</v>
       </c>
       <c r="G13">
         <v>14.7</v>
@@ -2579,28 +2579,28 @@
         <v>11.66</v>
       </c>
       <c r="M13">
-        <v>0.41159987</v>
+        <v>0.44901804</v>
       </c>
       <c r="N13">
-        <v>11.24840013</v>
+        <v>11.21098196</v>
       </c>
       <c r="O13">
-        <v>1.9122280221</v>
+        <v>1.9058669332</v>
       </c>
       <c r="P13">
-        <v>9.3361721079</v>
+        <v>9.305115026799999</v>
       </c>
       <c r="Q13">
-        <v>14.9761721079</v>
+        <v>14.9451150268</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.095223242050087</v>
+        <v>0.09569827622207561</v>
       </c>
       <c r="T13">
-        <v>1.141414366052818</v>
+        <v>1.152385132149552</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.32848319412735</v>
+        <v>25.9677762612834</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2625,22 +2625,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08922436307542653</v>
+        <v>0.08910765072627563</v>
       </c>
       <c r="C14">
-        <v>65.85281493564385</v>
+        <v>65.1478037317125</v>
       </c>
       <c r="D14">
-        <v>60.07961493564385</v>
+        <v>60.11850373171249</v>
       </c>
       <c r="E14">
-        <v>7.3368</v>
+        <v>8.0807</v>
       </c>
       <c r="F14">
-        <v>8.9268</v>
+        <v>9.6707</v>
       </c>
       <c r="G14">
         <v>14.7</v>
@@ -2661,28 +2661,28 @@
         <v>11.66</v>
       </c>
       <c r="M14">
-        <v>0.44901804</v>
+        <v>0.48643621</v>
       </c>
       <c r="N14">
-        <v>11.21098196</v>
+        <v>11.17356379</v>
       </c>
       <c r="O14">
-        <v>1.9058669332</v>
+        <v>1.8995058443</v>
       </c>
       <c r="P14">
-        <v>9.305115026799999</v>
+        <v>9.274057945699999</v>
       </c>
       <c r="Q14">
-        <v>14.9451150268</v>
+        <v>14.9140579457</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09569827622207561</v>
+        <v>0.09618423071985704</v>
       </c>
       <c r="T14">
-        <v>1.152385132149552</v>
+        <v>1.163608099765752</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.9677762612834</v>
+        <v>23.97025501041545</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2707,22 +2707,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08910765072627563</v>
+        <v>0.08899093837712471</v>
       </c>
       <c r="C15">
-        <v>65.1478037317125</v>
+        <v>64.44284290486875</v>
       </c>
       <c r="D15">
-        <v>60.11850373171249</v>
+        <v>60.15744290486876</v>
       </c>
       <c r="E15">
-        <v>8.0807</v>
+        <v>8.824600000000002</v>
       </c>
       <c r="F15">
-        <v>9.6707</v>
+        <v>10.4146</v>
       </c>
       <c r="G15">
         <v>14.7</v>
@@ -2743,28 +2743,28 @@
         <v>11.66</v>
       </c>
       <c r="M15">
-        <v>0.48643621</v>
+        <v>0.5238543800000001</v>
       </c>
       <c r="N15">
-        <v>11.17356379</v>
+        <v>11.13614562</v>
       </c>
       <c r="O15">
-        <v>1.8995058443</v>
+        <v>1.8931447554</v>
       </c>
       <c r="P15">
-        <v>9.274057945699999</v>
+        <v>9.243000864600001</v>
       </c>
       <c r="Q15">
-        <v>14.9140579457</v>
+        <v>14.8830008646</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09618423071985704</v>
+        <v>0.09668148648502875</v>
       </c>
       <c r="T15">
-        <v>1.163608099765752</v>
+        <v>1.17509206662884</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.97025501041545</v>
+        <v>22.25809393824291</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2789,22 +2789,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08899093837712471</v>
+        <v>0.08887422602797382</v>
       </c>
       <c r="C16">
-        <v>64.44284290486875</v>
+        <v>63.73793255306479</v>
       </c>
       <c r="D16">
-        <v>60.15744290486876</v>
+        <v>60.1964325530648</v>
       </c>
       <c r="E16">
-        <v>8.824600000000002</v>
+        <v>9.568500000000002</v>
       </c>
       <c r="F16">
-        <v>10.4146</v>
+        <v>11.1585</v>
       </c>
       <c r="G16">
         <v>14.7</v>
@@ -2825,28 +2825,28 @@
         <v>11.66</v>
       </c>
       <c r="M16">
-        <v>0.5238543800000001</v>
+        <v>0.5612725500000001</v>
       </c>
       <c r="N16">
-        <v>11.13614562</v>
+        <v>11.09872745</v>
       </c>
       <c r="O16">
-        <v>1.8931447554</v>
+        <v>1.8867836665</v>
       </c>
       <c r="P16">
-        <v>9.243000864600001</v>
+        <v>9.211943783500001</v>
       </c>
       <c r="Q16">
-        <v>14.8830008646</v>
+        <v>14.8519437835</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09668148648502875</v>
+        <v>0.09719044238585156</v>
       </c>
       <c r="T16">
-        <v>1.17509206662884</v>
+        <v>1.186846244476941</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.25809393824291</v>
+        <v>20.77422100902672</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2871,22 +2871,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08887422602797382</v>
+        <v>0.0887575136788229</v>
       </c>
       <c r="C17">
-        <v>63.73793255306479</v>
+        <v>63.03307277450698</v>
       </c>
       <c r="D17">
-        <v>60.1964325530648</v>
+        <v>60.23547277450697</v>
       </c>
       <c r="E17">
-        <v>9.5685</v>
+        <v>10.3124</v>
       </c>
       <c r="F17">
-        <v>11.1585</v>
+        <v>11.9024</v>
       </c>
       <c r="G17">
         <v>14.7</v>
@@ -2907,28 +2907,28 @@
         <v>11.66</v>
       </c>
       <c r="M17">
-        <v>0.56127255</v>
+        <v>0.59869072</v>
       </c>
       <c r="N17">
-        <v>11.09872745</v>
+        <v>11.06130928</v>
       </c>
       <c r="O17">
-        <v>1.8867836665</v>
+        <v>1.8804225776</v>
       </c>
       <c r="P17">
-        <v>9.211943783500001</v>
+        <v>9.180886702399999</v>
       </c>
       <c r="Q17">
-        <v>14.8519437835</v>
+        <v>14.8208867024</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09719044238585156</v>
+        <v>0.09771151628431299</v>
       </c>
       <c r="T17">
-        <v>1.186846244476941</v>
+        <v>1.198880283702379</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.77422100902672</v>
+        <v>19.47583219596255</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2953,22 +2953,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0887575136788229</v>
+        <v>0.08864080132967202</v>
       </c>
       <c r="C18">
-        <v>63.03307277450698</v>
+        <v>62.32826366765649</v>
       </c>
       <c r="D18">
-        <v>60.23547277450697</v>
+        <v>60.2745636676565</v>
       </c>
       <c r="E18">
-        <v>10.3124</v>
+        <v>11.0563</v>
       </c>
       <c r="F18">
-        <v>11.9024</v>
+        <v>12.6463</v>
       </c>
       <c r="G18">
         <v>14.7</v>
@@ -2989,28 +2989,28 @@
         <v>11.66</v>
       </c>
       <c r="M18">
-        <v>0.59869072</v>
+        <v>0.63610889</v>
       </c>
       <c r="N18">
-        <v>11.06130928</v>
+        <v>11.02389111</v>
       </c>
       <c r="O18">
-        <v>1.8804225776</v>
+        <v>1.8740614887</v>
       </c>
       <c r="P18">
-        <v>9.180886702399999</v>
+        <v>9.1498296213</v>
       </c>
       <c r="Q18">
-        <v>14.8208867024</v>
+        <v>14.7898296213</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09771151628431299</v>
+        <v>0.09824514618032773</v>
       </c>
       <c r="T18">
-        <v>1.198880283702379</v>
+        <v>1.211204299776622</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.47583219596255</v>
+        <v>18.33019500796475</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3035,22 +3035,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08864080132967202</v>
+        <v>0.08852408898052111</v>
       </c>
       <c r="C19">
-        <v>62.32826366765649</v>
+        <v>61.62350533123043</v>
       </c>
       <c r="D19">
-        <v>60.2745636676565</v>
+        <v>60.31370533123043</v>
       </c>
       <c r="E19">
-        <v>11.0563</v>
+        <v>11.8002</v>
       </c>
       <c r="F19">
-        <v>12.6463</v>
+        <v>13.3902</v>
       </c>
       <c r="G19">
         <v>14.7</v>
@@ -3071,28 +3071,28 @@
         <v>11.66</v>
       </c>
       <c r="M19">
-        <v>0.63610889</v>
+        <v>0.6735270600000001</v>
       </c>
       <c r="N19">
-        <v>11.02389111</v>
+        <v>10.98647294</v>
       </c>
       <c r="O19">
-        <v>1.8740614887</v>
+        <v>1.8677003998</v>
       </c>
       <c r="P19">
-        <v>9.1498296213</v>
+        <v>9.1187725402</v>
       </c>
       <c r="Q19">
-        <v>14.7898296213</v>
+        <v>14.7587725402</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09824514618032773</v>
+        <v>0.0987917914396599</v>
       </c>
       <c r="T19">
-        <v>1.211204299776622</v>
+        <v>1.223828901608774</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.33019500796475</v>
+        <v>17.3118508408556</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3117,22 +3117,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08852408898052111</v>
+        <v>0.0884073766313702</v>
       </c>
       <c r="C20">
-        <v>61.62350533123043</v>
+        <v>60.91879786420233</v>
       </c>
       <c r="D20">
-        <v>60.31370533123043</v>
+        <v>60.35289786420233</v>
       </c>
       <c r="E20">
-        <v>11.8002</v>
+        <v>12.5441</v>
       </c>
       <c r="F20">
-        <v>13.3902</v>
+        <v>14.1341</v>
       </c>
       <c r="G20">
         <v>14.7</v>
@@ -3153,28 +3153,28 @@
         <v>11.66</v>
       </c>
       <c r="M20">
-        <v>0.67352706</v>
+        <v>0.71094523</v>
       </c>
       <c r="N20">
-        <v>10.98647294</v>
+        <v>10.94905477</v>
       </c>
       <c r="O20">
-        <v>1.8677003998</v>
+        <v>1.8613393109</v>
       </c>
       <c r="P20">
-        <v>9.1187725402</v>
+        <v>9.0877154591</v>
       </c>
       <c r="Q20">
-        <v>14.7587725402</v>
+        <v>14.7277154591</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0987917914396599</v>
+        <v>0.09935193411280271</v>
       </c>
       <c r="T20">
-        <v>1.223828901608774</v>
+        <v>1.236765222004682</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.3118508408556</v>
+        <v>16.40070079660004</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0884073766313702</v>
+        <v>0.08829066428221932</v>
       </c>
       <c r="C21">
-        <v>60.91879786420233</v>
+        <v>60.21414136580324</v>
       </c>
       <c r="D21">
-        <v>60.35289786420233</v>
+        <v>60.39214136580325</v>
       </c>
       <c r="E21">
-        <v>12.5441</v>
+        <v>13.288</v>
       </c>
       <c r="F21">
-        <v>14.1341</v>
+        <v>14.878</v>
       </c>
       <c r="G21">
         <v>14.7</v>
@@ -3235,28 +3235,28 @@
         <v>11.66</v>
       </c>
       <c r="M21">
-        <v>0.71094523</v>
+        <v>0.7483634</v>
       </c>
       <c r="N21">
-        <v>10.94905477</v>
+        <v>10.9116366</v>
       </c>
       <c r="O21">
-        <v>1.8613393109</v>
+        <v>1.854978222</v>
       </c>
       <c r="P21">
-        <v>9.0877154591</v>
+        <v>9.056658378</v>
       </c>
       <c r="Q21">
-        <v>14.7277154591</v>
+        <v>14.696658378</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09935193411280271</v>
+        <v>0.09992608035277414</v>
       </c>
       <c r="T21">
-        <v>1.236765222004682</v>
+        <v>1.250024950410488</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.40070079660004</v>
+        <v>15.58066575677004</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3281,22 +3281,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08829066428221932</v>
+        <v>0.0881739519330684</v>
       </c>
       <c r="C22">
-        <v>60.21414136580324</v>
+        <v>59.50953593552244</v>
       </c>
       <c r="D22">
-        <v>60.39214136580325</v>
+        <v>60.43143593552245</v>
       </c>
       <c r="E22">
-        <v>13.288</v>
+        <v>14.0319</v>
       </c>
       <c r="F22">
-        <v>14.878</v>
+        <v>15.6219</v>
       </c>
       <c r="G22">
         <v>14.7</v>
@@ -3317,28 +3317,28 @@
         <v>11.66</v>
       </c>
       <c r="M22">
-        <v>0.7483634</v>
+        <v>0.78578157</v>
       </c>
       <c r="N22">
-        <v>10.9116366</v>
+        <v>10.87421843</v>
       </c>
       <c r="O22">
-        <v>1.854978222</v>
+        <v>1.8486171331</v>
       </c>
       <c r="P22">
-        <v>9.056658378</v>
+        <v>9.0256012969</v>
       </c>
       <c r="Q22">
-        <v>14.696658378</v>
+        <v>14.6656012969</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09992608035277414</v>
+        <v>0.1005147619405929</v>
       </c>
       <c r="T22">
-        <v>1.250024950410488</v>
+        <v>1.263620368143023</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.58066575677004</v>
+        <v>14.83872929216194</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3363,22 +3363,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0881739519330684</v>
+        <v>0.08805723958391751</v>
       </c>
       <c r="C23">
-        <v>59.50953593552245</v>
+        <v>58.80498167310835</v>
       </c>
       <c r="D23">
-        <v>60.43143593552245</v>
+        <v>60.47078167310836</v>
       </c>
       <c r="E23">
-        <v>14.0319</v>
+        <v>14.7758</v>
       </c>
       <c r="F23">
-        <v>15.6219</v>
+        <v>16.3658</v>
       </c>
       <c r="G23">
         <v>14.7</v>
@@ -3399,28 +3399,28 @@
         <v>11.66</v>
       </c>
       <c r="M23">
-        <v>0.7857815699999999</v>
+        <v>0.82319974</v>
       </c>
       <c r="N23">
-        <v>10.87421843</v>
+        <v>10.83680026</v>
       </c>
       <c r="O23">
-        <v>1.8486171331</v>
+        <v>1.8422560442</v>
       </c>
       <c r="P23">
-        <v>9.0256012969</v>
+        <v>8.9945442158</v>
       </c>
       <c r="Q23">
-        <v>14.6656012969</v>
+        <v>14.6345442158</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1005147619405929</v>
+        <v>0.1011185379280994</v>
       </c>
       <c r="T23">
-        <v>1.263620368143023</v>
+        <v>1.277564386330239</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.83872929216195</v>
+        <v>14.16424159706367</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3445,22 +3445,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08805723958391751</v>
+        <v>0.08794052723476659</v>
       </c>
       <c r="C24">
-        <v>58.80498167310835</v>
+        <v>58.10047867856926</v>
       </c>
       <c r="D24">
-        <v>60.47078167310836</v>
+        <v>60.51017867856927</v>
       </c>
       <c r="E24">
-        <v>14.7758</v>
+        <v>15.5197</v>
       </c>
       <c r="F24">
-        <v>16.3658</v>
+        <v>17.1097</v>
       </c>
       <c r="G24">
         <v>14.7</v>
@@ -3481,28 +3481,28 @@
         <v>11.66</v>
       </c>
       <c r="M24">
-        <v>0.82319974</v>
+        <v>0.86061791</v>
       </c>
       <c r="N24">
-        <v>10.83680026</v>
+        <v>10.79938209</v>
       </c>
       <c r="O24">
-        <v>1.8422560442</v>
+        <v>1.8358949553</v>
       </c>
       <c r="P24">
-        <v>8.9945442158</v>
+        <v>8.963487134699999</v>
       </c>
       <c r="Q24">
-        <v>14.6345442158</v>
+        <v>14.6034871347</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1011185379280994</v>
+        <v>0.1017379964087878</v>
       </c>
       <c r="T24">
-        <v>1.277564386330239</v>
+        <v>1.291870586808032</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.16424159706367</v>
+        <v>13.54840500588699</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3527,22 +3527,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08794052723476659</v>
+        <v>0.08782381488561569</v>
       </c>
       <c r="C25">
-        <v>58.10047867856926</v>
+        <v>57.39602705217433</v>
       </c>
       <c r="D25">
-        <v>60.51017867856927</v>
+        <v>60.54962705217433</v>
       </c>
       <c r="E25">
-        <v>15.5197</v>
+        <v>16.2636</v>
       </c>
       <c r="F25">
-        <v>17.1097</v>
+        <v>17.8536</v>
       </c>
       <c r="G25">
         <v>14.7</v>
@@ -3563,28 +3563,28 @@
         <v>11.66</v>
       </c>
       <c r="M25">
-        <v>0.86061791</v>
+        <v>0.89803608</v>
       </c>
       <c r="N25">
-        <v>10.79938209</v>
+        <v>10.76196392</v>
       </c>
       <c r="O25">
-        <v>1.8358949553</v>
+        <v>1.8295338664</v>
       </c>
       <c r="P25">
-        <v>8.963487134699999</v>
+        <v>8.932430053599999</v>
       </c>
       <c r="Q25">
-        <v>14.6034871347</v>
+        <v>14.5724300536</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1017379964087878</v>
+        <v>0.1023737564284417</v>
       </c>
       <c r="T25">
-        <v>1.291870586808032</v>
+        <v>1.306553266245767</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.54840500588699</v>
+        <v>12.9838881306417</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3609,22 +3609,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08782381488561569</v>
+        <v>0.08801835253646477</v>
       </c>
       <c r="C26">
-        <v>57.39602705217433</v>
+        <v>56.58640254640945</v>
       </c>
       <c r="D26">
-        <v>60.54962705217433</v>
+        <v>60.48390254640945</v>
       </c>
       <c r="E26">
-        <v>16.2636</v>
+        <v>17.0075</v>
       </c>
       <c r="F26">
-        <v>17.8536</v>
+        <v>18.5975</v>
       </c>
       <c r="G26">
         <v>14.7</v>
@@ -3645,45 +3645,45 @@
         <v>11.66</v>
       </c>
       <c r="M26">
-        <v>0.89803608</v>
+        <v>0.9633505</v>
       </c>
       <c r="N26">
-        <v>10.76196392</v>
+        <v>10.6966495</v>
       </c>
       <c r="O26">
-        <v>1.8295338664</v>
+        <v>1.818430415</v>
       </c>
       <c r="P26">
-        <v>8.932430053599999</v>
+        <v>8.878219085</v>
       </c>
       <c r="Q26">
-        <v>14.5724300536</v>
+        <v>14.518219085</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1023737564284417</v>
+        <v>0.1030264700486197</v>
       </c>
       <c r="T26">
-        <v>1.306553266245767</v>
+        <v>1.321627483801841</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.17</v>
       </c>
       <c r="W26">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>12.9838881306417</v>
+        <v>12.10359054155263</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3691,22 +3691,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08801835253646477</v>
+        <v>0.08791409018731387</v>
       </c>
       <c r="C27">
-        <v>56.58640254640945</v>
+        <v>55.87770980631735</v>
       </c>
       <c r="D27">
-        <v>60.48390254640945</v>
+        <v>60.51910980631735</v>
       </c>
       <c r="E27">
-        <v>17.0075</v>
+        <v>17.7514</v>
       </c>
       <c r="F27">
-        <v>18.5975</v>
+        <v>19.3414</v>
       </c>
       <c r="G27">
         <v>14.7</v>
@@ -3727,28 +3727,28 @@
         <v>11.66</v>
       </c>
       <c r="M27">
-        <v>0.9633505</v>
+        <v>1.00188452</v>
       </c>
       <c r="N27">
-        <v>10.6966495</v>
+        <v>10.65811548</v>
       </c>
       <c r="O27">
-        <v>1.818430415</v>
+        <v>1.8118796316</v>
       </c>
       <c r="P27">
-        <v>8.878219085</v>
+        <v>8.846235848399999</v>
       </c>
       <c r="Q27">
-        <v>14.518219085</v>
+        <v>14.4862358484</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1030264700486197</v>
+        <v>0.1036968245774512</v>
       </c>
       <c r="T27">
-        <v>1.321627483801841</v>
+        <v>1.337109112643215</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.10359054155263</v>
+        <v>11.63806782841599</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3773,22 +3773,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08791409018731387</v>
+        <v>0.08780982783816299</v>
       </c>
       <c r="C28">
-        <v>55.87770980631735</v>
+        <v>55.16905807790114</v>
       </c>
       <c r="D28">
-        <v>60.51910980631735</v>
+        <v>60.55435807790115</v>
       </c>
       <c r="E28">
-        <v>17.7514</v>
+        <v>18.4953</v>
       </c>
       <c r="F28">
-        <v>19.3414</v>
+        <v>20.0853</v>
       </c>
       <c r="G28">
         <v>14.7</v>
@@ -3809,28 +3809,28 @@
         <v>11.66</v>
       </c>
       <c r="M28">
-        <v>1.00188452</v>
+        <v>1.04041854</v>
       </c>
       <c r="N28">
-        <v>10.65811548</v>
+        <v>10.61958146</v>
       </c>
       <c r="O28">
-        <v>1.8118796316</v>
+        <v>1.8053288482</v>
       </c>
       <c r="P28">
-        <v>8.846235848399999</v>
+        <v>8.814252611800001</v>
       </c>
       <c r="Q28">
-        <v>14.4862358484</v>
+        <v>14.4542526118</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1036968245774512</v>
+        <v>0.1043855449837849</v>
       </c>
       <c r="T28">
-        <v>1.337109112643215</v>
+        <v>1.353014895699421</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.63806782841599</v>
+        <v>11.2070282792154</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3855,22 +3855,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08780982783816299</v>
+        <v>0.08770556548901208</v>
       </c>
       <c r="C29">
-        <v>55.16905807790114</v>
+        <v>54.4604474328622</v>
       </c>
       <c r="D29">
-        <v>60.55435807790115</v>
+        <v>60.58964743286219</v>
       </c>
       <c r="E29">
-        <v>18.4953</v>
+        <v>19.2392</v>
       </c>
       <c r="F29">
-        <v>20.0853</v>
+        <v>20.8292</v>
       </c>
       <c r="G29">
         <v>14.7</v>
@@ -3891,28 +3891,28 @@
         <v>11.66</v>
       </c>
       <c r="M29">
-        <v>1.04041854</v>
+        <v>1.07895256</v>
       </c>
       <c r="N29">
-        <v>10.61958146</v>
+        <v>10.58104744</v>
       </c>
       <c r="O29">
-        <v>1.8053288482</v>
+        <v>1.7987780648</v>
       </c>
       <c r="P29">
-        <v>8.814252611800001</v>
+        <v>8.7822693752</v>
       </c>
       <c r="Q29">
-        <v>14.4542526118</v>
+        <v>14.4222693752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1043855449837849</v>
+        <v>0.1050933965125168</v>
       </c>
       <c r="T29">
-        <v>1.353014895699421</v>
+        <v>1.369362506062743</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.2070282792154</v>
+        <v>10.80677726924342</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3937,22 +3937,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08770556548901208</v>
+        <v>0.08760130313986116</v>
       </c>
       <c r="C30">
-        <v>54.4604474328622</v>
+        <v>53.75187794306901</v>
       </c>
       <c r="D30">
-        <v>60.58964743286219</v>
+        <v>60.62497794306901</v>
       </c>
       <c r="E30">
-        <v>19.2392</v>
+        <v>19.9831</v>
       </c>
       <c r="F30">
-        <v>20.8292</v>
+        <v>21.5731</v>
       </c>
       <c r="G30">
         <v>14.7</v>
@@ -3973,28 +3973,28 @@
         <v>11.66</v>
       </c>
       <c r="M30">
-        <v>1.07895256</v>
+        <v>1.11748658</v>
       </c>
       <c r="N30">
-        <v>10.58104744</v>
+        <v>10.54251342</v>
       </c>
       <c r="O30">
-        <v>1.7987780648</v>
+        <v>1.7922272814</v>
       </c>
       <c r="P30">
-        <v>8.7822693752</v>
+        <v>8.7502861386</v>
       </c>
       <c r="Q30">
-        <v>14.4222693752</v>
+        <v>14.3902861386</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1050933965125168</v>
+        <v>0.1058211875209312</v>
       </c>
       <c r="T30">
-        <v>1.369362506062743</v>
+        <v>1.386170612492638</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.80677726924342</v>
+        <v>10.43412977720054</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4019,22 +4019,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08760130313986116</v>
+        <v>0.08749704079071026</v>
       </c>
       <c r="C31">
-        <v>53.75187794306902</v>
+        <v>53.04334968055786</v>
       </c>
       <c r="D31">
-        <v>60.62497794306901</v>
+        <v>60.66034968055786</v>
       </c>
       <c r="E31">
-        <v>19.9831</v>
+        <v>20.727</v>
       </c>
       <c r="F31">
-        <v>21.5731</v>
+        <v>22.317</v>
       </c>
       <c r="G31">
         <v>14.7</v>
@@ -4055,28 +4055,28 @@
         <v>11.66</v>
       </c>
       <c r="M31">
-        <v>1.11748658</v>
+        <v>1.1560206</v>
       </c>
       <c r="N31">
-        <v>10.54251342</v>
+        <v>10.5039794</v>
       </c>
       <c r="O31">
-        <v>1.7922272814</v>
+        <v>1.785676498</v>
       </c>
       <c r="P31">
-        <v>8.7502861386</v>
+        <v>8.718302902</v>
       </c>
       <c r="Q31">
-        <v>14.3902861386</v>
+        <v>14.358302902</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1058211875209312</v>
+        <v>0.1065697725581575</v>
       </c>
       <c r="T31">
-        <v>1.386170612492638</v>
+        <v>1.403458950534816</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.43412977720055</v>
+        <v>10.08632545129386</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4101,22 +4101,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08749704079071026</v>
+        <v>0.08783018844155936</v>
       </c>
       <c r="C32">
-        <v>53.04334968055786</v>
+        <v>52.18657148445951</v>
       </c>
       <c r="D32">
-        <v>60.66034968055786</v>
+        <v>60.54747148445951</v>
       </c>
       <c r="E32">
-        <v>20.727</v>
+        <v>21.4709</v>
       </c>
       <c r="F32">
-        <v>22.317</v>
+        <v>23.0609</v>
       </c>
       <c r="G32">
         <v>14.7</v>
@@ -4137,45 +4137,45 @@
         <v>11.66</v>
       </c>
       <c r="M32">
-        <v>1.1560206</v>
+        <v>1.23375815</v>
       </c>
       <c r="N32">
-        <v>10.5039794</v>
+        <v>10.42624185</v>
       </c>
       <c r="O32">
-        <v>1.785676498</v>
+        <v>1.7724611145</v>
       </c>
       <c r="P32">
-        <v>8.718302902</v>
+        <v>8.6537807355</v>
       </c>
       <c r="Q32">
-        <v>14.358302902</v>
+        <v>14.2937807355</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1065697725581575</v>
+        <v>0.1073400557124049</v>
       </c>
       <c r="T32">
-        <v>1.403458950534816</v>
+        <v>1.421248399824593</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.17</v>
       </c>
       <c r="W32">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>10.08632545129386</v>
+        <v>9.450798764733591</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4183,22 +4183,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08783018844155936</v>
+        <v>0.08774003609240846</v>
       </c>
       <c r="C33">
-        <v>52.18657148445951</v>
+        <v>51.47317572383558</v>
       </c>
       <c r="D33">
-        <v>60.54747148445951</v>
+        <v>60.57797572383559</v>
       </c>
       <c r="E33">
-        <v>21.4709</v>
+        <v>22.2148</v>
       </c>
       <c r="F33">
-        <v>23.0609</v>
+        <v>23.8048</v>
       </c>
       <c r="G33">
         <v>14.7</v>
@@ -4219,28 +4219,28 @@
         <v>11.66</v>
       </c>
       <c r="M33">
-        <v>1.23375815</v>
+        <v>1.2735568</v>
       </c>
       <c r="N33">
-        <v>10.42624185</v>
+        <v>10.3864432</v>
       </c>
       <c r="O33">
-        <v>1.7724611145</v>
+        <v>1.765695344</v>
       </c>
       <c r="P33">
-        <v>8.6537807355</v>
+        <v>8.620747855999999</v>
       </c>
       <c r="Q33">
-        <v>14.2937807355</v>
+        <v>14.260747856</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1073400557124049</v>
+        <v>0.1081329942535419</v>
       </c>
       <c r="T33">
-        <v>1.421248399824593</v>
+        <v>1.439561068211128</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.450798764733591</v>
+        <v>9.155461303335667</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08774003609240846</v>
+        <v>0.08764988374325756</v>
       </c>
       <c r="C34">
-        <v>51.47317572383558</v>
+        <v>50.7598107152028</v>
       </c>
       <c r="D34">
-        <v>60.57797572383559</v>
+        <v>60.6085107152028</v>
       </c>
       <c r="E34">
-        <v>22.2148</v>
+        <v>22.9587</v>
       </c>
       <c r="F34">
-        <v>23.8048</v>
+        <v>24.5487</v>
       </c>
       <c r="G34">
         <v>14.7</v>
@@ -4301,28 +4301,28 @@
         <v>11.66</v>
       </c>
       <c r="M34">
-        <v>1.2735568</v>
+        <v>1.31335545</v>
       </c>
       <c r="N34">
-        <v>10.3864432</v>
+        <v>10.34664455</v>
       </c>
       <c r="O34">
-        <v>1.765695344</v>
+        <v>1.7589295735</v>
       </c>
       <c r="P34">
-        <v>8.620747855999999</v>
+        <v>8.587714976500001</v>
       </c>
       <c r="Q34">
-        <v>14.260747856</v>
+        <v>14.2277149765</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1081329942535419</v>
+        <v>0.108949602601877</v>
       </c>
       <c r="T34">
-        <v>1.439561068211128</v>
+        <v>1.458420383415172</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.155461303335667</v>
+        <v>8.878023082022464</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4347,22 +4347,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08764988374325756</v>
+        <v>0.08755973139410665</v>
       </c>
       <c r="C35">
-        <v>50.7598107152028</v>
+        <v>50.0464765050872</v>
       </c>
       <c r="D35">
-        <v>60.6085107152028</v>
+        <v>60.6390765050872</v>
       </c>
       <c r="E35">
-        <v>22.9587</v>
+        <v>23.7026</v>
       </c>
       <c r="F35">
-        <v>24.5487</v>
+        <v>25.2926</v>
       </c>
       <c r="G35">
         <v>14.7</v>
@@ -4383,28 +4383,28 @@
         <v>11.66</v>
       </c>
       <c r="M35">
-        <v>1.31335545</v>
+        <v>1.3531541</v>
       </c>
       <c r="N35">
-        <v>10.34664455</v>
+        <v>10.3068459</v>
       </c>
       <c r="O35">
-        <v>1.7589295735</v>
+        <v>1.752163803</v>
       </c>
       <c r="P35">
-        <v>8.587714976500001</v>
+        <v>8.554682096999999</v>
       </c>
       <c r="Q35">
-        <v>14.2277149765</v>
+        <v>14.194682097</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.108949602601877</v>
+        <v>0.1097909566577374</v>
       </c>
       <c r="T35">
-        <v>1.458420383415172</v>
+        <v>1.477851193019339</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.878023082022464</v>
+        <v>8.616904756080626</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4429,22 +4429,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08755973139410665</v>
+        <v>0.08746957904495575</v>
       </c>
       <c r="C36">
-        <v>50.0464765050872</v>
+        <v>49.33317314010883</v>
       </c>
       <c r="D36">
-        <v>60.6390765050872</v>
+        <v>60.66967314010883</v>
       </c>
       <c r="E36">
-        <v>23.7026</v>
+        <v>24.4465</v>
       </c>
       <c r="F36">
-        <v>25.2926</v>
+        <v>26.0365</v>
       </c>
       <c r="G36">
         <v>14.7</v>
@@ -4465,28 +4465,28 @@
         <v>11.66</v>
       </c>
       <c r="M36">
-        <v>1.3531541</v>
+        <v>1.39295275</v>
       </c>
       <c r="N36">
-        <v>10.3068459</v>
+        <v>10.26704725</v>
       </c>
       <c r="O36">
-        <v>1.752163803</v>
+        <v>1.7453980325</v>
       </c>
       <c r="P36">
-        <v>8.554682096999999</v>
+        <v>8.5216492175</v>
       </c>
       <c r="Q36">
-        <v>14.194682097</v>
+        <v>14.1616492175</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1097909566577374</v>
+        <v>0.1106581985307012</v>
       </c>
       <c r="T36">
-        <v>1.477851193019339</v>
+        <v>1.497879873688249</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.616904756080626</v>
+        <v>8.370707477335467</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4511,22 +4511,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08746957904495575</v>
+        <v>0.08737942669580484</v>
       </c>
       <c r="C37">
-        <v>49.33317314010883</v>
+        <v>48.61990066698176</v>
       </c>
       <c r="D37">
-        <v>60.66967314010883</v>
+        <v>60.70030066698177</v>
       </c>
       <c r="E37">
-        <v>24.4465</v>
+        <v>25.1904</v>
       </c>
       <c r="F37">
-        <v>26.0365</v>
+        <v>26.7804</v>
       </c>
       <c r="G37">
         <v>14.7</v>
@@ -4547,28 +4547,28 @@
         <v>11.66</v>
       </c>
       <c r="M37">
-        <v>1.39295275</v>
+        <v>1.4327514</v>
       </c>
       <c r="N37">
-        <v>10.26704725</v>
+        <v>10.2272486</v>
       </c>
       <c r="O37">
-        <v>1.7453980325</v>
+        <v>1.738632262</v>
       </c>
       <c r="P37">
-        <v>8.5216492175</v>
+        <v>8.488616338</v>
       </c>
       <c r="Q37">
-        <v>14.1616492175</v>
+        <v>14.128616338</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1106581985307012</v>
+        <v>0.1115525417121951</v>
       </c>
       <c r="T37">
-        <v>1.497879873688249</v>
+        <v>1.518534450628062</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.370707477335467</v>
+        <v>8.138187825187257</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4593,22 +4593,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08737942669580485</v>
+        <v>0.08728927434665394</v>
       </c>
       <c r="C38">
-        <v>48.61990066698176</v>
+        <v>47.90665913251455</v>
       </c>
       <c r="D38">
-        <v>60.70030066698177</v>
+        <v>60.73095913251454</v>
       </c>
       <c r="E38">
-        <v>25.1904</v>
+        <v>25.9343</v>
       </c>
       <c r="F38">
-        <v>26.7804</v>
+        <v>27.5243</v>
       </c>
       <c r="G38">
         <v>14.7</v>
@@ -4629,28 +4629,28 @@
         <v>11.66</v>
       </c>
       <c r="M38">
-        <v>1.4327514</v>
+        <v>1.47255005</v>
       </c>
       <c r="N38">
-        <v>10.2272486</v>
+        <v>10.18744995</v>
       </c>
       <c r="O38">
-        <v>1.738632262</v>
+        <v>1.7318664915</v>
       </c>
       <c r="P38">
-        <v>8.488616338</v>
+        <v>8.4555834585</v>
       </c>
       <c r="Q38">
-        <v>14.128616338</v>
+        <v>14.0955834585</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1115525417121951</v>
+        <v>0.1124752767407206</v>
       </c>
       <c r="T38">
-        <v>1.518534450628062</v>
+        <v>1.539844728423108</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.138187825187259</v>
+        <v>7.9182368028849</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4675,22 +4675,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08728927434665394</v>
+        <v>0.08719912199750304</v>
       </c>
       <c r="C39">
-        <v>47.90665913251455</v>
+        <v>47.19344858361027</v>
       </c>
       <c r="D39">
-        <v>60.73095913251454</v>
+        <v>60.76164858361027</v>
       </c>
       <c r="E39">
-        <v>25.9343</v>
+        <v>26.6782</v>
       </c>
       <c r="F39">
-        <v>27.5243</v>
+        <v>28.2682</v>
       </c>
       <c r="G39">
         <v>14.7</v>
@@ -4711,28 +4711,28 @@
         <v>11.66</v>
       </c>
       <c r="M39">
-        <v>1.47255005</v>
+        <v>1.5123487</v>
       </c>
       <c r="N39">
-        <v>10.18744995</v>
+        <v>10.1476513</v>
       </c>
       <c r="O39">
-        <v>1.7318664915</v>
+        <v>1.725100721</v>
       </c>
       <c r="P39">
-        <v>8.4555834585</v>
+        <v>8.422550578999999</v>
       </c>
       <c r="Q39">
-        <v>14.0955834585</v>
+        <v>14.062550579</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1124752767407206</v>
+        <v>0.1134277774153275</v>
       </c>
       <c r="T39">
-        <v>1.539844728423108</v>
+        <v>1.561842434534122</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.9182368028849</v>
+        <v>7.709862150177402</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4757,22 +4757,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08719912199750304</v>
+        <v>0.08736792964835213</v>
       </c>
       <c r="C40">
-        <v>47.19344858361027</v>
+        <v>46.39210879114806</v>
       </c>
       <c r="D40">
-        <v>60.76164858361027</v>
+        <v>60.70420879114806</v>
       </c>
       <c r="E40">
-        <v>26.6782</v>
+        <v>27.4221</v>
       </c>
       <c r="F40">
-        <v>28.2682</v>
+        <v>29.0121</v>
       </c>
       <c r="G40">
         <v>14.7</v>
@@ -4793,45 +4793,45 @@
         <v>11.66</v>
       </c>
       <c r="M40">
-        <v>1.5123487</v>
+        <v>1.57535703</v>
       </c>
       <c r="N40">
-        <v>10.1476513</v>
+        <v>10.08464297</v>
       </c>
       <c r="O40">
-        <v>1.725100721</v>
+        <v>1.7143893049</v>
       </c>
       <c r="P40">
-        <v>8.422550578999999</v>
+        <v>8.3702536651</v>
       </c>
       <c r="Q40">
-        <v>14.062550579</v>
+        <v>14.0102536651</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1134277774153275</v>
+        <v>0.1144115076202494</v>
       </c>
       <c r="T40">
-        <v>1.561842434534122</v>
+        <v>1.584561376911072</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.17</v>
       </c>
       <c r="W40">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.709862150177402</v>
+        <v>7.401496789588073</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4839,22 +4839,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08736792964835213</v>
+        <v>0.08728441729920124</v>
       </c>
       <c r="C41">
-        <v>46.39210879114806</v>
+        <v>45.67661176706844</v>
       </c>
       <c r="D41">
-        <v>60.70420879114806</v>
+        <v>60.73261176706843</v>
       </c>
       <c r="E41">
-        <v>27.4221</v>
+        <v>28.166</v>
       </c>
       <c r="F41">
-        <v>29.0121</v>
+        <v>29.756</v>
       </c>
       <c r="G41">
         <v>14.7</v>
@@ -4875,28 +4875,28 @@
         <v>11.66</v>
       </c>
       <c r="M41">
-        <v>1.57535703</v>
+        <v>1.6157508</v>
       </c>
       <c r="N41">
-        <v>10.08464297</v>
+        <v>10.0442492</v>
       </c>
       <c r="O41">
-        <v>1.7143893049</v>
+        <v>1.707522364</v>
       </c>
       <c r="P41">
-        <v>8.3702536651</v>
+        <v>8.336726835999999</v>
       </c>
       <c r="Q41">
-        <v>14.0102536651</v>
+        <v>13.976726836</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1144115076202494</v>
+        <v>0.1154280288320021</v>
       </c>
       <c r="T41">
-        <v>1.584561376911072</v>
+        <v>1.608037617367253</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.401496789588073</v>
+        <v>7.21645936984837</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4921,22 +4921,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08728441729920124</v>
+        <v>0.08720090495005034</v>
       </c>
       <c r="C42">
-        <v>45.67661176706844</v>
+        <v>44.96114133444582</v>
       </c>
       <c r="D42">
-        <v>60.73261176706843</v>
+        <v>60.76104133444583</v>
       </c>
       <c r="E42">
-        <v>28.166</v>
+        <v>28.9099</v>
       </c>
       <c r="F42">
-        <v>29.756</v>
+        <v>30.4999</v>
       </c>
       <c r="G42">
         <v>14.7</v>
@@ -4957,28 +4957,28 @@
         <v>11.66</v>
       </c>
       <c r="M42">
-        <v>1.6157508</v>
+        <v>1.65614457</v>
       </c>
       <c r="N42">
-        <v>10.0442492</v>
+        <v>10.00385543</v>
       </c>
       <c r="O42">
-        <v>1.707522364</v>
+        <v>1.7006554231</v>
       </c>
       <c r="P42">
-        <v>8.336726835999999</v>
+        <v>8.303200006899999</v>
       </c>
       <c r="Q42">
-        <v>13.976726836</v>
+        <v>13.9432000069</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1154280288320021</v>
+        <v>0.1164790083899158</v>
       </c>
       <c r="T42">
-        <v>1.608037617367253</v>
+        <v>1.632309662584661</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.21645936984837</v>
+        <v>7.040448165705726</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5003,22 +5003,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08720090495005034</v>
+        <v>0.08711739260089942</v>
       </c>
       <c r="C43">
-        <v>44.96114133444582</v>
+        <v>44.24569753064094</v>
       </c>
       <c r="D43">
-        <v>60.76104133444583</v>
+        <v>60.78949753064094</v>
       </c>
       <c r="E43">
-        <v>28.9099</v>
+        <v>29.6538</v>
       </c>
       <c r="F43">
-        <v>30.4999</v>
+        <v>31.2438</v>
       </c>
       <c r="G43">
         <v>14.7</v>
@@ -5039,28 +5039,28 @@
         <v>11.66</v>
       </c>
       <c r="M43">
-        <v>1.65614457</v>
+        <v>1.69653834</v>
       </c>
       <c r="N43">
-        <v>10.00385543</v>
+        <v>9.96346166</v>
       </c>
       <c r="O43">
-        <v>1.7006554231</v>
+        <v>1.6937884822</v>
       </c>
       <c r="P43">
-        <v>8.303200006899999</v>
+        <v>8.2696731778</v>
       </c>
       <c r="Q43">
-        <v>13.9432000069</v>
+        <v>13.9096731778</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1164790083899158</v>
+        <v>0.1175662286222404</v>
       </c>
       <c r="T43">
-        <v>1.632309662584661</v>
+        <v>1.657418674878531</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.040448165705726</v>
+        <v>6.872818447474637</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5085,22 +5085,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08711739260089943</v>
+        <v>0.08703388025174855</v>
       </c>
       <c r="C44">
-        <v>44.24569753064095</v>
+        <v>43.53028039308448</v>
       </c>
       <c r="D44">
-        <v>60.78949753064094</v>
+        <v>60.81798039308449</v>
       </c>
       <c r="E44">
-        <v>29.6538</v>
+        <v>30.3977</v>
       </c>
       <c r="F44">
-        <v>31.2438</v>
+        <v>31.9877</v>
       </c>
       <c r="G44">
         <v>14.7</v>
@@ -5121,28 +5121,28 @@
         <v>11.66</v>
       </c>
       <c r="M44">
-        <v>1.69653834</v>
+        <v>1.73693211</v>
       </c>
       <c r="N44">
-        <v>9.96346166</v>
+        <v>9.92306789</v>
       </c>
       <c r="O44">
-        <v>1.6937884822</v>
+        <v>1.6869215413</v>
       </c>
       <c r="P44">
-        <v>8.2696731778</v>
+        <v>8.2361463487</v>
       </c>
       <c r="Q44">
-        <v>13.9096731778</v>
+        <v>13.8761463487</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1175662286222404</v>
+        <v>0.1186915969328922</v>
       </c>
       <c r="T44">
-        <v>1.657418674878531</v>
+        <v>1.683408705147625</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.872818447474638</v>
+        <v>6.712985460324065</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5167,22 +5167,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08703388025174855</v>
+        <v>0.08695036790259764</v>
       </c>
       <c r="C45">
-        <v>43.53028039308448</v>
+        <v>42.81488995927739</v>
       </c>
       <c r="D45">
-        <v>60.81798039308449</v>
+        <v>60.8464899592774</v>
       </c>
       <c r="E45">
-        <v>30.3977</v>
+        <v>31.1416</v>
       </c>
       <c r="F45">
-        <v>31.9877</v>
+        <v>32.7316</v>
       </c>
       <c r="G45">
         <v>14.7</v>
@@ -5203,28 +5203,28 @@
         <v>11.66</v>
       </c>
       <c r="M45">
-        <v>1.73693211</v>
+        <v>1.77732588</v>
       </c>
       <c r="N45">
-        <v>9.92306789</v>
+        <v>9.882674120000001</v>
       </c>
       <c r="O45">
-        <v>1.6869215413</v>
+        <v>1.6800546004</v>
       </c>
       <c r="P45">
-        <v>8.2361463487</v>
+        <v>8.202619519600001</v>
       </c>
       <c r="Q45">
-        <v>13.8761463487</v>
+        <v>13.8426195196</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1186915969328922</v>
+        <v>0.1198571569689243</v>
       </c>
       <c r="T45">
-        <v>1.683408705147625</v>
+        <v>1.710326950783472</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.712985460324065</v>
+        <v>6.560417608953064</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5249,22 +5249,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08695036790259764</v>
+        <v>0.08686685555344671</v>
       </c>
       <c r="C46">
-        <v>42.81488995927739</v>
+        <v>42.09952626679092</v>
       </c>
       <c r="D46">
-        <v>60.8464899592774</v>
+        <v>60.87502626679093</v>
       </c>
       <c r="E46">
-        <v>31.1416</v>
+        <v>31.8855</v>
       </c>
       <c r="F46">
-        <v>32.7316</v>
+        <v>33.4755</v>
       </c>
       <c r="G46">
         <v>14.7</v>
@@ -5285,28 +5285,28 @@
         <v>11.66</v>
       </c>
       <c r="M46">
-        <v>1.77732588</v>
+        <v>1.81771965</v>
       </c>
       <c r="N46">
-        <v>9.882674120000001</v>
+        <v>9.842280349999999</v>
       </c>
       <c r="O46">
-        <v>1.6800546004</v>
+        <v>1.6731876595</v>
       </c>
       <c r="P46">
-        <v>8.202619519600001</v>
+        <v>8.169092690499999</v>
       </c>
       <c r="Q46">
-        <v>13.8426195196</v>
+        <v>13.8090926905</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1198571569689243</v>
+        <v>0.1210651010062667</v>
       </c>
       <c r="T46">
-        <v>1.710326950783472</v>
+        <v>1.738224041715168</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.560417608953064</v>
+        <v>6.414630550976328</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08686685555344671</v>
+        <v>0.08678334320429582</v>
       </c>
       <c r="C47">
-        <v>42.09952626679092</v>
+        <v>41.38418935326681</v>
       </c>
       <c r="D47">
-        <v>60.87502626679093</v>
+        <v>60.90358935326682</v>
       </c>
       <c r="E47">
-        <v>31.8855</v>
+        <v>32.6294</v>
       </c>
       <c r="F47">
-        <v>33.4755</v>
+        <v>34.2194</v>
       </c>
       <c r="G47">
         <v>14.7</v>
@@ -5367,28 +5367,28 @@
         <v>11.66</v>
       </c>
       <c r="M47">
-        <v>1.81771965</v>
+        <v>1.85811342</v>
       </c>
       <c r="N47">
-        <v>9.842280349999999</v>
+        <v>9.80188658</v>
       </c>
       <c r="O47">
-        <v>1.6731876595</v>
+        <v>1.6663207186</v>
       </c>
       <c r="P47">
-        <v>8.169092690499999</v>
+        <v>8.1355658614</v>
       </c>
       <c r="Q47">
-        <v>13.8090926905</v>
+        <v>13.7755658614</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1210651010062667</v>
+        <v>0.1223177837116589</v>
       </c>
       <c r="T47">
-        <v>1.738224041715168</v>
+        <v>1.767154358236926</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.414630550976328</v>
+        <v>6.275182060737713</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5413,22 +5413,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08678334320429582</v>
+        <v>0.08669983085514492</v>
       </c>
       <c r="C48">
-        <v>41.38418935326681</v>
+        <v>40.66887925641754</v>
       </c>
       <c r="D48">
-        <v>60.90358935326682</v>
+        <v>60.93217925641755</v>
       </c>
       <c r="E48">
-        <v>32.6294</v>
+        <v>33.3733</v>
       </c>
       <c r="F48">
-        <v>34.2194</v>
+        <v>34.9633</v>
       </c>
       <c r="G48">
         <v>14.7</v>
@@ -5449,28 +5449,28 @@
         <v>11.66</v>
       </c>
       <c r="M48">
-        <v>1.85811342</v>
+        <v>1.89850719</v>
       </c>
       <c r="N48">
-        <v>9.80188658</v>
+        <v>9.76149281</v>
       </c>
       <c r="O48">
-        <v>1.6663207186</v>
+        <v>1.6594537777</v>
       </c>
       <c r="P48">
-        <v>8.1355658614</v>
+        <v>8.1020390323</v>
       </c>
       <c r="Q48">
-        <v>13.7755658614</v>
+        <v>13.7420390323</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1223177837116589</v>
+        <v>0.1236177374625376</v>
       </c>
       <c r="T48">
-        <v>1.767154358236926</v>
+        <v>1.79717638481611</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.275182060737713</v>
+        <v>6.141667548807122</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5495,22 +5495,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08669983085514492</v>
+        <v>0.087014718505994</v>
       </c>
       <c r="C49">
-        <v>40.66887925641754</v>
+        <v>39.81731949549146</v>
       </c>
       <c r="D49">
-        <v>60.93217925641755</v>
+        <v>60.82451949549146</v>
       </c>
       <c r="E49">
-        <v>33.3733</v>
+        <v>34.1172</v>
       </c>
       <c r="F49">
-        <v>34.9633</v>
+        <v>35.7072</v>
       </c>
       <c r="G49">
         <v>14.7</v>
@@ -5531,45 +5531,45 @@
         <v>11.66</v>
       </c>
       <c r="M49">
-        <v>1.89850719</v>
+        <v>1.97460816</v>
       </c>
       <c r="N49">
-        <v>9.76149281</v>
+        <v>9.685391839999999</v>
       </c>
       <c r="O49">
-        <v>1.6594537777</v>
+        <v>1.6465166128</v>
       </c>
       <c r="P49">
-        <v>8.1020390323</v>
+        <v>8.0388752272</v>
       </c>
       <c r="Q49">
-        <v>13.7420390323</v>
+        <v>13.6788752272</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1236177374625376</v>
+        <v>0.1249676894346038</v>
       </c>
       <c r="T49">
-        <v>1.79717638481611</v>
+        <v>1.828353104725262</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.17</v>
       </c>
       <c r="W49">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.141667548807122</v>
+        <v>5.904969014206848</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5577,22 +5577,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.087014718505994</v>
+        <v>0.08693950615684311</v>
       </c>
       <c r="C50">
-        <v>39.81731949549146</v>
+        <v>39.09909992209325</v>
       </c>
       <c r="D50">
-        <v>60.82451949549146</v>
+        <v>60.85019992209324</v>
       </c>
       <c r="E50">
-        <v>34.1172</v>
+        <v>34.86109999999999</v>
       </c>
       <c r="F50">
-        <v>35.7072</v>
+        <v>36.4511</v>
       </c>
       <c r="G50">
         <v>14.7</v>
@@ -5613,28 +5613,28 @@
         <v>11.66</v>
       </c>
       <c r="M50">
-        <v>1.97460816</v>
+        <v>2.01574583</v>
       </c>
       <c r="N50">
-        <v>9.685391839999999</v>
+        <v>9.64425417</v>
       </c>
       <c r="O50">
-        <v>1.6465166128</v>
+        <v>1.6395232089</v>
       </c>
       <c r="P50">
-        <v>8.0388752272</v>
+        <v>8.0047309611</v>
       </c>
       <c r="Q50">
-        <v>13.6788752272</v>
+        <v>13.6447309611</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1249676894346038</v>
+        <v>0.1263705806996923</v>
       </c>
       <c r="T50">
-        <v>1.828353104725262</v>
+        <v>1.86075244110144</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.904969014206848</v>
+        <v>5.784459442488343</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5659,22 +5659,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08693950615684311</v>
+        <v>0.0868642938076922</v>
       </c>
       <c r="C51">
-        <v>39.09909992209325</v>
+        <v>38.38090204267208</v>
       </c>
       <c r="D51">
-        <v>60.85019992209324</v>
+        <v>60.87590204267208</v>
       </c>
       <c r="E51">
-        <v>34.86109999999999</v>
+        <v>35.605</v>
       </c>
       <c r="F51">
-        <v>36.4511</v>
+        <v>37.195</v>
       </c>
       <c r="G51">
         <v>14.7</v>
@@ -5695,28 +5695,28 @@
         <v>11.66</v>
       </c>
       <c r="M51">
-        <v>2.01574583</v>
+        <v>2.0568835</v>
       </c>
       <c r="N51">
-        <v>9.64425417</v>
+        <v>9.6031165</v>
       </c>
       <c r="O51">
-        <v>1.6395232089</v>
+        <v>1.632529805</v>
       </c>
       <c r="P51">
-        <v>8.0047309611</v>
+        <v>7.970586695000001</v>
       </c>
       <c r="Q51">
-        <v>13.6447309611</v>
+        <v>13.610586695</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1263705806996923</v>
+        <v>0.1278295876153844</v>
       </c>
       <c r="T51">
-        <v>1.86075244110144</v>
+        <v>1.894447750932665</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.784459442488343</v>
+        <v>5.668770253638575</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5741,22 +5741,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0868642938076922</v>
+        <v>0.08678908145854131</v>
       </c>
       <c r="C52">
-        <v>38.38090204267208</v>
+        <v>37.66272588472914</v>
       </c>
       <c r="D52">
-        <v>60.87590204267208</v>
+        <v>60.90162588472915</v>
       </c>
       <c r="E52">
-        <v>35.605</v>
+        <v>36.3489</v>
       </c>
       <c r="F52">
-        <v>37.195</v>
+        <v>37.9389</v>
       </c>
       <c r="G52">
         <v>14.7</v>
@@ -5777,28 +5777,28 @@
         <v>11.66</v>
       </c>
       <c r="M52">
-        <v>2.0568835</v>
+        <v>2.09802117</v>
       </c>
       <c r="N52">
-        <v>9.6031165</v>
+        <v>9.561978829999999</v>
       </c>
       <c r="O52">
-        <v>1.632529805</v>
+        <v>1.6255364011</v>
       </c>
       <c r="P52">
-        <v>7.970586695000001</v>
+        <v>7.9364424289</v>
       </c>
       <c r="Q52">
-        <v>13.610586695</v>
+        <v>13.5764424289</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1278295876153844</v>
+        <v>0.1293481458337578</v>
       </c>
       <c r="T52">
-        <v>1.894447750932665</v>
+        <v>1.929518379532511</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.668770253638575</v>
+        <v>5.557617895724092</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5823,22 +5823,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08678908145854131</v>
+        <v>0.08671386910939038</v>
       </c>
       <c r="C53">
-        <v>37.66272588472914</v>
+        <v>36.9445714758121</v>
       </c>
       <c r="D53">
-        <v>60.90162588472915</v>
+        <v>60.9273714758121</v>
       </c>
       <c r="E53">
-        <v>36.3489</v>
+        <v>37.0928</v>
       </c>
       <c r="F53">
-        <v>37.9389</v>
+        <v>38.6828</v>
       </c>
       <c r="G53">
         <v>14.7</v>
@@ -5859,28 +5859,28 @@
         <v>11.66</v>
       </c>
       <c r="M53">
-        <v>2.09802117</v>
+        <v>2.13915884</v>
       </c>
       <c r="N53">
-        <v>9.561978829999999</v>
+        <v>9.52084116</v>
       </c>
       <c r="O53">
-        <v>1.6255364011</v>
+        <v>1.6185429972</v>
       </c>
       <c r="P53">
-        <v>7.9364424289</v>
+        <v>7.902298162799999</v>
       </c>
       <c r="Q53">
-        <v>13.5764424289</v>
+        <v>13.5422981628</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1293481458337578</v>
+        <v>0.13092997731123</v>
       </c>
       <c r="T53">
-        <v>1.929518379532511</v>
+        <v>1.966050284324018</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.557617895724092</v>
+        <v>5.45074062849863</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5905,22 +5905,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08671386910939038</v>
+        <v>0.08663865676023949</v>
       </c>
       <c r="C54">
-        <v>36.9445714758121</v>
+        <v>36.22643884351516</v>
       </c>
       <c r="D54">
-        <v>60.9273714758121</v>
+        <v>60.95313884351517</v>
       </c>
       <c r="E54">
-        <v>37.0928</v>
+        <v>37.8367</v>
       </c>
       <c r="F54">
-        <v>38.6828</v>
+        <v>39.4267</v>
       </c>
       <c r="G54">
         <v>14.7</v>
@@ -5941,28 +5941,28 @@
         <v>11.66</v>
       </c>
       <c r="M54">
-        <v>2.13915884</v>
+        <v>2.18029651</v>
       </c>
       <c r="N54">
-        <v>9.52084116</v>
+        <v>9.47970349</v>
       </c>
       <c r="O54">
-        <v>1.6185429972</v>
+        <v>1.6115495933</v>
       </c>
       <c r="P54">
-        <v>7.902298162799999</v>
+        <v>7.8681538967</v>
       </c>
       <c r="Q54">
-        <v>13.5422981628</v>
+        <v>13.5081538967</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.13092997731123</v>
+        <v>0.132579120766467</v>
       </c>
       <c r="T54">
-        <v>1.966050284324018</v>
+        <v>2.004136738255589</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.45074062849863</v>
+        <v>5.347896465696769</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5987,22 +5987,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08663865676023949</v>
+        <v>0.08656344441108857</v>
       </c>
       <c r="C55">
-        <v>36.22643884351516</v>
+        <v>35.50832801547934</v>
       </c>
       <c r="D55">
-        <v>60.95313884351517</v>
+        <v>60.97892801547935</v>
       </c>
       <c r="E55">
-        <v>37.8367</v>
+        <v>38.5806</v>
       </c>
       <c r="F55">
-        <v>39.4267</v>
+        <v>40.1706</v>
       </c>
       <c r="G55">
         <v>14.7</v>
@@ -6023,28 +6023,28 @@
         <v>11.66</v>
       </c>
       <c r="M55">
-        <v>2.18029651</v>
+        <v>2.22143418</v>
       </c>
       <c r="N55">
-        <v>9.47970349</v>
+        <v>9.438565820000001</v>
       </c>
       <c r="O55">
-        <v>1.6115495933</v>
+        <v>1.6045561894</v>
       </c>
       <c r="P55">
-        <v>7.8681538967</v>
+        <v>7.834009630600001</v>
       </c>
       <c r="Q55">
-        <v>13.5081538967</v>
+        <v>13.4740096306</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.132579120766467</v>
+        <v>0.1342999661110621</v>
       </c>
       <c r="T55">
-        <v>2.004136738255589</v>
+        <v>2.043879124966793</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.347896465696769</v>
+        <v>5.248861345961644</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6069,22 +6069,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08656344441108857</v>
+        <v>0.08648823206193769</v>
       </c>
       <c r="C56">
-        <v>35.50832801547934</v>
+        <v>34.79023901939235</v>
       </c>
       <c r="D56">
-        <v>60.97892801547935</v>
+        <v>61.00473901939235</v>
       </c>
       <c r="E56">
-        <v>38.5806</v>
+        <v>39.3245</v>
       </c>
       <c r="F56">
-        <v>40.1706</v>
+        <v>40.9145</v>
       </c>
       <c r="G56">
         <v>14.7</v>
@@ -6105,28 +6105,28 @@
         <v>11.66</v>
       </c>
       <c r="M56">
-        <v>2.22143418</v>
+        <v>2.26257185</v>
       </c>
       <c r="N56">
-        <v>9.438565820000001</v>
+        <v>9.39742815</v>
       </c>
       <c r="O56">
-        <v>1.6045561894</v>
+        <v>1.5975627855</v>
       </c>
       <c r="P56">
-        <v>7.834009630600001</v>
+        <v>7.7998653645</v>
       </c>
       <c r="Q56">
-        <v>13.4740096306</v>
+        <v>13.4398653645</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1342999661110621</v>
+        <v>0.1360972934709727</v>
       </c>
       <c r="T56">
-        <v>2.043879124966793</v>
+        <v>2.085387839976274</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.248861345961644</v>
+        <v>5.153427503307794</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6151,22 +6151,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08648823206193769</v>
+        <v>0.08641301971278678</v>
       </c>
       <c r="C57">
-        <v>34.79023901939235</v>
+        <v>34.07217188298885</v>
       </c>
       <c r="D57">
-        <v>61.00473901939235</v>
+        <v>61.03057188298886</v>
       </c>
       <c r="E57">
-        <v>39.3245</v>
+        <v>40.0684</v>
       </c>
       <c r="F57">
-        <v>40.9145</v>
+        <v>41.65840000000001</v>
       </c>
       <c r="G57">
         <v>14.7</v>
@@ -6187,28 +6187,28 @@
         <v>11.66</v>
       </c>
       <c r="M57">
-        <v>2.26257185</v>
+        <v>2.30370952</v>
       </c>
       <c r="N57">
-        <v>9.39742815</v>
+        <v>9.35629048</v>
       </c>
       <c r="O57">
-        <v>1.5975627855</v>
+        <v>1.5905693816</v>
       </c>
       <c r="P57">
-        <v>7.7998653645</v>
+        <v>7.7657210984</v>
       </c>
       <c r="Q57">
-        <v>13.4398653645</v>
+        <v>13.4057210984</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1360972934709727</v>
+        <v>0.1379763175290609</v>
       </c>
       <c r="T57">
-        <v>2.085387839976274</v>
+        <v>2.128783314758912</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.153427503307794</v>
+        <v>5.061402012177298</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6233,22 +6233,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08641301971278678</v>
+        <v>0.08633780736363587</v>
       </c>
       <c r="C58">
-        <v>34.07217188298885</v>
+        <v>33.35412663405052</v>
       </c>
       <c r="D58">
-        <v>61.03057188298886</v>
+        <v>61.05642663405052</v>
       </c>
       <c r="E58">
-        <v>40.0684</v>
+        <v>40.8123</v>
       </c>
       <c r="F58">
-        <v>41.65840000000001</v>
+        <v>42.4023</v>
       </c>
       <c r="G58">
         <v>14.7</v>
@@ -6269,28 +6269,28 @@
         <v>11.66</v>
       </c>
       <c r="M58">
-        <v>2.30370952</v>
+        <v>2.34484719</v>
       </c>
       <c r="N58">
-        <v>9.35629048</v>
+        <v>9.315152810000001</v>
       </c>
       <c r="O58">
-        <v>1.5905693816</v>
+        <v>1.5835759777</v>
       </c>
       <c r="P58">
-        <v>7.7657210984</v>
+        <v>7.7315768323</v>
       </c>
       <c r="Q58">
-        <v>13.4057210984</v>
+        <v>13.3715768323</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1379763175290609</v>
+        <v>0.1399427380549672</v>
       </c>
       <c r="T58">
-        <v>2.128783314758912</v>
+        <v>2.174197183717486</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.061402012177298</v>
+        <v>4.972605485647873</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6315,22 +6315,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08633780736363587</v>
+        <v>0.08626259501448497</v>
       </c>
       <c r="C59">
-        <v>33.35412663405052</v>
+        <v>32.63610330040606</v>
       </c>
       <c r="D59">
-        <v>61.05642663405052</v>
+        <v>61.08230330040607</v>
       </c>
       <c r="E59">
-        <v>40.8123</v>
+        <v>41.5562</v>
       </c>
       <c r="F59">
-        <v>42.4023</v>
+        <v>43.14620000000001</v>
       </c>
       <c r="G59">
         <v>14.7</v>
@@ -6351,28 +6351,28 @@
         <v>11.66</v>
       </c>
       <c r="M59">
-        <v>2.34484719</v>
+        <v>2.385984860000001</v>
       </c>
       <c r="N59">
-        <v>9.315152810000001</v>
+        <v>9.274015139999999</v>
       </c>
       <c r="O59">
-        <v>1.5835759777</v>
+        <v>1.5765825738</v>
       </c>
       <c r="P59">
-        <v>7.7315768323</v>
+        <v>7.6974325662</v>
       </c>
       <c r="Q59">
-        <v>13.3715768323</v>
+        <v>13.3374325662</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1399427380549672</v>
+        <v>0.1420027976535357</v>
       </c>
       <c r="T59">
-        <v>2.174197183717486</v>
+        <v>2.221773617864565</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.972605485647873</v>
+        <v>4.886870908309115</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08626259501448498</v>
+        <v>0.08618738266533407</v>
       </c>
       <c r="C60">
-        <v>32.63610330040607</v>
+        <v>31.91810190993146</v>
       </c>
       <c r="D60">
-        <v>61.08230330040607</v>
+        <v>61.10820190993146</v>
       </c>
       <c r="E60">
-        <v>41.5562</v>
+        <v>42.30009999999999</v>
       </c>
       <c r="F60">
-        <v>43.1462</v>
+        <v>43.8901</v>
       </c>
       <c r="G60">
         <v>14.7</v>
@@ -6433,28 +6433,28 @@
         <v>11.66</v>
       </c>
       <c r="M60">
-        <v>2.38598486</v>
+        <v>2.42712253</v>
       </c>
       <c r="N60">
-        <v>9.274015139999999</v>
+        <v>9.23287747</v>
       </c>
       <c r="O60">
-        <v>1.5765825738</v>
+        <v>1.5695891699</v>
       </c>
       <c r="P60">
-        <v>7.6974325662</v>
+        <v>7.6632883001</v>
       </c>
       <c r="Q60">
-        <v>13.3374325662</v>
+        <v>13.3032883001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1420027976535357</v>
+        <v>0.1441633479642294</v>
       </c>
       <c r="T60">
-        <v>2.221773617864565</v>
+        <v>2.271670853677354</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.886870908309116</v>
+        <v>4.804042587829301</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6479,22 +6479,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08618738266533407</v>
+        <v>0.08611217031618316</v>
       </c>
       <c r="C61">
-        <v>31.91810190993146</v>
+        <v>31.20012249054993</v>
       </c>
       <c r="D61">
-        <v>61.10820190993146</v>
+        <v>61.13412249054993</v>
       </c>
       <c r="E61">
-        <v>42.30009999999999</v>
+        <v>43.044</v>
       </c>
       <c r="F61">
-        <v>43.8901</v>
+        <v>44.634</v>
       </c>
       <c r="G61">
         <v>14.7</v>
@@ -6515,28 +6515,28 @@
         <v>11.66</v>
       </c>
       <c r="M61">
-        <v>2.42712253</v>
+        <v>2.4682602</v>
       </c>
       <c r="N61">
-        <v>9.23287747</v>
+        <v>9.191739800000001</v>
       </c>
       <c r="O61">
-        <v>1.5695891699</v>
+        <v>1.562595766</v>
       </c>
       <c r="P61">
-        <v>7.6632883001</v>
+        <v>7.629144034</v>
       </c>
       <c r="Q61">
-        <v>13.3032883001</v>
+        <v>13.269144034</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1441633479642294</v>
+        <v>0.1464319257904579</v>
       </c>
       <c r="T61">
-        <v>2.271670853677354</v>
+        <v>2.324062951280783</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.804042587829301</v>
+        <v>4.723975211365479</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6561,22 +6561,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08611217031618316</v>
+        <v>0.08603695796703227</v>
       </c>
       <c r="C62">
-        <v>31.20012249054993</v>
+        <v>30.48216507023213</v>
       </c>
       <c r="D62">
-        <v>61.13412249054993</v>
+        <v>61.16006507023212</v>
       </c>
       <c r="E62">
-        <v>43.044</v>
+        <v>43.78789999999999</v>
       </c>
       <c r="F62">
-        <v>44.634</v>
+        <v>45.3779</v>
       </c>
       <c r="G62">
         <v>14.7</v>
@@ -6597,28 +6597,28 @@
         <v>11.66</v>
       </c>
       <c r="M62">
-        <v>2.4682602</v>
+        <v>2.50939787</v>
       </c>
       <c r="N62">
-        <v>9.191739800000001</v>
+        <v>9.150602129999999</v>
       </c>
       <c r="O62">
-        <v>1.562595766</v>
+        <v>1.5556023621</v>
       </c>
       <c r="P62">
-        <v>7.629144034</v>
+        <v>7.594999767899999</v>
       </c>
       <c r="Q62">
-        <v>13.269144034</v>
+        <v>13.2349997679</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1464319257904579</v>
+        <v>0.1488168409411084</v>
       </c>
       <c r="T62">
-        <v>2.324062951280783</v>
+        <v>2.379141823120285</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.723975211365479</v>
+        <v>4.646532994785717</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6643,22 +6643,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08603695796703227</v>
+        <v>0.08596174561788136</v>
       </c>
       <c r="C63">
-        <v>30.48216507023213</v>
+        <v>29.76422967699617</v>
       </c>
       <c r="D63">
-        <v>61.16006507023212</v>
+        <v>61.18602967699618</v>
       </c>
       <c r="E63">
-        <v>43.78789999999999</v>
+        <v>44.5318</v>
       </c>
       <c r="F63">
-        <v>45.3779</v>
+        <v>46.1218</v>
       </c>
       <c r="G63">
         <v>14.7</v>
@@ -6679,28 +6679,28 @@
         <v>11.66</v>
       </c>
       <c r="M63">
-        <v>2.50939787</v>
+        <v>2.55053554</v>
       </c>
       <c r="N63">
-        <v>9.150602129999999</v>
+        <v>9.10946446</v>
       </c>
       <c r="O63">
-        <v>1.5556023621</v>
+        <v>1.5486089582</v>
       </c>
       <c r="P63">
-        <v>7.594999767899999</v>
+        <v>7.5608555018</v>
       </c>
       <c r="Q63">
-        <v>13.2349997679</v>
+        <v>13.2008555018</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1488168409411084</v>
+        <v>0.151327277941793</v>
       </c>
       <c r="T63">
-        <v>2.379141823120285</v>
+        <v>2.437119582951341</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.646532994785717</v>
+        <v>4.571588914224657</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6725,22 +6725,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08596174561788136</v>
+        <v>0.08719378326873045</v>
       </c>
       <c r="C64">
-        <v>29.76422967699617</v>
+        <v>28.59776695393734</v>
       </c>
       <c r="D64">
-        <v>61.18602967699618</v>
+        <v>60.76346695393734</v>
       </c>
       <c r="E64">
-        <v>44.5318</v>
+        <v>45.2757</v>
       </c>
       <c r="F64">
-        <v>46.1218</v>
+        <v>46.8657</v>
       </c>
       <c r="G64">
         <v>14.7</v>
@@ -6761,45 +6761,45 @@
         <v>11.66</v>
       </c>
       <c r="M64">
-        <v>2.55053554</v>
+        <v>2.70883746</v>
       </c>
       <c r="N64">
-        <v>9.10946446</v>
+        <v>8.95116254</v>
       </c>
       <c r="O64">
-        <v>1.5486089582</v>
+        <v>1.5216976318</v>
       </c>
       <c r="P64">
-        <v>7.5608555018</v>
+        <v>7.4294649082</v>
       </c>
       <c r="Q64">
-        <v>13.2008555018</v>
+        <v>13.0694649082</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.151327277941793</v>
+        <v>0.153973414239812</v>
       </c>
       <c r="T64">
-        <v>2.437119582951341</v>
+        <v>2.498231275746236</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.17</v>
       </c>
       <c r="W64">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.571588914224657</v>
+        <v>4.304429546688269</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6807,22 +6807,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08719378326873045</v>
+        <v>0.08713932091957954</v>
       </c>
       <c r="C65">
-        <v>28.59776695393734</v>
+        <v>27.87242304309029</v>
       </c>
       <c r="D65">
-        <v>60.76346695393734</v>
+        <v>60.78202304309029</v>
       </c>
       <c r="E65">
-        <v>45.2757</v>
+        <v>46.0196</v>
       </c>
       <c r="F65">
-        <v>46.8657</v>
+        <v>47.6096</v>
       </c>
       <c r="G65">
         <v>14.7</v>
@@ -6843,28 +6843,28 @@
         <v>11.66</v>
       </c>
       <c r="M65">
-        <v>2.70883746</v>
+        <v>2.75183488</v>
       </c>
       <c r="N65">
-        <v>8.95116254</v>
+        <v>8.90816512</v>
       </c>
       <c r="O65">
-        <v>1.5216976318</v>
+        <v>1.5143880704</v>
       </c>
       <c r="P65">
-        <v>7.4294649082</v>
+        <v>7.3937770496</v>
       </c>
       <c r="Q65">
-        <v>13.0694649082</v>
+        <v>13.0337770496</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.153973414239812</v>
+        <v>0.1567665581099432</v>
       </c>
       <c r="T65">
-        <v>2.498231275746236</v>
+        <v>2.562738062585293</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.304429546688269</v>
+        <v>4.237172835021264</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6889,22 +6889,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08713932091957954</v>
+        <v>0.08708485857042865</v>
       </c>
       <c r="C66">
-        <v>27.87242304309029</v>
+        <v>27.14709046910883</v>
       </c>
       <c r="D66">
-        <v>60.78202304309029</v>
+        <v>60.80059046910883</v>
       </c>
       <c r="E66">
-        <v>46.0196</v>
+        <v>46.7635</v>
       </c>
       <c r="F66">
-        <v>47.6096</v>
+        <v>48.3535</v>
       </c>
       <c r="G66">
         <v>14.7</v>
@@ -6925,28 +6925,28 @@
         <v>11.66</v>
       </c>
       <c r="M66">
-        <v>2.75183488</v>
+        <v>2.7948323</v>
       </c>
       <c r="N66">
-        <v>8.90816512</v>
+        <v>8.865167700000001</v>
       </c>
       <c r="O66">
-        <v>1.5143880704</v>
+        <v>1.507078509</v>
       </c>
       <c r="P66">
-        <v>7.3937770496</v>
+        <v>7.358089191</v>
       </c>
       <c r="Q66">
-        <v>13.0337770496</v>
+        <v>12.998089191</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1567665581099432</v>
+        <v>0.1597193102012247</v>
       </c>
       <c r="T66">
-        <v>2.562738062585293</v>
+        <v>2.630930951529439</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.237172835021264</v>
+        <v>4.171985560636321</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6971,22 +6971,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08708485857042865</v>
+        <v>0.08703039622127776</v>
       </c>
       <c r="C67">
-        <v>27.14709046910883</v>
+        <v>26.42176924238552</v>
       </c>
       <c r="D67">
-        <v>60.80059046910883</v>
+        <v>60.81916924238552</v>
       </c>
       <c r="E67">
-        <v>46.7635</v>
+        <v>47.5074</v>
       </c>
       <c r="F67">
-        <v>48.3535</v>
+        <v>49.0974</v>
       </c>
       <c r="G67">
         <v>14.7</v>
@@ -7007,28 +7007,28 @@
         <v>11.66</v>
       </c>
       <c r="M67">
-        <v>2.7948323</v>
+        <v>2.83782972</v>
       </c>
       <c r="N67">
-        <v>8.865167700000001</v>
+        <v>8.82217028</v>
       </c>
       <c r="O67">
-        <v>1.507078509</v>
+        <v>1.4997689476</v>
       </c>
       <c r="P67">
-        <v>7.358089191</v>
+        <v>7.3224013324</v>
       </c>
       <c r="Q67">
-        <v>12.998089191</v>
+        <v>12.9624013324</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1597193102012247</v>
+        <v>0.1628457535919934</v>
       </c>
       <c r="T67">
-        <v>2.630930951529439</v>
+        <v>2.703135186882064</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.171985560636321</v>
+        <v>4.108773658202438</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7053,22 +7053,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08703039622127776</v>
+        <v>0.08697593387212685</v>
       </c>
       <c r="C68">
-        <v>26.42176924238552</v>
+        <v>25.69645937332567</v>
       </c>
       <c r="D68">
-        <v>60.81916924238552</v>
+        <v>60.83775937332567</v>
       </c>
       <c r="E68">
-        <v>47.5074</v>
+        <v>48.2513</v>
       </c>
       <c r="F68">
-        <v>49.0974</v>
+        <v>49.8413</v>
       </c>
       <c r="G68">
         <v>14.7</v>
@@ -7089,28 +7089,28 @@
         <v>11.66</v>
       </c>
       <c r="M68">
-        <v>2.83782972</v>
+        <v>2.880827140000001</v>
       </c>
       <c r="N68">
-        <v>8.82217028</v>
+        <v>8.779172859999999</v>
       </c>
       <c r="O68">
-        <v>1.4997689476</v>
+        <v>1.4924593862</v>
       </c>
       <c r="P68">
-        <v>7.3224013324</v>
+        <v>7.286713473799999</v>
       </c>
       <c r="Q68">
-        <v>12.9624013324</v>
+        <v>12.9267134738</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1628457535919934</v>
+        <v>0.1661616784003844</v>
       </c>
       <c r="T68">
-        <v>2.703135186882064</v>
+        <v>2.779715436498484</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.108773658202438</v>
+        <v>4.047448678229266</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7135,22 +7135,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08697593387212685</v>
+        <v>0.08889687152297593</v>
       </c>
       <c r="C69">
-        <v>25.69645937332567</v>
+        <v>24.30366350784615</v>
       </c>
       <c r="D69">
-        <v>60.83775937332567</v>
+        <v>60.18886350784615</v>
       </c>
       <c r="E69">
-        <v>48.2513</v>
+        <v>48.9952</v>
       </c>
       <c r="F69">
-        <v>49.8413</v>
+        <v>50.58520000000001</v>
       </c>
       <c r="G69">
         <v>14.7</v>
@@ -7171,45 +7171,45 @@
         <v>11.66</v>
       </c>
       <c r="M69">
-        <v>2.880827140000001</v>
+        <v>3.100872760000001</v>
       </c>
       <c r="N69">
-        <v>8.779172859999999</v>
+        <v>8.559127239999999</v>
       </c>
       <c r="O69">
-        <v>1.4924593862</v>
+        <v>1.4550516308</v>
       </c>
       <c r="P69">
-        <v>7.286713473799999</v>
+        <v>7.104075609199999</v>
       </c>
       <c r="Q69">
-        <v>12.9267134738</v>
+        <v>12.7440756092</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1661616784003844</v>
+        <v>0.1696848485092998</v>
       </c>
       <c r="T69">
-        <v>2.779715436498484</v>
+        <v>2.861081951715931</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.17</v>
       </c>
       <c r="W69">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.047448678229266</v>
+        <v>3.760231683934041</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7217,22 +7217,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08889687152297593</v>
+        <v>0.08887145917382502</v>
       </c>
       <c r="C70">
-        <v>24.30366350784615</v>
+        <v>23.56825747873335</v>
       </c>
       <c r="D70">
-        <v>60.18886350784615</v>
+        <v>60.19735747873335</v>
       </c>
       <c r="E70">
-        <v>48.9952</v>
+        <v>49.7391</v>
       </c>
       <c r="F70">
-        <v>50.58520000000001</v>
+        <v>51.3291</v>
       </c>
       <c r="G70">
         <v>14.7</v>
@@ -7253,28 +7253,28 @@
         <v>11.66</v>
       </c>
       <c r="M70">
-        <v>3.100872760000001</v>
+        <v>3.14647383</v>
       </c>
       <c r="N70">
-        <v>8.559127239999999</v>
+        <v>8.51352617</v>
       </c>
       <c r="O70">
-        <v>1.4550516308</v>
+        <v>1.4472994489</v>
       </c>
       <c r="P70">
-        <v>7.104075609199999</v>
+        <v>7.0662267211</v>
       </c>
       <c r="Q70">
-        <v>12.7440756092</v>
+        <v>12.7062267211</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1696848485092998</v>
+        <v>0.1734353199155646</v>
       </c>
       <c r="T70">
-        <v>2.861081951715931</v>
+        <v>2.947697919528052</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.760231683934041</v>
+        <v>3.705735572572679</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7299,22 +7299,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08887145917382502</v>
+        <v>0.08884604682467412</v>
       </c>
       <c r="C71">
-        <v>23.56825747873335</v>
+        <v>22.83285384733068</v>
       </c>
       <c r="D71">
-        <v>60.19735747873335</v>
+        <v>60.20585384733069</v>
       </c>
       <c r="E71">
-        <v>49.7391</v>
+        <v>50.483</v>
       </c>
       <c r="F71">
-        <v>51.3291</v>
+        <v>52.07300000000001</v>
       </c>
       <c r="G71">
         <v>14.7</v>
@@ -7335,28 +7335,28 @@
         <v>11.66</v>
       </c>
       <c r="M71">
-        <v>3.14647383</v>
+        <v>3.192074900000001</v>
       </c>
       <c r="N71">
-        <v>8.51352617</v>
+        <v>8.467925099999999</v>
       </c>
       <c r="O71">
-        <v>1.4472994489</v>
+        <v>1.439547267</v>
       </c>
       <c r="P71">
-        <v>7.0662267211</v>
+        <v>7.028377832999999</v>
       </c>
       <c r="Q71">
-        <v>12.7062267211</v>
+        <v>12.668377833</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1734353199155646</v>
+        <v>0.1774358227489138</v>
       </c>
       <c r="T71">
-        <v>2.947697919528052</v>
+        <v>3.040088285194313</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.705735572572679</v>
+        <v>3.652796492964497</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7381,22 +7381,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08884604682467412</v>
+        <v>0.08882063447552323</v>
       </c>
       <c r="C72">
-        <v>22.83285384733068</v>
+        <v>22.09745261465358</v>
       </c>
       <c r="D72">
-        <v>60.20585384733069</v>
+        <v>60.21435261465358</v>
       </c>
       <c r="E72">
-        <v>50.483</v>
+        <v>51.2269</v>
       </c>
       <c r="F72">
-        <v>52.07300000000001</v>
+        <v>52.8169</v>
       </c>
       <c r="G72">
         <v>14.7</v>
@@ -7417,28 +7417,28 @@
         <v>11.66</v>
       </c>
       <c r="M72">
-        <v>3.192074900000001</v>
+        <v>3.23767597</v>
       </c>
       <c r="N72">
-        <v>8.467925099999999</v>
+        <v>8.42232403</v>
       </c>
       <c r="O72">
-        <v>1.439547267</v>
+        <v>1.4317950851</v>
       </c>
       <c r="P72">
-        <v>7.028377832999999</v>
+        <v>6.9905289449</v>
       </c>
       <c r="Q72">
-        <v>12.668377833</v>
+        <v>12.6305289449</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1774358227489138</v>
+        <v>0.1817122223293905</v>
       </c>
       <c r="T72">
-        <v>3.040088285194313</v>
+        <v>3.13885040021687</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.652796492964497</v>
+        <v>3.60134865503542</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7463,22 +7463,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08882063447552321</v>
+        <v>0.08879522212637232</v>
       </c>
       <c r="C73">
-        <v>22.0974526146536</v>
+        <v>21.36205378171799</v>
       </c>
       <c r="D73">
-        <v>60.2143526146536</v>
+        <v>60.22285378171799</v>
       </c>
       <c r="E73">
-        <v>51.22689999999999</v>
+        <v>51.9708</v>
       </c>
       <c r="F73">
-        <v>52.8169</v>
+        <v>53.5608</v>
       </c>
       <c r="G73">
         <v>14.7</v>
@@ -7499,28 +7499,28 @@
         <v>11.66</v>
       </c>
       <c r="M73">
-        <v>3.23767597</v>
+        <v>3.28327704</v>
       </c>
       <c r="N73">
-        <v>8.42232403</v>
+        <v>8.37672296</v>
       </c>
       <c r="O73">
-        <v>1.4317950851</v>
+        <v>1.4240429032</v>
       </c>
       <c r="P73">
-        <v>6.9905289449</v>
+        <v>6.9526800568</v>
       </c>
       <c r="Q73">
-        <v>12.6305289449</v>
+        <v>12.5926800568</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1817122223293904</v>
+        <v>0.1862940790227583</v>
       </c>
       <c r="T73">
-        <v>3.138850400216869</v>
+        <v>3.24466695202675</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.601348655035421</v>
+        <v>3.551329923715484</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7545,22 +7545,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08879522212637232</v>
+        <v>0.08876980977722142</v>
       </c>
       <c r="C74">
-        <v>21.36205378171799</v>
+        <v>20.62665734954047</v>
       </c>
       <c r="D74">
-        <v>60.22285378171799</v>
+        <v>60.23135734954046</v>
       </c>
       <c r="E74">
-        <v>51.9708</v>
+        <v>52.71469999999999</v>
       </c>
       <c r="F74">
-        <v>53.5608</v>
+        <v>54.3047</v>
       </c>
       <c r="G74">
         <v>14.7</v>
@@ -7581,28 +7581,28 @@
         <v>11.66</v>
       </c>
       <c r="M74">
-        <v>3.28327704</v>
+        <v>3.32887811</v>
       </c>
       <c r="N74">
-        <v>8.37672296</v>
+        <v>8.33112189</v>
       </c>
       <c r="O74">
-        <v>1.4240429032</v>
+        <v>1.4162907213</v>
       </c>
       <c r="P74">
-        <v>6.9526800568</v>
+        <v>6.9148311687</v>
       </c>
       <c r="Q74">
-        <v>12.5926800568</v>
+        <v>12.5548311687</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1862940790227583</v>
+        <v>0.1912153325082274</v>
       </c>
       <c r="T74">
-        <v>3.24466695202675</v>
+        <v>3.358321766933659</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.551329923715484</v>
+        <v>3.502681568596094</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7627,22 +7627,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08876980977722142</v>
+        <v>0.09046415742807051</v>
       </c>
       <c r="C75">
-        <v>20.62665734954047</v>
+        <v>19.32099753583764</v>
       </c>
       <c r="D75">
-        <v>60.23135734954046</v>
+        <v>59.66959753583764</v>
       </c>
       <c r="E75">
-        <v>52.71469999999999</v>
+        <v>53.4586</v>
       </c>
       <c r="F75">
-        <v>54.3047</v>
+        <v>55.0486</v>
       </c>
       <c r="G75">
         <v>14.7</v>
@@ -7663,45 +7663,45 @@
         <v>11.66</v>
       </c>
       <c r="M75">
-        <v>3.32887811</v>
+        <v>3.52861526</v>
       </c>
       <c r="N75">
-        <v>8.33112189</v>
+        <v>8.13138474</v>
       </c>
       <c r="O75">
-        <v>1.4162907213</v>
+        <v>1.3823354058</v>
       </c>
       <c r="P75">
-        <v>6.9148311687</v>
+        <v>6.7490493342</v>
       </c>
       <c r="Q75">
-        <v>12.5548311687</v>
+        <v>12.3890493342</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1912153325082274</v>
+        <v>0.1965151439541174</v>
       </c>
       <c r="T75">
-        <v>3.358321766933659</v>
+        <v>3.480719259910332</v>
       </c>
       <c r="U75">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.17</v>
       </c>
       <c r="W75">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>3.502681568596094</v>
+        <v>3.304412394339642</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7709,22 +7709,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09046415742807051</v>
+        <v>0.09046198507891962</v>
       </c>
       <c r="C76">
-        <v>19.32099753583764</v>
+        <v>18.57781106778577</v>
       </c>
       <c r="D76">
-        <v>59.66959753583764</v>
+        <v>59.67031106778578</v>
       </c>
       <c r="E76">
-        <v>53.4586</v>
+        <v>54.2025</v>
       </c>
       <c r="F76">
-        <v>55.0486</v>
+        <v>55.7925</v>
       </c>
       <c r="G76">
         <v>14.7</v>
@@ -7745,28 +7745,28 @@
         <v>11.66</v>
       </c>
       <c r="M76">
-        <v>3.52861526</v>
+        <v>3.57629925</v>
       </c>
       <c r="N76">
-        <v>8.13138474</v>
+        <v>8.08370075</v>
       </c>
       <c r="O76">
-        <v>1.3823354058</v>
+        <v>1.3742291275</v>
       </c>
       <c r="P76">
-        <v>6.7490493342</v>
+        <v>6.709471622500001</v>
       </c>
       <c r="Q76">
-        <v>12.3890493342</v>
+        <v>12.3494716225</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1965151439541174</v>
+        <v>0.2022389403156784</v>
       </c>
       <c r="T76">
-        <v>3.480719259910332</v>
+        <v>3.612908552325137</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.304412394339642</v>
+        <v>3.260353562415114</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7791,22 +7791,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09046198507891962</v>
+        <v>0.0904598127297687</v>
       </c>
       <c r="C77">
-        <v>18.57781106778577</v>
+        <v>17.83462461679903</v>
       </c>
       <c r="D77">
-        <v>59.67031106778578</v>
+        <v>59.67102461679903</v>
       </c>
       <c r="E77">
-        <v>54.2025</v>
+        <v>54.9464</v>
       </c>
       <c r="F77">
-        <v>55.7925</v>
+        <v>56.5364</v>
       </c>
       <c r="G77">
         <v>14.7</v>
@@ -7827,28 +7827,28 @@
         <v>11.66</v>
       </c>
       <c r="M77">
-        <v>3.57629925</v>
+        <v>3.62398324</v>
       </c>
       <c r="N77">
-        <v>8.08370075</v>
+        <v>8.036016759999999</v>
       </c>
       <c r="O77">
-        <v>1.3742291275</v>
+        <v>1.3661228492</v>
       </c>
       <c r="P77">
-        <v>6.709471622500001</v>
+        <v>6.669893910799999</v>
       </c>
       <c r="Q77">
-        <v>12.3494716225</v>
+        <v>12.3098939108</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2022389403156784</v>
+        <v>0.2084397197073696</v>
       </c>
       <c r="T77">
-        <v>3.612908552325137</v>
+        <v>3.756113619107843</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.260353562415114</v>
+        <v>3.217454173435967</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7873,22 +7873,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0904598127297687</v>
+        <v>0.09045764038061779</v>
       </c>
       <c r="C78">
-        <v>17.83462461679903</v>
+        <v>17.09143818287799</v>
       </c>
       <c r="D78">
-        <v>59.67102461679903</v>
+        <v>59.67173818287799</v>
       </c>
       <c r="E78">
-        <v>54.9464</v>
+        <v>55.6903</v>
       </c>
       <c r="F78">
-        <v>56.5364</v>
+        <v>57.2803</v>
       </c>
       <c r="G78">
         <v>14.7</v>
@@ -7909,28 +7909,28 @@
         <v>11.66</v>
       </c>
       <c r="M78">
-        <v>3.62398324</v>
+        <v>3.671667230000001</v>
       </c>
       <c r="N78">
-        <v>8.036016759999999</v>
+        <v>7.98833277</v>
       </c>
       <c r="O78">
-        <v>1.3661228492</v>
+        <v>1.3580165709</v>
       </c>
       <c r="P78">
-        <v>6.669893910799999</v>
+        <v>6.630316199099999</v>
       </c>
       <c r="Q78">
-        <v>12.3098939108</v>
+        <v>12.2703161991</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2084397197073696</v>
+        <v>0.2151796973070339</v>
       </c>
       <c r="T78">
-        <v>3.756113619107843</v>
+        <v>3.911771300393393</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.217454173435967</v>
+        <v>3.175669054300435</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7955,22 +7955,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09045764038061779</v>
+        <v>0.0904554680314669</v>
       </c>
       <c r="C79">
-        <v>17.09143818287799</v>
+        <v>16.34825176602329</v>
       </c>
       <c r="D79">
-        <v>59.67173818287799</v>
+        <v>59.67245176602329</v>
       </c>
       <c r="E79">
-        <v>55.6903</v>
+        <v>56.4342</v>
       </c>
       <c r="F79">
-        <v>57.2803</v>
+        <v>58.0242</v>
       </c>
       <c r="G79">
         <v>14.7</v>
@@ -7991,28 +7991,28 @@
         <v>11.66</v>
       </c>
       <c r="M79">
-        <v>3.671667230000001</v>
+        <v>3.71935122</v>
       </c>
       <c r="N79">
-        <v>7.98833277</v>
+        <v>7.94064878</v>
       </c>
       <c r="O79">
-        <v>1.3580165709</v>
+        <v>1.3499102926</v>
       </c>
       <c r="P79">
-        <v>6.630316199099999</v>
+        <v>6.590738487399999</v>
       </c>
       <c r="Q79">
-        <v>12.2703161991</v>
+        <v>12.2307384874</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2151796973070339</v>
+        <v>0.2225324001430314</v>
       </c>
       <c r="T79">
-        <v>3.911771300393393</v>
+        <v>4.08157967997763</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -8029,7 +8029,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.175669054300435</v>
+        <v>3.134955348476071</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8037,22 +8037,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0904554680314669</v>
+        <v>0.090453295682316</v>
       </c>
       <c r="C80">
-        <v>16.34825176602329</v>
+        <v>15.60506536623551</v>
       </c>
       <c r="D80">
-        <v>59.67245176602329</v>
+        <v>59.67316536623552</v>
       </c>
       <c r="E80">
-        <v>56.4342</v>
+        <v>57.1781</v>
       </c>
       <c r="F80">
-        <v>58.0242</v>
+        <v>58.7681</v>
       </c>
       <c r="G80">
         <v>14.7</v>
@@ -8073,28 +8073,28 @@
         <v>11.66</v>
       </c>
       <c r="M80">
-        <v>3.71935122</v>
+        <v>3.76703521</v>
       </c>
       <c r="N80">
-        <v>7.94064878</v>
+        <v>7.89296479</v>
       </c>
       <c r="O80">
-        <v>1.3499102926</v>
+        <v>1.3418040143</v>
       </c>
       <c r="P80">
-        <v>6.590738487399999</v>
+        <v>6.5511607757</v>
       </c>
       <c r="Q80">
-        <v>12.2307384874</v>
+        <v>12.1911607757</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2225324001430314</v>
+        <v>0.2305853603919809</v>
       </c>
       <c r="T80">
-        <v>4.08157967997763</v>
+        <v>4.267560286188936</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.134955348476071</v>
+        <v>3.095272369381437</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8119,22 +8119,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.090453295682316</v>
+        <v>0.09045112333316509</v>
       </c>
       <c r="C81">
-        <v>15.60506536623551</v>
+        <v>14.8618789835153</v>
       </c>
       <c r="D81">
-        <v>59.67316536623552</v>
+        <v>59.6738789835153</v>
       </c>
       <c r="E81">
-        <v>57.1781</v>
+        <v>57.922</v>
       </c>
       <c r="F81">
-        <v>58.7681</v>
+        <v>59.512</v>
       </c>
       <c r="G81">
         <v>14.7</v>
@@ -8155,28 +8155,28 @@
         <v>11.66</v>
       </c>
       <c r="M81">
-        <v>3.76703521</v>
+        <v>3.8147192</v>
       </c>
       <c r="N81">
-        <v>7.89296479</v>
+        <v>7.845280799999999</v>
       </c>
       <c r="O81">
-        <v>1.3418040143</v>
+        <v>1.333697736</v>
       </c>
       <c r="P81">
-        <v>6.5511607757</v>
+        <v>6.511583064</v>
       </c>
       <c r="Q81">
-        <v>12.1911607757</v>
+        <v>12.151583064</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2305853603919809</v>
+        <v>0.2394436166658255</v>
       </c>
       <c r="T81">
-        <v>4.267560286188936</v>
+        <v>4.472138953021374</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.095272369381437</v>
+        <v>3.056581464764169</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8201,22 +8201,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09045112333316509</v>
+        <v>0.0904489509840142</v>
       </c>
       <c r="C82">
-        <v>14.8618789835153</v>
+        <v>14.11869261786324</v>
       </c>
       <c r="D82">
-        <v>59.6738789835153</v>
+        <v>59.67459261786325</v>
       </c>
       <c r="E82">
-        <v>57.922</v>
+        <v>58.6659</v>
       </c>
       <c r="F82">
-        <v>59.512</v>
+        <v>60.2559</v>
       </c>
       <c r="G82">
         <v>14.7</v>
@@ -8237,28 +8237,28 @@
         <v>11.66</v>
       </c>
       <c r="M82">
-        <v>3.8147192</v>
+        <v>3.862403190000001</v>
       </c>
       <c r="N82">
-        <v>7.845280799999999</v>
+        <v>7.79759681</v>
       </c>
       <c r="O82">
-        <v>1.333697736</v>
+        <v>1.3255914577</v>
       </c>
       <c r="P82">
-        <v>6.511583064</v>
+        <v>6.4720053523</v>
       </c>
       <c r="Q82">
-        <v>12.151583064</v>
+        <v>12.1120053523</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2394436166658255</v>
+        <v>0.2492343209684958</v>
       </c>
       <c r="T82">
-        <v>4.472138953021374</v>
+        <v>4.69825221636249</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.056581464764169</v>
+        <v>3.018845891125105</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8283,22 +8283,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0904489509840142</v>
+        <v>0.09575545863486327</v>
       </c>
       <c r="C83">
-        <v>14.11869261786324</v>
+        <v>11.68102042676398</v>
       </c>
       <c r="D83">
-        <v>59.67459261786325</v>
+        <v>57.98082042676398</v>
       </c>
       <c r="E83">
-        <v>58.6659</v>
+        <v>59.4098</v>
       </c>
       <c r="F83">
-        <v>60.2559</v>
+        <v>60.99980000000001</v>
       </c>
       <c r="G83">
         <v>14.7</v>
@@ -8319,45 +8319,45 @@
         <v>11.66</v>
       </c>
       <c r="M83">
-        <v>3.862403190000001</v>
+        <v>4.385885620000001</v>
       </c>
       <c r="N83">
-        <v>7.79759681</v>
+        <v>7.274114379999999</v>
       </c>
       <c r="O83">
-        <v>1.3255914577</v>
+        <v>1.2365994446</v>
       </c>
       <c r="P83">
-        <v>6.4720053523</v>
+        <v>6.037514935399999</v>
       </c>
       <c r="Q83">
-        <v>12.1120053523</v>
+        <v>11.6775149354</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2492343209684958</v>
+        <v>0.260112881304796</v>
       </c>
       <c r="T83">
-        <v>4.69825221636249</v>
+        <v>4.949489175630394</v>
       </c>
       <c r="U83">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V83">
         <v>0.17</v>
       </c>
       <c r="W83">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.018845891125105</v>
+        <v>2.658528062571773</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8365,22 +8365,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09575545863486327</v>
+        <v>0.09581802628571237</v>
       </c>
       <c r="C84">
-        <v>11.68102042676398</v>
+        <v>10.9177229326541</v>
       </c>
       <c r="D84">
-        <v>57.98082042676398</v>
+        <v>57.96142293265411</v>
       </c>
       <c r="E84">
-        <v>59.4098</v>
+        <v>60.1537</v>
       </c>
       <c r="F84">
-        <v>60.99980000000001</v>
+        <v>61.7437</v>
       </c>
       <c r="G84">
         <v>14.7</v>
@@ -8401,28 +8401,28 @@
         <v>11.66</v>
       </c>
       <c r="M84">
-        <v>4.385885620000001</v>
+        <v>4.43937203</v>
       </c>
       <c r="N84">
-        <v>7.274114379999999</v>
+        <v>7.22062797</v>
       </c>
       <c r="O84">
-        <v>1.2365994446</v>
+        <v>1.2275067549</v>
       </c>
       <c r="P84">
-        <v>6.037514935399999</v>
+        <v>5.9931212151</v>
       </c>
       <c r="Q84">
-        <v>11.6775149354</v>
+        <v>11.6331212151</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.260112881304796</v>
+        <v>0.2722712722688964</v>
       </c>
       <c r="T84">
-        <v>4.949489175630394</v>
+        <v>5.230283424223936</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.658528062571773</v>
+        <v>2.626497603986571</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8447,22 +8447,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09581802628571237</v>
+        <v>0.09588059393656148</v>
       </c>
       <c r="C85">
-        <v>10.9177229326541</v>
+        <v>10.15443841307401</v>
       </c>
       <c r="D85">
-        <v>57.96142293265411</v>
+        <v>57.94203841307402</v>
       </c>
       <c r="E85">
-        <v>60.1537</v>
+        <v>60.8976</v>
       </c>
       <c r="F85">
-        <v>61.7437</v>
+        <v>62.48760000000001</v>
       </c>
       <c r="G85">
         <v>14.7</v>
@@ -8483,28 +8483,28 @@
         <v>11.66</v>
       </c>
       <c r="M85">
-        <v>4.43937203</v>
+        <v>4.492858440000001</v>
       </c>
       <c r="N85">
-        <v>7.22062797</v>
+        <v>7.167141559999999</v>
       </c>
       <c r="O85">
-        <v>1.2275067549</v>
+        <v>1.2184140652</v>
       </c>
       <c r="P85">
-        <v>5.9931212151</v>
+        <v>5.948727494799999</v>
       </c>
       <c r="Q85">
-        <v>11.6331212151</v>
+        <v>11.5887274948</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2722712722688964</v>
+        <v>0.2859494621035094</v>
       </c>
       <c r="T85">
-        <v>5.230283424223936</v>
+        <v>5.546176953891671</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.626497603986571</v>
+        <v>2.595229775367683</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8529,22 +8529,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09588059393656148</v>
+        <v>0.09594316158741056</v>
       </c>
       <c r="C86">
-        <v>10.15443841307402</v>
+        <v>9.391166855010539</v>
       </c>
       <c r="D86">
-        <v>57.94203841307402</v>
+        <v>57.92266685501054</v>
       </c>
       <c r="E86">
-        <v>60.8976</v>
+        <v>61.64149999999999</v>
       </c>
       <c r="F86">
-        <v>62.4876</v>
+        <v>63.2315</v>
       </c>
       <c r="G86">
         <v>14.7</v>
@@ -8565,28 +8565,28 @@
         <v>11.66</v>
       </c>
       <c r="M86">
-        <v>4.49285844</v>
+        <v>4.546344850000001</v>
       </c>
       <c r="N86">
-        <v>7.16714156</v>
+        <v>7.11365515</v>
       </c>
       <c r="O86">
-        <v>1.2184140652</v>
+        <v>1.2093213755</v>
       </c>
       <c r="P86">
-        <v>5.9487274948</v>
+        <v>5.9043337745</v>
       </c>
       <c r="Q86">
-        <v>11.5887274948</v>
+        <v>11.5443337745</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2859494621035092</v>
+        <v>0.3014514105827371</v>
       </c>
       <c r="T86">
-        <v>5.546176953891668</v>
+        <v>5.904189620848433</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.595229775367684</v>
+        <v>2.564697660363358</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8611,22 +8611,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09594316158741056</v>
+        <v>0.09600572923825967</v>
       </c>
       <c r="C87">
-        <v>9.391166855010539</v>
+        <v>8.627908245467871</v>
       </c>
       <c r="D87">
-        <v>57.92266685501054</v>
+        <v>57.90330824546788</v>
       </c>
       <c r="E87">
-        <v>61.64149999999999</v>
+        <v>62.3854</v>
       </c>
       <c r="F87">
-        <v>63.2315</v>
+        <v>63.9754</v>
       </c>
       <c r="G87">
         <v>14.7</v>
@@ -8647,28 +8647,28 @@
         <v>11.66</v>
       </c>
       <c r="M87">
-        <v>4.546344850000001</v>
+        <v>4.59983126</v>
       </c>
       <c r="N87">
-        <v>7.11365515</v>
+        <v>7.06016874</v>
       </c>
       <c r="O87">
-        <v>1.2093213755</v>
+        <v>1.2002286858</v>
       </c>
       <c r="P87">
-        <v>5.9043337745</v>
+        <v>5.8599400542</v>
       </c>
       <c r="Q87">
-        <v>11.5443337745</v>
+        <v>11.4999400542</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3014514105827371</v>
+        <v>0.3191679231304262</v>
       </c>
       <c r="T87">
-        <v>5.904189620848433</v>
+        <v>6.313346954513307</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.564697660363358</v>
+        <v>2.534875594545179</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8693,22 +8693,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09600572923825967</v>
+        <v>0.09606829688910876</v>
       </c>
       <c r="C88">
-        <v>8.627908245467871</v>
+        <v>7.864662571467605</v>
       </c>
       <c r="D88">
-        <v>57.90330824546788</v>
+        <v>57.88396257146761</v>
       </c>
       <c r="E88">
-        <v>62.3854</v>
+        <v>63.1293</v>
       </c>
       <c r="F88">
-        <v>63.9754</v>
+        <v>64.7193</v>
       </c>
       <c r="G88">
         <v>14.7</v>
@@ -8729,28 +8729,28 @@
         <v>11.66</v>
       </c>
       <c r="M88">
-        <v>4.59983126</v>
+        <v>4.653317670000001</v>
       </c>
       <c r="N88">
-        <v>7.06016874</v>
+        <v>7.006682329999999</v>
       </c>
       <c r="O88">
-        <v>1.2002286858</v>
+        <v>1.1911359961</v>
       </c>
       <c r="P88">
-        <v>5.8599400542</v>
+        <v>5.8155463339</v>
       </c>
       <c r="Q88">
-        <v>11.4999400542</v>
+        <v>11.4555463339</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3191679231304262</v>
+        <v>0.3396100529931443</v>
       </c>
       <c r="T88">
-        <v>6.313346954513307</v>
+        <v>6.78545157028047</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.534875594545179</v>
+        <v>2.505739093458453</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8775,22 +8775,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09606829688910876</v>
+        <v>0.09897942453995787</v>
       </c>
       <c r="C89">
-        <v>7.864662571467605</v>
+        <v>6.234727420492945</v>
       </c>
       <c r="D89">
-        <v>57.88396257146761</v>
+        <v>56.99792742049295</v>
       </c>
       <c r="E89">
-        <v>63.1293</v>
+        <v>63.8732</v>
       </c>
       <c r="F89">
-        <v>64.7193</v>
+        <v>65.4632</v>
       </c>
       <c r="G89">
         <v>14.7</v>
@@ -8811,45 +8811,45 @@
         <v>11.66</v>
       </c>
       <c r="M89">
-        <v>4.653317670000001</v>
+        <v>4.96211056</v>
       </c>
       <c r="N89">
-        <v>7.006682329999999</v>
+        <v>6.69788944</v>
       </c>
       <c r="O89">
-        <v>1.1911359961</v>
+        <v>1.1386412048</v>
       </c>
       <c r="P89">
-        <v>5.8155463339</v>
+        <v>5.5592482352</v>
       </c>
       <c r="Q89">
-        <v>11.4555463339</v>
+        <v>11.1992482352</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3396100529931443</v>
+        <v>0.3634592044996489</v>
       </c>
       <c r="T89">
-        <v>6.78545157028047</v>
+        <v>7.336240288675494</v>
       </c>
       <c r="U89">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.17</v>
       </c>
       <c r="W89">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.505739093458453</v>
+        <v>2.349806571016829</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8857,22 +8857,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09897942453995787</v>
+        <v>0.09907436219080695</v>
       </c>
       <c r="C90">
-        <v>6.234727420492945</v>
+        <v>5.462388556115513</v>
       </c>
       <c r="D90">
-        <v>56.99792742049295</v>
+        <v>56.96948855611551</v>
       </c>
       <c r="E90">
-        <v>63.8732</v>
+        <v>64.61709999999999</v>
       </c>
       <c r="F90">
-        <v>65.4632</v>
+        <v>66.2071</v>
       </c>
       <c r="G90">
         <v>14.7</v>
@@ -8893,28 +8893,28 @@
         <v>11.66</v>
       </c>
       <c r="M90">
-        <v>4.96211056</v>
+        <v>5.01849818</v>
       </c>
       <c r="N90">
-        <v>6.69788944</v>
+        <v>6.64150182</v>
       </c>
       <c r="O90">
-        <v>1.1386412048</v>
+        <v>1.1290553094</v>
       </c>
       <c r="P90">
-        <v>5.5592482352</v>
+        <v>5.5124465106</v>
       </c>
       <c r="Q90">
-        <v>11.1992482352</v>
+        <v>11.1524465106</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3634592044996489</v>
+        <v>0.3916445653709724</v>
       </c>
       <c r="T90">
-        <v>7.336240288675494</v>
+        <v>7.987172410415067</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.349806571016829</v>
+        <v>2.323404249994169</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8939,22 +8939,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09907436219080695</v>
+        <v>0.09916929984165607</v>
       </c>
       <c r="C91">
-        <v>5.462388556115513</v>
+        <v>4.69007805647739</v>
       </c>
       <c r="D91">
-        <v>56.96948855611551</v>
+        <v>56.94107805647739</v>
       </c>
       <c r="E91">
-        <v>64.61709999999999</v>
+        <v>65.361</v>
       </c>
       <c r="F91">
-        <v>66.2071</v>
+        <v>66.95100000000001</v>
       </c>
       <c r="G91">
         <v>14.7</v>
@@ -8975,28 +8975,28 @@
         <v>11.66</v>
       </c>
       <c r="M91">
-        <v>5.01849818</v>
+        <v>5.074885800000001</v>
       </c>
       <c r="N91">
-        <v>6.64150182</v>
+        <v>6.5851142</v>
       </c>
       <c r="O91">
-        <v>1.1290553094</v>
+        <v>1.119469414</v>
       </c>
       <c r="P91">
-        <v>5.5124465106</v>
+        <v>5.465644785999999</v>
       </c>
       <c r="Q91">
-        <v>11.1524465106</v>
+        <v>11.105644786</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3916445653709724</v>
+        <v>0.4254669984165607</v>
       </c>
       <c r="T91">
-        <v>7.987172410415067</v>
+        <v>8.768290956502556</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.323404249994169</v>
+        <v>2.297588647216455</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09916929984165607</v>
+        <v>0.09926423749250515</v>
       </c>
       <c r="C92">
-        <v>4.69007805647739</v>
+        <v>3.917795879163535</v>
       </c>
       <c r="D92">
-        <v>56.94107805647739</v>
+        <v>56.91269587916354</v>
       </c>
       <c r="E92">
-        <v>65.361</v>
+        <v>66.1049</v>
       </c>
       <c r="F92">
-        <v>66.95100000000001</v>
+        <v>67.6949</v>
       </c>
       <c r="G92">
         <v>14.7</v>
@@ -9057,28 +9057,28 @@
         <v>11.66</v>
       </c>
       <c r="M92">
-        <v>5.074885800000001</v>
+        <v>5.13127342</v>
       </c>
       <c r="N92">
-        <v>6.5851142</v>
+        <v>6.52872658</v>
       </c>
       <c r="O92">
-        <v>1.119469414</v>
+        <v>1.1098835186</v>
       </c>
       <c r="P92">
-        <v>5.465644785999999</v>
+        <v>5.4188430614</v>
       </c>
       <c r="Q92">
-        <v>11.105644786</v>
+        <v>11.0588430614</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4254669984165607</v>
+        <v>0.4668055276945018</v>
       </c>
       <c r="T92">
-        <v>8.768290956502556</v>
+        <v>9.722991401720597</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.297588647216455</v>
+        <v>2.272340420323967</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9103,22 +9103,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09926423749250515</v>
+        <v>0.09935917514335424</v>
       </c>
       <c r="C93">
-        <v>3.917795879163535</v>
+        <v>3.145541981843422</v>
       </c>
       <c r="D93">
-        <v>56.91269587916354</v>
+        <v>56.88434198184342</v>
       </c>
       <c r="E93">
-        <v>66.1049</v>
+        <v>66.8488</v>
       </c>
       <c r="F93">
-        <v>67.6949</v>
+        <v>68.4388</v>
       </c>
       <c r="G93">
         <v>14.7</v>
@@ -9139,28 +9139,28 @@
         <v>11.66</v>
       </c>
       <c r="M93">
-        <v>5.13127342</v>
+        <v>5.18766104</v>
       </c>
       <c r="N93">
-        <v>6.52872658</v>
+        <v>6.47233896</v>
       </c>
       <c r="O93">
-        <v>1.1098835186</v>
+        <v>1.1002976232</v>
       </c>
       <c r="P93">
-        <v>5.4188430614</v>
+        <v>5.3720413368</v>
       </c>
       <c r="Q93">
-        <v>11.0588430614</v>
+        <v>11.0120413368</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4668055276945018</v>
+        <v>0.5184786892919283</v>
       </c>
       <c r="T93">
-        <v>9.722991401720597</v>
+        <v>10.91636695824315</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.272340420323967</v>
+        <v>2.247641067929141</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9185,22 +9185,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09935917514335424</v>
+        <v>0.09945411279420334</v>
       </c>
       <c r="C94">
-        <v>3.145541981843422</v>
+        <v>2.373316322270782</v>
       </c>
       <c r="D94">
-        <v>56.88434198184342</v>
+        <v>56.8560163222708</v>
       </c>
       <c r="E94">
-        <v>66.8488</v>
+        <v>67.59270000000001</v>
       </c>
       <c r="F94">
-        <v>68.4388</v>
+        <v>69.18270000000001</v>
       </c>
       <c r="G94">
         <v>14.7</v>
@@ -9221,28 +9221,28 @@
         <v>11.66</v>
       </c>
       <c r="M94">
-        <v>5.18766104</v>
+        <v>5.244048660000002</v>
       </c>
       <c r="N94">
-        <v>6.47233896</v>
+        <v>6.415951339999999</v>
       </c>
       <c r="O94">
-        <v>1.1002976232</v>
+        <v>1.0907117278</v>
       </c>
       <c r="P94">
-        <v>5.3720413368</v>
+        <v>5.325239612199999</v>
       </c>
       <c r="Q94">
-        <v>11.0120413368</v>
+        <v>10.9652396122</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5184786892919283</v>
+        <v>0.5849156113457623</v>
       </c>
       <c r="T94">
-        <v>10.91636695824315</v>
+        <v>12.45070695948643</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.247641067929141</v>
+        <v>2.223472884403021</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9267,22 +9267,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09945411279420334</v>
+        <v>0.09954905044505244</v>
       </c>
       <c r="C95">
-        <v>2.373316322270782</v>
+        <v>1.60111885828357</v>
       </c>
       <c r="D95">
-        <v>56.8560163222708</v>
+        <v>56.82771885828357</v>
       </c>
       <c r="E95">
-        <v>67.59270000000001</v>
+        <v>68.3366</v>
       </c>
       <c r="F95">
-        <v>69.18270000000001</v>
+        <v>69.92660000000001</v>
       </c>
       <c r="G95">
         <v>14.7</v>
@@ -9303,28 +9303,28 @@
         <v>11.66</v>
       </c>
       <c r="M95">
-        <v>5.244048660000002</v>
+        <v>5.300436280000001</v>
       </c>
       <c r="N95">
-        <v>6.415951339999999</v>
+        <v>6.359563719999999</v>
       </c>
       <c r="O95">
-        <v>1.0907117278</v>
+        <v>1.0811258324</v>
       </c>
       <c r="P95">
-        <v>5.325239612199999</v>
+        <v>5.278437887599999</v>
       </c>
       <c r="Q95">
-        <v>10.9652396122</v>
+        <v>10.9184378876</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5849156113457623</v>
+        <v>0.6734981740842079</v>
       </c>
       <c r="T95">
-        <v>12.45070695948643</v>
+        <v>14.49649362781081</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.223472884403021</v>
+        <v>2.199818917547669</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9349,22 +9349,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09954905044505244</v>
+        <v>0.09964398809590154</v>
       </c>
       <c r="C96">
-        <v>1.60111885828357</v>
+        <v>0.8289495478035178</v>
       </c>
       <c r="D96">
-        <v>56.82771885828357</v>
+        <v>56.79944954780353</v>
       </c>
       <c r="E96">
-        <v>68.3366</v>
+        <v>69.0805</v>
       </c>
       <c r="F96">
-        <v>69.92660000000001</v>
+        <v>70.6705</v>
       </c>
       <c r="G96">
         <v>14.7</v>
@@ -9385,28 +9385,28 @@
         <v>11.66</v>
       </c>
       <c r="M96">
-        <v>5.300436280000001</v>
+        <v>5.356823900000001</v>
       </c>
       <c r="N96">
-        <v>6.359563719999999</v>
+        <v>6.303176099999999</v>
       </c>
       <c r="O96">
-        <v>1.0811258324</v>
+        <v>1.071539937</v>
       </c>
       <c r="P96">
-        <v>5.278437887599999</v>
+        <v>5.231636162999999</v>
       </c>
       <c r="Q96">
-        <v>10.9184378876</v>
+        <v>10.871636163</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6734981740842079</v>
+        <v>0.7975137619180318</v>
       </c>
       <c r="T96">
-        <v>14.49649362781081</v>
+        <v>17.36059496346494</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.199818917547669</v>
+        <v>2.176662928941905</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9431,22 +9431,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09964398809590154</v>
+        <v>0.09973892574675064</v>
       </c>
       <c r="C97">
-        <v>0.8289495478035178</v>
+        <v>0.05680834883611396</v>
       </c>
       <c r="D97">
-        <v>56.79944954780353</v>
+        <v>56.77120834883612</v>
       </c>
       <c r="E97">
-        <v>69.0805</v>
+        <v>69.8244</v>
       </c>
       <c r="F97">
-        <v>70.6705</v>
+        <v>71.4144</v>
       </c>
       <c r="G97">
         <v>14.7</v>
@@ -9467,28 +9467,28 @@
         <v>11.66</v>
       </c>
       <c r="M97">
-        <v>5.356823900000001</v>
+        <v>5.413211520000001</v>
       </c>
       <c r="N97">
-        <v>6.303176099999999</v>
+        <v>6.246788479999999</v>
       </c>
       <c r="O97">
-        <v>1.071539937</v>
+        <v>1.0619540416</v>
       </c>
       <c r="P97">
-        <v>5.231636162999999</v>
+        <v>5.184834438399999</v>
       </c>
       <c r="Q97">
-        <v>10.871636163</v>
+        <v>10.8248344384</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7975137619180318</v>
+        <v>0.9835371436687675</v>
       </c>
       <c r="T97">
-        <v>17.36059496346494</v>
+        <v>21.65674696694613</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.176662928941905</v>
+        <v>2.153989356765427</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9513,22 +9513,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09973892574675063</v>
+        <v>0.09983386339759973</v>
       </c>
       <c r="C98">
-        <v>0.05680834883611396</v>
+        <v>-0.7153047805297064</v>
       </c>
       <c r="D98">
-        <v>56.77120834883612</v>
+        <v>56.74299521947029</v>
       </c>
       <c r="E98">
-        <v>69.8244</v>
+        <v>70.56829999999999</v>
       </c>
       <c r="F98">
-        <v>71.4144</v>
+        <v>72.1583</v>
       </c>
       <c r="G98">
         <v>14.7</v>
@@ -9549,28 +9549,28 @@
         <v>11.66</v>
       </c>
       <c r="M98">
-        <v>5.413211520000001</v>
+        <v>5.469599140000001</v>
       </c>
       <c r="N98">
-        <v>6.246788479999999</v>
+        <v>6.19040086</v>
       </c>
       <c r="O98">
-        <v>1.0619540416</v>
+        <v>1.0523681462</v>
       </c>
       <c r="P98">
-        <v>5.184834438399999</v>
+        <v>5.138032713799999</v>
       </c>
       <c r="Q98">
-        <v>10.8248344384</v>
+        <v>10.7780327138</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9835371436687649</v>
+        <v>1.293576113253323</v>
       </c>
       <c r="T98">
-        <v>21.65674696694607</v>
+        <v>28.81700030608137</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.153989356765427</v>
+        <v>2.131783280922484</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9595,22 +9595,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09983386339759973</v>
+        <v>0.09992880104844884</v>
       </c>
       <c r="C99">
-        <v>-0.7153047805297064</v>
+        <v>-1.487389882121732</v>
       </c>
       <c r="D99">
-        <v>56.74299521947029</v>
+        <v>56.71481011787827</v>
       </c>
       <c r="E99">
-        <v>70.56829999999999</v>
+        <v>71.31219999999999</v>
       </c>
       <c r="F99">
-        <v>72.1583</v>
+        <v>72.90219999999999</v>
       </c>
       <c r="G99">
         <v>14.7</v>
@@ -9631,28 +9631,28 @@
         <v>11.66</v>
       </c>
       <c r="M99">
-        <v>5.469599140000001</v>
+        <v>5.52598676</v>
       </c>
       <c r="N99">
-        <v>6.19040086</v>
+        <v>6.13401324</v>
       </c>
       <c r="O99">
-        <v>1.0523681462</v>
+        <v>1.0427822508</v>
       </c>
       <c r="P99">
-        <v>5.138032713799999</v>
+        <v>5.0912309892</v>
       </c>
       <c r="Q99">
-        <v>10.7780327138</v>
+        <v>10.7312309892</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.293576113253323</v>
+        <v>1.91365405242244</v>
       </c>
       <c r="T99">
-        <v>28.81700030608137</v>
+        <v>43.13750698435197</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.131783280922484</v>
+        <v>2.110030390300826</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9677,22 +9677,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09992880104844884</v>
+        <v>0.1000237386992979</v>
       </c>
       <c r="C100">
-        <v>-1.487389882121732</v>
+        <v>-2.259446997684677</v>
       </c>
       <c r="D100">
-        <v>56.71481011787827</v>
+        <v>56.68665300231532</v>
       </c>
       <c r="E100">
-        <v>71.31219999999999</v>
+        <v>72.0561</v>
       </c>
       <c r="F100">
-        <v>72.90219999999999</v>
+        <v>73.6461</v>
       </c>
       <c r="G100">
         <v>14.7</v>
@@ -9713,28 +9713,28 @@
         <v>11.66</v>
       </c>
       <c r="M100">
-        <v>5.52598676</v>
+        <v>5.582374380000001</v>
       </c>
       <c r="N100">
-        <v>6.13401324</v>
+        <v>6.077625619999999</v>
       </c>
       <c r="O100">
-        <v>1.0427822508</v>
+        <v>1.0331963554</v>
       </c>
       <c r="P100">
-        <v>5.0912309892</v>
+        <v>5.0444292646</v>
       </c>
       <c r="Q100">
-        <v>10.7312309892</v>
+        <v>10.6844292646</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.91365405242244</v>
+        <v>3.773887869929789</v>
       </c>
       <c r="T100">
-        <v>43.13750698435197</v>
+        <v>86.09902701916373</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9751,91 +9751,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.110030390300826</v>
+        <v>2.088716952014959</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1000237386992979</v>
-      </c>
-      <c r="C101">
-        <v>-2.259446997684677</v>
-      </c>
-      <c r="D101">
-        <v>56.68665300231532</v>
-      </c>
-      <c r="E101">
-        <v>72.0561</v>
-      </c>
-      <c r="F101">
-        <v>73.6461</v>
-      </c>
-      <c r="G101">
-        <v>14.7</v>
-      </c>
-      <c r="H101">
-        <v>72.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.3</v>
-      </c>
-      <c r="K101">
-        <v>5.64</v>
-      </c>
-      <c r="L101">
-        <v>11.66</v>
-      </c>
-      <c r="M101">
-        <v>5.582374380000001</v>
-      </c>
-      <c r="N101">
-        <v>6.077625619999999</v>
-      </c>
-      <c r="O101">
-        <v>1.0331963554</v>
-      </c>
-      <c r="P101">
-        <v>5.0444292646</v>
-      </c>
-      <c r="Q101">
-        <v>10.6844292646</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.773887869929789</v>
-      </c>
-      <c r="T101">
-        <v>86.09902701916373</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.17</v>
-      </c>
-      <c r="W101">
-        <v>0.062914</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.088716952014959</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
